--- a/data/record_collection.xlsx
+++ b/data/record_collection.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Albums" sheetId="1" r:id="Rfc5e5a39be584981"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracks" sheetId="2" r:id="R346b9125d76f4a3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research_26_41" sheetId="3" r:id="R399d00c2e8644940"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Albums" sheetId="1" r:id="Rf8931e66d2164752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracks" sheetId="2" r:id="Rfe5492459f274665"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research_26_41" sheetId="3" r:id="R3224f335299f4653"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45,7 +45,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -55,6 +55,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -88,7 +98,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1">
@@ -140,6 +150,24 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -218,8 +246,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="AlbumsTable" displayName="AlbumsTable" ref="A1:AD42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="30">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="AlbumsTable" displayName="AlbumsTable" ref="A1:AI42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="35">
     <x:tableColumn id="1" name="Collection ID"/>
     <x:tableColumn id="2" name="Artist (Japanese)"/>
     <x:tableColumn id="3" name="Artist (English)"/>
@@ -250,6 +278,11 @@
     <x:tableColumn id="28" name="Verification Issues"/>
     <x:tableColumn id="29" name="Verification Status"/>
     <x:tableColumn id="30" name="Last Updated"/>
+    <x:tableColumn id="31" name="Album Summary"/>
+    <x:tableColumn id="32" name="Summary Source"/>
+    <x:tableColumn id="33" name="Summary Source Label"/>
+    <x:tableColumn id="34" name="Artist Info URL"/>
+    <x:tableColumn id="35" name="Artist Info Label"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -515,101 +548,121 @@
     <x:col min="28" max="28" width="60" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="24" hidden="0" customWidth="1"/>
     <x:col min="30" max="30" width="18" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="80" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="60" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="36" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="60" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="32" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
-      <x:c r="A1" s="20" t="str">
+      <x:c r="A1" s="27" t="str">
         <x:v>Collection ID</x:v>
       </x:c>
-      <x:c r="B1" s="20" t="str">
+      <x:c r="B1" s="27" t="str">
         <x:v>Artist (Japanese)</x:v>
       </x:c>
-      <x:c r="C1" s="20" t="str">
+      <x:c r="C1" s="27" t="str">
         <x:v>Artist (English)</x:v>
       </x:c>
-      <x:c r="D1" s="20" t="str">
+      <x:c r="D1" s="27" t="str">
         <x:v>Title (Japanese)</x:v>
       </x:c>
-      <x:c r="E1" s="20" t="str">
+      <x:c r="E1" s="27" t="str">
         <x:v>Title (English)</x:v>
       </x:c>
-      <x:c r="F1" s="20" t="str">
+      <x:c r="F1" s="27" t="str">
         <x:v>Label</x:v>
       </x:c>
-      <x:c r="G1" s="20" t="str">
+      <x:c r="G1" s="27" t="str">
         <x:v>Catalog Number</x:v>
       </x:c>
-      <x:c r="H1" s="20" t="str">
+      <x:c r="H1" s="27" t="str">
         <x:v>Year</x:v>
       </x:c>
-      <x:c r="I1" s="20" t="str">
+      <x:c r="I1" s="27" t="str">
         <x:v>Format</x:v>
       </x:c>
-      <x:c r="J1" s="20" t="str">
+      <x:c r="J1" s="27" t="str">
         <x:v>Country</x:v>
       </x:c>
-      <x:c r="K1" s="20" t="str">
+      <x:c r="K1" s="27" t="str">
         <x:v>Genre</x:v>
       </x:c>
-      <x:c r="L1" s="20" t="str">
+      <x:c r="L1" s="27" t="str">
         <x:v>Retail Price (JPY)</x:v>
       </x:c>
-      <x:c r="M1" s="20" t="str">
+      <x:c r="M1" s="27" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="N1" s="20" t="str">
+      <x:c r="N1" s="27" t="str">
         <x:v>Source Photo</x:v>
       </x:c>
-      <x:c r="O1" s="20" t="str">
+      <x:c r="O1" s="27" t="str">
         <x:v>Cover Image Filename</x:v>
       </x:c>
-      <x:c r="P1" s="20" t="str">
+      <x:c r="P1" s="27" t="str">
         <x:v>Discogs URL</x:v>
       </x:c>
-      <x:c r="Q1" s="21" t="str">
+      <x:c r="Q1" s="28" t="str">
         <x:v>Cover Source</x:v>
       </x:c>
-      <x:c r="R1" s="21" t="str">
+      <x:c r="R1" s="28" t="str">
         <x:v>Cover Status</x:v>
       </x:c>
-      <x:c r="S1" s="21" t="str">
+      <x:c r="S1" s="28" t="str">
         <x:v>Research Notes</x:v>
       </x:c>
-      <x:c r="T1" s="21" t="str">
+      <x:c r="T1" s="28" t="str">
         <x:v>Obi</x:v>
       </x:c>
-      <x:c r="U1" s="21" t="str">
+      <x:c r="U1" s="28" t="str">
         <x:v>Shelf Location</x:v>
       </x:c>
-      <x:c r="V1" s="21" t="str">
+      <x:c r="V1" s="28" t="str">
         <x:v>Vinyl Condition</x:v>
       </x:c>
-      <x:c r="W1" s="21" t="str">
+      <x:c r="W1" s="28" t="str">
         <x:v>Sleeve Condition</x:v>
       </x:c>
-      <x:c r="X1" s="21" t="str">
+      <x:c r="X1" s="28" t="str">
         <x:v>Inserts</x:v>
       </x:c>
-      <x:c r="Y1" s="21" t="str">
+      <x:c r="Y1" s="28" t="str">
         <x:v>Purchase Date</x:v>
       </x:c>
-      <x:c r="Z1" s="21" t="str">
+      <x:c r="Z1" s="28" t="str">
         <x:v>Price Paid</x:v>
       </x:c>
-      <x:c r="AA1" s="21" t="str">
+      <x:c r="AA1" s="28" t="str">
         <x:v>Purchase Currency</x:v>
       </x:c>
-      <x:c r="AB1" s="21" t="str">
+      <x:c r="AB1" s="28" t="str">
         <x:v>Verification Issues</x:v>
       </x:c>
-      <x:c r="AC1" s="21" t="str">
+      <x:c r="AC1" s="28" t="str">
         <x:v>Verification Status</x:v>
       </x:c>
-      <x:c r="AD1" s="21" t="str">
+      <x:c r="AD1" s="28" t="str">
         <x:v>Last Updated</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" ht="90" customHeight="1">
+      <x:c r="AE1" s="28" t="str">
+        <x:v>Album Summary</x:v>
+      </x:c>
+      <x:c r="AF1" s="28" t="str">
+        <x:v>Summary Source</x:v>
+      </x:c>
+      <x:c r="AG1" s="28" t="str">
+        <x:v>Summary Source Label</x:v>
+      </x:c>
+      <x:c r="AH1" s="28" t="str">
+        <x:v>Artist Info URL</x:v>
+      </x:c>
+      <x:c r="AI1" s="28" t="str">
+        <x:v>Artist Info Label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="120" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>01</x:v>
       </x:c>
@@ -687,8 +740,23 @@
       <x:c r="AD2" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" ht="90" customHeight="1">
+      <x:c r="AE2" s="12" t="str">
+        <x:v>A collection of enka songs with travelling and period-story themes, including “Meigetsu Akagiyama”, “Ruten” and “Akagi no Komoriuta”. The source listing documents a later export pressing of the same programme; the pressing of this copy still needs confirmation.</x:v>
+      </x:c>
+      <x:c r="AF2" s="12" t="str">
+        <x:v>https://www.discogs.com/release/5826667</x:v>
+      </x:c>
+      <x:c r="AG2" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH2" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/495700</x:v>
+      </x:c>
+      <x:c r="AI2" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="120" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>02</x:v>
       </x:c>
@@ -762,8 +830,23 @@
       <x:c r="AD3" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="90" customHeight="1">
+      <x:c r="AE3" s="12" t="str">
+        <x:v>This twelve-song collection pairs the title song with “Jūroku no Koi”, “Mineko no Komoriuta” and “Furusato Koiuta”, drawing on enka and kayōkyoku repertoire.</x:v>
+      </x:c>
+      <x:c r="AF3" s="12" t="str">
+        <x:v>https://www.discogs.com/release/7413926</x:v>
+      </x:c>
+      <x:c r="AG3" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH3" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/3756573</x:v>
+      </x:c>
+      <x:c r="AI3" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="120" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>03</x:v>
       </x:c>
@@ -804,17 +887,22 @@
       <x:c r="N4" s="6" t="str">
         <x:v>IMG_3229.jpg — bottom left</x:v>
       </x:c>
-      <x:c r="O4" s="6" t="str"/>
+      <x:c r="O4" s="6" t="str">
+        <x:v>03_reference_crop.jpg</x:v>
+      </x:c>
       <x:c r="P4" s="6" t="str">
         <x:v>https://www.discogs.com/release/9146810</x:v>
       </x:c>
-      <x:c r="Q4" s="12" t="str"/>
+      <x:c r="Q4" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3229.jpg</x:v>
+      </x:c>
       <x:c r="R4" s="12" t="str">
-        <x:v>pending</x:v>
+        <x:v>reference_photo</x:v>
       </x:c>
       <x:c r="S4" s="12" t="str">
         <x:v>Photo audit 2026-09-17: IMG_3229.jpg, bottom left. Pale sleeve with portrait in a dark kimono and sakura branches; no obi visible.
-Earlier imported notes (retained as history; may contain superseded readings): CORRECTED ID: not 石川さゆり. Cover brands「さくらの歌」; Discogs/FanFan list as「さくら貝の歌 倍賞千恵子の日本の詩」SKK-680 (1971 gatefold). No obi on this copy. Photo credit: Shinsuke Ame.</x:v>
+Earlier imported notes (retained as history; may contain superseded readings): CORRECTED ID: not 石川さゆり. Cover brands「さくらの歌」; Discogs/FanFan list as「さくら貝の歌 倍賞千恵子の日本の詩」SKK-680 (1971 gatefold). No obi on this copy. Photo credit: Shinsuke Ame.
+2026-09-17 artwork update: user authorised a straightened crop of the original reference photo while a clean online match remains unavailable.</x:v>
       </x:c>
       <x:c r="T4" s="12" t="str">
         <x:v>Not visible in supplied photo</x:v>
@@ -835,8 +923,23 @@
       <x:c r="AD4" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" ht="90" customHeight="1">
+      <x:c r="AE4" s="12" t="str">
+        <x:v>A Japanese song collection by Chieko Baisho, presented with a cherry-blossom portrait sleeve. The photographed cover is the identification source here: its full title and exact edition still need confirmation.</x:v>
+      </x:c>
+      <x:c r="AF4" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3229.jpg</x:v>
+      </x:c>
+      <x:c r="AG4" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH4" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/575464</x:v>
+      </x:c>
+      <x:c r="AI4" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="120" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>04</x:v>
       </x:c>
@@ -910,8 +1013,23 @@
       <x:c r="AD5" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="90" customHeight="1">
+      <x:c r="AE5" s="12" t="str">
+        <x:v>A twelve-track album built around songs of separation, including the title track, “Kyoto kara Hakata made” and “Ryōta no Komoriuta”. Released by RCA in 1972.</x:v>
+      </x:c>
+      <x:c r="AF5" s="12" t="str">
+        <x:v>https://www.discogs.com/release/14837576</x:v>
+      </x:c>
+      <x:c r="AG5" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH5" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/1070643</x:v>
+      </x:c>
+      <x:c r="AI5" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="120" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>05</x:v>
       </x:c>
@@ -987,8 +1105,23 @@
       <x:c r="AD6" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="90" customHeight="1">
+      <x:c r="AE6" s="12" t="str">
+        <x:v>Honda’s 1971 folk and popular-song album includes “Aru Asa Umarete”, “Kibō no Kuni” and the title song “Ieji”. The sleeve presents it under the English title Going Home.</x:v>
+      </x:c>
+      <x:c r="AF6" s="12" t="str">
+        <x:v>https://www.discogs.com/release/29605807</x:v>
+      </x:c>
+      <x:c r="AG6" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH6" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/1330031</x:v>
+      </x:c>
+      <x:c r="AI6" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="120" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>06</x:v>
       </x:c>
@@ -1027,17 +1160,22 @@
       <x:c r="N7" s="6" t="str">
         <x:v>IMG_3230.jpg — top right</x:v>
       </x:c>
-      <x:c r="O7" s="6" t="str"/>
+      <x:c r="O7" s="6" t="str">
+        <x:v>06_reference_crop.jpg</x:v>
+      </x:c>
       <x:c r="P7" s="6" t="str">
         <x:v>https://www.discogs.com/search/?q=%E9%83%BD%E3%81%AF%E3%82%8B%E3%81%BF%20%20%E9%83%BD%E3%81%AF%E3%82%8B%E3%81%BF%E3%81%AE%E6%B5%81%E3%81%97%E5%94%84%20/%20%E9%AD%85%E5%8A%9B%E3%81%AE%E3%81%99%E3%81%B9%E3%81%A6</x:v>
       </x:c>
-      <x:c r="Q7" s="12" t="str"/>
+      <x:c r="Q7" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3230.jpg</x:v>
+      </x:c>
       <x:c r="R7" s="12" t="str">
-        <x:v>pending</x:v>
+        <x:v>reference_photo</x:v>
       </x:c>
       <x:c r="S7" s="12" t="str">
         <x:v>Photo audit 2026-09-17: IMG_3230.jpg, top right. Red kimono portrait with red obi. A separate album from #01.
-Earlier imported notes (retained as history; may contain superseded readings): DIFFERENT from #01: red kimono close-up cover, red obi, ¥2400. Branded 流し唄 with 魅力のすべて. Full Discogs match uncertain; tracklist only partially visible on obi — DO NOT invent. Treat as separate collection entry.</x:v>
+Earlier imported notes (retained as history; may contain superseded readings): DIFFERENT from #01: red kimono close-up cover, red obi, ¥2400. Branded 流し唄 with 魅力のすべて. Full Discogs match uncertain; tracklist only partially visible on obi — DO NOT invent. Treat as separate collection entry.
+2026-09-17 artwork update: user authorised a straightened crop of the original reference photo while a clean online match remains unavailable.</x:v>
       </x:c>
       <x:c r="T7" s="12" t="str">
         <x:v>Present (visible in photo)</x:v>
@@ -1058,8 +1196,23 @@
       <x:c r="AD7" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="90" customHeight="1">
+      <x:c r="AE7" s="12" t="str">
+        <x:v>The sleeve presents this collection as Harumi Miyako’s Nagashiuta / Miryoku no Subete. Its red-kimono portrait distinguishes it from the other Nagashiuta record in this collection; the exact edition remains unidentified.</x:v>
+      </x:c>
+      <x:c r="AF7" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3230.jpg</x:v>
+      </x:c>
+      <x:c r="AG7" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH7" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/495700</x:v>
+      </x:c>
+      <x:c r="AI7" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="120" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>07</x:v>
       </x:c>
@@ -1133,8 +1286,23 @@
       <x:c r="AD8" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="90" customHeight="1">
+      <x:c r="AE8" s="12" t="str">
+        <x:v>A fourteen-song selection spanning “Osaka Shigure”, “Kita no Yado kara” and “Suki ni Natta Hito”. This is the AX-7293 collection, distinct from the other Best Album sleeve on these shelves.</x:v>
+      </x:c>
+      <x:c r="AF8" s="12" t="str">
+        <x:v>https://www.discogs.com/release/19552204</x:v>
+      </x:c>
+      <x:c r="AG8" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH8" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/495700</x:v>
+      </x:c>
+      <x:c r="AI8" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="120" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>08</x:v>
       </x:c>
@@ -1210,8 +1378,23 @@
       <x:c r="AD9" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="90" customHeight="1">
+      <x:c r="AE9" s="12" t="str">
+        <x:v>Sixteen enka selections, opening with “Uminari no Uta” and “Kita no Yado kara”. The programme also includes “Namida no Renrakusen” and “Anko Tsubaki wa Koi no Hana”.</x:v>
+      </x:c>
+      <x:c r="AF9" s="12" t="str">
+        <x:v>https://www.discogs.com/release/21285337</x:v>
+      </x:c>
+      <x:c r="AG9" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH9" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/495700</x:v>
+      </x:c>
+      <x:c r="AI9" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="120" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>09</x:v>
       </x:c>
@@ -1285,8 +1468,23 @@
       <x:c r="AD10" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="90" customHeight="1">
+      <x:c r="AE10" s="12" t="str">
+        <x:v>A two-record selection of twenty-four songs, including “Hitorine no Komoriuta”, “Sensō wa Shiranai” and “Toki ni wa Haha no Nai Ko no Yō ni”. Released on Polydor in 1970.</x:v>
+      </x:c>
+      <x:c r="AF10" s="12" t="str">
+        <x:v>https://www.discogs.com/release/10000075</x:v>
+      </x:c>
+      <x:c r="AG10" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH10" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/66364</x:v>
+      </x:c>
+      <x:c r="AI10" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="120" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>10</x:v>
       </x:c>
@@ -1358,8 +1556,23 @@
       <x:c r="AD11" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="90" customHeight="1">
+      <x:c r="AE11" s="12" t="str">
+        <x:v>A family-oriented collection of familiar international songs. Its twelve selections include “Do-Re-Mi”, “Please Mr. Postman”, “Jambalaya” and “Over the Rainbow”.</x:v>
+      </x:c>
+      <x:c r="AF11" s="12" t="str">
+        <x:v>https://www.discogs.com/release/11651826</x:v>
+      </x:c>
+      <x:c r="AG11" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH11" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/7792268</x:v>
+      </x:c>
+      <x:c r="AI11" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="120" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>11</x:v>
       </x:c>
@@ -1435,8 +1648,23 @@
       <x:c r="AD12" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="90" customHeight="1">
+      <x:c r="AE12" s="12" t="str">
+        <x:v>A twelve-song selection in CBS/Sony’s Gift Pack Series, bringing together “Shiroi Hana”, “Mimi o Sumashite Goran” and “Aki demo nai noni”.</x:v>
+      </x:c>
+      <x:c r="AF12" s="12" t="str">
+        <x:v>https://www.discogs.com/release/6410826</x:v>
+      </x:c>
+      <x:c r="AG12" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH12" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/1330031</x:v>
+      </x:c>
+      <x:c r="AI12" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="120" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>12</x:v>
       </x:c>
@@ -1512,8 +1740,23 @@
       <x:c r="AD13" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="90" customHeight="1">
+      <x:c r="AE13" s="12" t="str">
+        <x:v>A collection of enduring folk songs, including “Hitori no Te”, “Tōi Sekai ni” and “Kyō no Hi wa Sayōnara”. The title track opens this 1971 CBS/Sony album.</x:v>
+      </x:c>
+      <x:c r="AF13" s="12" t="str">
+        <x:v>https://www.discogs.com/release/14124740</x:v>
+      </x:c>
+      <x:c r="AG13" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH13" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/1330031</x:v>
+      </x:c>
+      <x:c r="AI13" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="120" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>13</x:v>
       </x:c>
@@ -1550,17 +1793,22 @@
       <x:c r="N14" s="6" t="str">
         <x:v>IMG_3236.jpg — top left</x:v>
       </x:c>
-      <x:c r="O14" s="6" t="str"/>
+      <x:c r="O14" s="6" t="str">
+        <x:v>13_reference_crop.jpg</x:v>
+      </x:c>
       <x:c r="P14" s="6" t="str">
         <x:v>https://www.discogs.com/search/?q=%E5%AE%AE%E5%9F%8E%E9%81%93%E9%9B%84%EF%BC%88%E4%BD%9C%E5%93%81%EF%BC%89%EF%BC%8F%E6%BC%94%E5%A5%8F%EF%BC%9A%E5%AE%AE%E5%9F%8E%E5%96%9C%E4%BB%A3%E5%AD%90%E3%83%BB%E5%AE%AE%E5%9F%8E%E6%95%B0%E6%B1%9F%E3%83%BB%E4%BC%8A%E8%97%A4%E4%BA%AC%E5%AD%90%20%E4%BB%96%20SJL-2080%20%E7%AE%8F%20%E5%90%8D%E6%9B%B2%E3%81%AE%E8%AA%BF%E3%81%B9%E3%80%883%E3%80%89%EF%BC%8F%E5%AE%AE%E5%9F%8E%E9%81%93%E9%9B%84%E4%BD%9C%E5%93%81%E9%9B%86</x:v>
       </x:c>
-      <x:c r="Q14" s="12" t="str"/>
+      <x:c r="Q14" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3236.jpg</x:v>
+      </x:c>
       <x:c r="R14" s="12" t="str">
-        <x:v>pending</x:v>
+        <x:v>reference_photo</x:v>
       </x:c>
       <x:c r="S14" s="12" t="str">
         <x:v>Photo audit 2026-09-17: IMG_3236.jpg, top left. Artist, title and visible catalogue identifier checked against the original photograph.
-Earlier imported notes (retained as history; may contain superseded readings): Jacket clearly prints SJL-2080 (not SJ-3008-3). Performers on jacket: 宮城喜代子(箏), 宮城数江(唄・箏), 伊藤京子(唄)他. 'KOTO music' branding. Pieces listed on front.</x:v>
+Earlier imported notes (retained as history; may contain superseded readings): Jacket clearly prints SJL-2080 (not SJ-3008-3). Performers on jacket: 宮城喜代子(箏), 宮城数江(唄・箏), 伊藤京子(唄)他. 'KOTO music' branding. Pieces listed on front.
+2026-09-17 artwork update: user authorised a straightened crop of the original reference photo while a clean online match remains unavailable.</x:v>
       </x:c>
       <x:c r="T14" s="12" t="str">
         <x:v>Not visible in supplied photo</x:v>
@@ -1581,8 +1829,23 @@
       <x:c r="AD14" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="90" customHeight="1">
+      <x:c r="AE14" s="12" t="str">
+        <x:v>Volume three of a koto collection devoted to compositions by Michio Miyagi. The sleeve credits performers including Kiyoko Miyagi and Kazue Miyagi, and lists “Haru no Umi” among the works.</x:v>
+      </x:c>
+      <x:c r="AF14" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3236.jpg</x:v>
+      </x:c>
+      <x:c r="AG14" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH14" s="12" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Michio_Miyagi</x:v>
+      </x:c>
+      <x:c r="AI14" s="12" t="str">
+        <x:v>Wikipedia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="120" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>14</x:v>
       </x:c>
@@ -1656,8 +1919,23 @@
       <x:c r="AD15" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="90" customHeight="1">
+      <x:c r="AE15" s="12" t="str">
+        <x:v>A selection of twelve songs, including “Jūsan’ya”, “Atooi Shamisen”, “Gion Kouta” and “Tenryū Kudareba”. The programme draws on Japanese traditional and popular-song repertoire.</x:v>
+      </x:c>
+      <x:c r="AF15" s="12" t="str">
+        <x:v>https://www.discogs.com/release/10151877</x:v>
+      </x:c>
+      <x:c r="AG15" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH15" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/7511264</x:v>
+      </x:c>
+      <x:c r="AI15" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="120" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>15</x:v>
       </x:c>
@@ -1729,8 +2007,23 @@
       <x:c r="AD16" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="90" customHeight="1">
+      <x:c r="AE16" s="12" t="str">
+        <x:v>Released on 5 March 1971, this is the third album in Sony’s official Red Birds discography. It sits between Red Birds and Takeda no Komoriuta in the group’s early recording history.</x:v>
+      </x:c>
+      <x:c r="AF16" s="12" t="str">
+        <x:v>https://www.sonymusic.co.jp/Music/Info/junkoyamamoto/akaitoridisc.html</x:v>
+      </x:c>
+      <x:c r="AG16" s="12" t="str">
+        <x:v>Sony Music discography</x:v>
+      </x:c>
+      <x:c r="AH16" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/2812156</x:v>
+      </x:c>
+      <x:c r="AI16" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="120" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>16</x:v>
       </x:c>
@@ -1805,8 +2098,23 @@
       <x:c r="AD17" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="90" customHeight="1">
+      <x:c r="AE17" s="12" t="str">
+        <x:v>Originally released on 10 April 1978, this nine-track album opens with the spoken “Genki Desu ka” and includes “Wakareuta”, “Keshō” and “Sejō”. This collection holds the C28A0146 reissue; its pressing date is still unconfirmed.</x:v>
+      </x:c>
+      <x:c r="AF17" s="12" t="str">
+        <x:v>https://www.yamahamusic.co.jp/s/ymc/discography/266?ima=0000&amp;link=ROBO004</x:v>
+      </x:c>
+      <x:c r="AG17" s="12" t="str">
+        <x:v>Yamaha Music album notes</x:v>
+      </x:c>
+      <x:c r="AH17" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/1082785</x:v>
+      </x:c>
+      <x:c r="AI17" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="120" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>17</x:v>
       </x:c>
@@ -1882,8 +2190,23 @@
       <x:c r="AD18" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" ht="90" customHeight="1">
+      <x:c r="AE18" s="12" t="str">
+        <x:v>Iruka’s JULIA is represented here by the PANAM GWP-1019 LP. The artist’s official discography documents the album alongside her wider recording catalogue.</x:v>
+      </x:c>
+      <x:c r="AF18" s="12" t="str">
+        <x:v>https://www.crownrecord.co.jp/s/c01/artist/iruka/discography</x:v>
+      </x:c>
+      <x:c r="AG18" s="12" t="str">
+        <x:v>Nippon Crown discography</x:v>
+      </x:c>
+      <x:c r="AH18" s="12" t="str">
+        <x:v>https://www.crownrecord.co.jp/s/c01/artist/iruka/discography</x:v>
+      </x:c>
+      <x:c r="AI18" s="12" t="str">
+        <x:v>Official artist page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="120" customHeight="1">
       <x:c r="A19" s="6" t="str">
         <x:v>18</x:v>
       </x:c>
@@ -1957,8 +2280,23 @@
       <x:c r="AD19" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" ht="90" customHeight="1">
+      <x:c r="AE19" s="12" t="str">
+        <x:v>A twelve-song folk album by Wish, ending with “Rokugatsu no Komoriuta”. Other selections include “Kazaguruma”, “Tegami” and “Shihatsu Ressha de”.</x:v>
+      </x:c>
+      <x:c r="AF19" s="12" t="str">
+        <x:v>https://www.discogs.com/release/15856177</x:v>
+      </x:c>
+      <x:c r="AG19" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH19" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/6163738</x:v>
+      </x:c>
+      <x:c r="AI19" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="120" customHeight="1">
       <x:c r="A20" s="6" t="str">
         <x:v>19</x:v>
       </x:c>
@@ -2032,8 +2370,23 @@
       <x:c r="AD20" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" ht="90" customHeight="1">
+      <x:c r="AE20" s="12" t="str">
+        <x:v>A ten-song album from 1983, closing with its title song, “Umi no Mieru Heya”. The programme also includes “Watashi wa Ima”, “Shabon-dama” and “Room Mirror”.</x:v>
+      </x:c>
+      <x:c r="AF20" s="12" t="str">
+        <x:v>https://www.discogs.com/release/16035381</x:v>
+      </x:c>
+      <x:c r="AG20" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH20" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/7500205</x:v>
+      </x:c>
+      <x:c r="AI20" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="120" customHeight="1">
       <x:c r="A21" s="6" t="str">
         <x:v>20</x:v>
       </x:c>
@@ -2107,8 +2460,23 @@
       <x:c r="AD21" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22" ht="90" customHeight="1">
+      <x:c r="AE21" s="12" t="str">
+        <x:v>The Columbia sleeve identifies this as Chiyoko Shimakura’s Aishōshū, a collection of favourite songs. The visible catalogue number is ALS-5027; the release year still needs confirmation.</x:v>
+      </x:c>
+      <x:c r="AF21" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3237.jpg</x:v>
+      </x:c>
+      <x:c r="AG21" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH21" s="12" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Chiyoko_Shimakura</x:v>
+      </x:c>
+      <x:c r="AI21" s="12" t="str">
+        <x:v>Wikipedia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="120" customHeight="1">
       <x:c r="A22" s="6" t="str">
         <x:v>21</x:v>
       </x:c>
@@ -2182,8 +2550,23 @@
       <x:c r="AD22" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" ht="90" customHeight="1">
+      <x:c r="AE22" s="12" t="str">
+        <x:v>A vocal jazz set mixing standards and contemporary songs, from “How About You?” and “These Foolish Things” to Stevie Wonder’s “Too Shy to Say”. Released by Philips in 1980.</x:v>
+      </x:c>
+      <x:c r="AF22" s="12" t="str">
+        <x:v>https://www.discogs.com/release/4576441</x:v>
+      </x:c>
+      <x:c r="AG22" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH22" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/2762163</x:v>
+      </x:c>
+      <x:c r="AI22" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="120" customHeight="1">
       <x:c r="A23" s="6" t="str">
         <x:v>22</x:v>
       </x:c>
@@ -2257,8 +2640,23 @@
       <x:c r="AD23" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" ht="90" customHeight="1">
+      <x:c r="AE23" s="12" t="str">
+        <x:v>This two-record collection gathers twenty-four songs, including “Jūshichi no Natsu”, “Hajimete no Dekigoto” and “Watashi no Aoi Tori”. It is Junko Sakurada’s edition of Victor’s Best Collection ’76 series.</x:v>
+      </x:c>
+      <x:c r="AF23" s="12" t="str">
+        <x:v>https://www.discogs.com/release/7643818</x:v>
+      </x:c>
+      <x:c r="AG23" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH23" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/3390757</x:v>
+      </x:c>
+      <x:c r="AI23" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="120" customHeight="1">
       <x:c r="A24" s="6" t="str">
         <x:v>23</x:v>
       </x:c>
@@ -2336,8 +2734,23 @@
       <x:c r="AD24" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" ht="90" customHeight="1">
+      <x:c r="AE24" s="12" t="str">
+        <x:v>A two-record Ayumi Ishida collection in Columbia’s Green &amp; Glorious 3000 series. The obi advertises songs including “Blue Light Yokohama” and “Taiyō wa Naiteiru”.</x:v>
+      </x:c>
+      <x:c r="AF24" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3238.jpg</x:v>
+      </x:c>
+      <x:c r="AG24" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH24" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/311861</x:v>
+      </x:c>
+      <x:c r="AI24" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="120" customHeight="1">
       <x:c r="A25" s="6" t="str">
         <x:v>24</x:v>
       </x:c>
@@ -2374,17 +2787,22 @@
       <x:c r="N25" s="6" t="str">
         <x:v>IMG_3238.jpg — bottom right</x:v>
       </x:c>
-      <x:c r="O25" s="6" t="str"/>
+      <x:c r="O25" s="6" t="str">
+        <x:v>24_reference_crop.jpg</x:v>
+      </x:c>
       <x:c r="P25" s="6" t="str">
         <x:v>https://www.discogs.com/search/?q=%E9%83%BD%E3%81%AF%E3%82%8B%E3%81%BF%20%20%E3%83%99%E3%82%B9%E3%83%88%E3%82%A2%E3%83%AB%E3%83%90%E3%83%A0</x:v>
       </x:c>
-      <x:c r="Q25" s="12" t="str"/>
+      <x:c r="Q25" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3238.jpg</x:v>
+      </x:c>
       <x:c r="R25" s="12" t="str">
-        <x:v>pending</x:v>
+        <x:v>reference_photo</x:v>
       </x:c>
       <x:c r="S25" s="12" t="str">
         <x:v>Photo audit 2026-09-17: IMG_3238.jpg, bottom right. Cream kimono, peach background and blue sakura border. Separate from #07.
-Earlier imported notes (retained as history; may contain superseded readings): DISTINCT from #07 and #08. Cream/off-white kimono, peach background, navy blue sakura border, vertical red title panel. Catalog number not visible on front crop. Tracklist unverified for this specific jacket — incomplete.</x:v>
+Earlier imported notes (retained as history; may contain superseded readings): DISTINCT from #07 and #08. Cream/off-white kimono, peach background, navy blue sakura border, vertical red title panel. Catalog number not visible on front crop. Tracklist unverified for this specific jacket — incomplete.
+2026-09-17 artwork update: user authorised a straightened crop of the original reference photo while a clean online match remains unavailable.</x:v>
       </x:c>
       <x:c r="T25" s="12" t="str">
         <x:v>Not visible in supplied photo</x:v>
@@ -2405,8 +2823,23 @@
       <x:c r="AD25" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" ht="90" customHeight="1">
+      <x:c r="AE25" s="12" t="str">
+        <x:v>A Harumi Miyako compilation titled Best Album, identifiable here by its blue blossom border. Its precise catalogue number and programme still need checking, so it is kept separate from the AX-7293 compilation.</x:v>
+      </x:c>
+      <x:c r="AF25" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3238.jpg</x:v>
+      </x:c>
+      <x:c r="AG25" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH25" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/495700</x:v>
+      </x:c>
+      <x:c r="AI25" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="120" customHeight="1">
       <x:c r="A26" s="6" t="str">
         <x:v>25</x:v>
       </x:c>
@@ -2480,8 +2913,23 @@
       <x:c r="AD26" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" ht="90" customHeight="1">
+      <x:c r="AE26" s="12" t="str">
+        <x:v>A twenty-four-song, two-record anthology including “Coffee Rumba”, “Tokyo Blues” and “Akashia no Ame ga Yamu Toki”. The title translates approximately as Love, Affection, and Tears.</x:v>
+      </x:c>
+      <x:c r="AF26" s="12" t="str">
+        <x:v>https://www.discogs.com/release/11645824</x:v>
+      </x:c>
+      <x:c r="AG26" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH26" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/1088200</x:v>
+      </x:c>
+      <x:c r="AI26" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="120" customHeight="1">
       <x:c r="A27" s="6" t="str">
         <x:v>26</x:v>
       </x:c>
@@ -2555,8 +3003,23 @@
       <x:c r="AD27" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" ht="90" customHeight="1">
+      <x:c r="AE27" s="12" t="str">
+        <x:v>A lullaby programme combining Japanese songs with international selections such as “Hushabye Mountain”, “Summertime” and “Hush Little Baby”. Released on Philips in 1968.</x:v>
+      </x:c>
+      <x:c r="AF27" s="12" t="str">
+        <x:v>https://www.discogs.com/release/14059461</x:v>
+      </x:c>
+      <x:c r="AG27" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH27" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/440134</x:v>
+      </x:c>
+      <x:c r="AI27" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="120" customHeight="1">
       <x:c r="A28" s="6" t="str">
         <x:v>27</x:v>
       </x:c>
@@ -2630,8 +3093,23 @@
       <x:c r="AD28" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" ht="90" customHeight="1">
+      <x:c r="AE28" s="12" t="str">
+        <x:v>Yamagata’s debut album, originally released on 25 March 1973 when she was sixteen. Its folk repertoire includes “Kaze ni Fukarete Ikō”, “Akai Hana Shiroi Hana” and “Mayonaka no Guitar”.</x:v>
+      </x:c>
+      <x:c r="AF28" s="12" t="str">
+        <x:v>https://columbia.jp/artist-info/yamagatasumiko/discography/COCP-39360.html</x:v>
+      </x:c>
+      <x:c r="AG28" s="12" t="str">
+        <x:v>Columbia album notes</x:v>
+      </x:c>
+      <x:c r="AH28" s="12" t="str">
+        <x:v>https://columbia.jp/j-digs/artists/sumikoyamagata.html</x:v>
+      </x:c>
+      <x:c r="AI28" s="12" t="str">
+        <x:v>Columbia artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="120" customHeight="1">
       <x:c r="A29" s="6" t="str">
         <x:v>28</x:v>
       </x:c>
@@ -2705,8 +3183,23 @@
       <x:c r="AD29" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="30" ht="90" customHeight="1">
+      <x:c r="AE29" s="12" t="str">
+        <x:v>Recorded at Tokyo’s Sankei Hall on 27 October 1969, this recital pairs Ishida’s songs with film themes and international favourites. Selections include “Blue Light Yokohama”, “Scarborough Fair” and “The Shadow of Your Smile”.</x:v>
+      </x:c>
+      <x:c r="AF29" s="12" t="str">
+        <x:v>https://www.discogs.com/release/5305338</x:v>
+      </x:c>
+      <x:c r="AG29" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH29" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/311861</x:v>
+      </x:c>
+      <x:c r="AI29" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="120" customHeight="1">
       <x:c r="A30" s="6" t="str">
         <x:v>29</x:v>
       </x:c>
@@ -2782,8 +3275,23 @@
       <x:c r="AD30" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="31" ht="90" customHeight="1">
+      <x:c r="AE30" s="12" t="str">
+        <x:v>Nishida interprets twelve Japanese lyrical songs, including “Hamabe no Uta”, “Kōjō no Tsuki”, “Hana” and the title piece. The collection was issued by Polydor in 1970.</x:v>
+      </x:c>
+      <x:c r="AF30" s="12" t="str">
+        <x:v>https://www.discogs.com/release/35741143</x:v>
+      </x:c>
+      <x:c r="AG30" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH30" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/1088200</x:v>
+      </x:c>
+      <x:c r="AI30" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="120" customHeight="1">
       <x:c r="A31" s="6" t="str">
         <x:v>30</x:v>
       </x:c>
@@ -2857,8 +3365,23 @@
       <x:c r="AD31" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="32" ht="90" customHeight="1">
+      <x:c r="AE31" s="12" t="str">
+        <x:v>An enka album led by “Omoide-zake”, alongside interpretations of “Tsugaru Kaikyō Fuyugeshiki”, “Kita no Yado kara” and “Kitaguni no Haru”. Released in 1979.</x:v>
+      </x:c>
+      <x:c r="AF31" s="12" t="str">
+        <x:v>https://www.discogs.com/release/9432885</x:v>
+      </x:c>
+      <x:c r="AG31" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH31" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/5666652</x:v>
+      </x:c>
+      <x:c r="AI31" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="120" customHeight="1">
       <x:c r="A32" s="6" t="str">
         <x:v>31</x:v>
       </x:c>
@@ -2932,8 +3455,23 @@
       <x:c r="AD32" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="33" ht="90" customHeight="1">
+      <x:c r="AE32" s="12" t="str">
+        <x:v>The second volume of Uta wa Waga Inochi, presented in a blue Columbia sleeve. The photographed copy identifies Hibari Misora and catalogue ALS-5059; the sleeve is retained as the primary identification source.</x:v>
+      </x:c>
+      <x:c r="AF32" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3233.jpg</x:v>
+      </x:c>
+      <x:c r="AG32" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH32" s="12" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Hibari_Misora</x:v>
+      </x:c>
+      <x:c r="AI32" s="12" t="str">
+        <x:v>Wikipedia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="120" customHeight="1">
       <x:c r="A33" s="6" t="str">
         <x:v>32</x:v>
       </x:c>
@@ -3007,8 +3545,23 @@
       <x:c r="AD33" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="34" ht="90" customHeight="1">
+      <x:c r="AE33" s="12" t="str">
+        <x:v>A Victor album bearing the title “Anata ni Ageru”. The photographed sleeve confirms Mineko Nishikawa and catalogue SJX-198, with a close-up portrait and pink title panel.</x:v>
+      </x:c>
+      <x:c r="AF33" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3233.jpg</x:v>
+      </x:c>
+      <x:c r="AG33" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH33" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/3756573</x:v>
+      </x:c>
+      <x:c r="AI33" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="120" customHeight="1">
       <x:c r="A34" s="6" t="str">
         <x:v>33</x:v>
       </x:c>
@@ -3049,17 +3602,23 @@
       <x:c r="N34" s="6" t="str">
         <x:v>IMG_3233.jpg — bottom right</x:v>
       </x:c>
-      <x:c r="O34" s="6" t="str"/>
+      <x:c r="O34" s="6" t="str">
+        <x:v>33_official_front.jpg</x:v>
+      </x:c>
       <x:c r="P34" s="6" t="str">
         <x:v>https://www.discogs.com/search/?q=%E9%83%BD%E3%81%AF%E3%82%8B%E3%81%BF%20AX-7226%20%E5%A4%A7%E9%98%AA%E3%81%97%E3%81%90%E3%82%8C</x:v>
       </x:c>
-      <x:c r="Q34" s="12" t="str"/>
+      <x:c r="Q34" s="12" t="str">
+        <x:v>https://columbia.jp/artist-info/harumi/discography/COKM-46459.html</x:v>
+      </x:c>
       <x:c r="R34" s="12" t="str">
-        <x:v>pending</x:v>
+        <x:v>official</x:v>
       </x:c>
       <x:c r="S34" s="12" t="str">
         <x:v>Photo audit 2026-09-17: IMG_3233.jpg, bottom right. AX-7226 is printed at the top right; the prior AK-7168 reading was incorrect.
-Earlier imported notes (retained as history; may contain superseded readings): Green vertical banner lists tracks matching Columbia album AX-7226 (1980-02-25). Photo tentatively read AK-7168 (AK-216 is the single). Prefer official AX-7226; verify spine/label. 12 tracks.</x:v>
+Earlier imported notes (retained as history; may contain superseded readings): Green vertical banner lists tracks matching Columbia album AX-7226 (1980-02-25). Photo tentatively read AK-7168 (AK-216 is the single). Prefer official AX-7226; verify spine/label. 12 tracks.
+2026-09-17 artwork update: user authorised a straightened crop of the original reference photo while a clean online match remains unavailable.
+Clean matching front cover sourced from Columbia: https://columbia.jp/artist-info/jacket/COKM-46459.jpg. Original LP date 1980-02-25; the 2026 date on the page is the digital reissue.</x:v>
       </x:c>
       <x:c r="T34" s="12" t="str">
         <x:v>Present (visible in photo)</x:v>
@@ -3078,8 +3637,23 @@
       <x:c r="AD34" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="35" ht="90" customHeight="1">
+      <x:c r="AE34" s="12" t="str">
+        <x:v>Originally issued on 25 February 1980, this twelve-song album opens with “Osaka Shigure” and includes “Sayonara Kaikyō” and “Harumi”. Columbia’s official reissue page confirms the original AX-7226 catalogue number.</x:v>
+      </x:c>
+      <x:c r="AF34" s="12" t="str">
+        <x:v>https://columbia.jp/artist-info/harumi/discography/COKM-46459.html</x:v>
+      </x:c>
+      <x:c r="AG34" s="12" t="str">
+        <x:v>Columbia album notes</x:v>
+      </x:c>
+      <x:c r="AH34" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/495700</x:v>
+      </x:c>
+      <x:c r="AI34" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="120" customHeight="1">
       <x:c r="A35" s="6" t="str">
         <x:v>34</x:v>
       </x:c>
@@ -3118,17 +3692,22 @@
       <x:c r="N35" s="6" t="str">
         <x:v>IMG_3234.jpg — top left</x:v>
       </x:c>
-      <x:c r="O35" s="6" t="str"/>
+      <x:c r="O35" s="6" t="str">
+        <x:v>34_reference_crop.jpg</x:v>
+      </x:c>
       <x:c r="P35" s="6" t="str">
         <x:v>https://www.discogs.com/search/?q=%E8%A5%BF%E5%B7%9D%E5%B3%B0%E5%AD%90%20SJV-836~7%20%E3%83%99%E3%82%B9%E3%83%88%E3%83%BB%E3%82%B3%E3%83%AC%E3%82%AF%E3%82%B7%E3%83%A7%E3%83%B3%20%2776</x:v>
       </x:c>
-      <x:c r="Q35" s="12" t="str"/>
+      <x:c r="Q35" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3234.jpg</x:v>
+      </x:c>
       <x:c r="R35" s="12" t="str">
-        <x:v>pending</x:v>
+        <x:v>reference_photo</x:v>
       </x:c>
       <x:c r="S35" s="12" t="str">
         <x:v>Photo audit 2026-09-17: IMG_3234.jpg, top left. Victor two-record set. Catalogue SJV-836~7 is visible on the sleeve.
-Earlier imported notes (retained as history; may contain superseded readings): Victor SJV-836~7 confirmed. Distinct from #22 Sakurada SJV-832~3. Parent SXV-8002 incorrect.</x:v>
+Earlier imported notes (retained as history; may contain superseded readings): Victor SJV-836~7 confirmed. Distinct from #22 Sakurada SJV-832~3. Parent SXV-8002 incorrect.
+2026-09-17 artwork update: user authorised a straightened crop of the original reference photo while a clean online match remains unavailable.</x:v>
       </x:c>
       <x:c r="T35" s="12" t="str">
         <x:v>Not visible in supplied photo</x:v>
@@ -3149,8 +3728,23 @@
       <x:c r="AD35" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="36" ht="90" customHeight="1">
+      <x:c r="AE35" s="12" t="str">
+        <x:v>Mineko Nishikawa’s two-record contribution to Victor’s Best Collection ’76 series. Its SJV-836–7 catalogue number distinguishes it from Junko Sakurada’s similarly titled set.</x:v>
+      </x:c>
+      <x:c r="AF35" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3234.jpg</x:v>
+      </x:c>
+      <x:c r="AG35" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH35" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/3756573</x:v>
+      </x:c>
+      <x:c r="AI35" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="120" customHeight="1">
       <x:c r="A36" s="6" t="str">
         <x:v>35</x:v>
       </x:c>
@@ -3223,8 +3817,23 @@
       <x:c r="AD36" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="37" ht="90" customHeight="1">
+      <x:c r="AE36" s="12" t="str">
+        <x:v>A twelve-track collection led by “Kanashimi no Machi”, with “Onna no Melody” and “Ai no Kodoku”. This RCA issue uses the CD-4 four-channel format advertised as QuadraDisc on the sleeve.</x:v>
+      </x:c>
+      <x:c r="AF36" s="12" t="str">
+        <x:v>https://www.discogs.com/release/15416408</x:v>
+      </x:c>
+      <x:c r="AG36" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH36" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/1070643</x:v>
+      </x:c>
+      <x:c r="AI36" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="120" customHeight="1">
       <x:c r="A37" s="6" t="str">
         <x:v>36</x:v>
       </x:c>
@@ -3298,8 +3907,23 @@
       <x:c r="AD37" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="38" ht="90" customHeight="1">
+      <x:c r="AE37" s="12" t="str">
+        <x:v>A two-record Hibari Misora collection in the Golden Star Deluxe series. The photographed sleeve confirms AB-7001–2; the detailed programme is awaiting verification rather than borrowing another singer’s track list.</x:v>
+      </x:c>
+      <x:c r="AF37" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3234.jpg</x:v>
+      </x:c>
+      <x:c r="AG37" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH37" s="12" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Hibari_Misora</x:v>
+      </x:c>
+      <x:c r="AI37" s="12" t="str">
+        <x:v>Wikipedia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="120" customHeight="1">
       <x:c r="A38" s="6" t="str">
         <x:v>37</x:v>
       </x:c>
@@ -3336,15 +3960,20 @@
       <x:c r="N38" s="6" t="str">
         <x:v>IMG_3234.jpg — bottom right</x:v>
       </x:c>
-      <x:c r="O38" s="6" t="str"/>
+      <x:c r="O38" s="6" t="str">
+        <x:v>37_reference_crop.jpg</x:v>
+      </x:c>
       <x:c r="P38" s="6" t="str"/>
-      <x:c r="Q38" s="12" t="str"/>
+      <x:c r="Q38" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3234.jpg</x:v>
+      </x:c>
       <x:c r="R38" s="12" t="str">
-        <x:v>pending</x:v>
+        <x:v>reference_photo</x:v>
       </x:c>
       <x:c r="S38" s="12" t="str">
         <x:v>Photo audit 2026-09-17: IMG_3234.jpg, bottom right. Sony SQ four-channel sampler with black concentric-groove artwork. SPEC-94019 is a candidate, not a photo-confirmed identifier.
-Earlier imported notes (retained as history; may contain superseded readings): Black groove-art cover; bottom text 地球はひとつ SQ 4チャンネル; Sony + SX-1318 on jacket. SQ 4-channel demo/sampler known for including 原信夫とシャープス＆フラッツ「Bitter Sweet Samba」. Full side-assigned tracklist not verified without inventing — omit tracks.</x:v>
+Earlier imported notes (retained as history; may contain superseded readings): Black groove-art cover; bottom text 地球はひとつ SQ 4チャンネル; Sony + SX-1318 on jacket. SQ 4-channel demo/sampler known for including 原信夫とシャープス＆フラッツ「Bitter Sweet Samba」. Full side-assigned tracklist not verified without inventing — omit tracks.
+2026-09-17 artwork update: user authorised a straightened crop of the original reference photo while a clean online match remains unavailable.</x:v>
       </x:c>
       <x:c r="T38" s="12" t="str">
         <x:v>Not visible in supplied photo</x:v>
@@ -3365,8 +3994,19 @@
       <x:c r="AD38" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="39" ht="90" customHeight="1">
+      <x:c r="AE38" s="12" t="str">
+        <x:v>A Sony demonstration record promoting SQ four-channel sound, under the title Chikyū wa Hitotsu (“The Earth Is One”). The exact edition and performers are still being checked.</x:v>
+      </x:c>
+      <x:c r="AF38" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3234.jpg</x:v>
+      </x:c>
+      <x:c r="AG38" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH38" s="12" t="str"/>
+      <x:c r="AI38" s="12" t="str"/>
+    </x:row>
+    <x:row r="39" ht="120" customHeight="1">
       <x:c r="A39" s="6" t="str">
         <x:v>38</x:v>
       </x:c>
@@ -3440,8 +4080,23 @@
       <x:c r="AD39" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="40" ht="90" customHeight="1">
+      <x:c r="AE39" s="12" t="str">
+        <x:v>Sony’s official discography dates Studio Live to 20 December 1971, following Takeda no Komoriuta. It is an early Red Birds release, distinct from the later Million People concert album.</x:v>
+      </x:c>
+      <x:c r="AF39" s="12" t="str">
+        <x:v>https://www.sonymusic.co.jp/Music/Info/junkoyamamoto/akaitoridisc.html</x:v>
+      </x:c>
+      <x:c r="AG39" s="12" t="str">
+        <x:v>Sony Music discography</x:v>
+      </x:c>
+      <x:c r="AH39" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/2812156</x:v>
+      </x:c>
+      <x:c r="AI39" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="120" customHeight="1">
       <x:c r="A40" s="6" t="str">
         <x:v>39</x:v>
       </x:c>
@@ -3480,17 +4135,22 @@
       <x:c r="N40" s="6" t="str">
         <x:v>IMG_3235.jpg — top right</x:v>
       </x:c>
-      <x:c r="O40" s="6" t="str"/>
+      <x:c r="O40" s="6" t="str">
+        <x:v>39_reference_crop.jpg</x:v>
+      </x:c>
       <x:c r="P40" s="6" t="str">
         <x:v>https://www.discogs.com/search/?q=%E8%B5%A4%E3%81%84%E9%B3%A5%20ETP-60223~24%20%E3%82%B4%E3%83%BC%E3%83%AB%E3%83%87%E3%83%B3%E3%83%BB%E3%83%87%E3%82%A3%E3%82%B9%E3%82%AF</x:v>
       </x:c>
-      <x:c r="Q40" s="12" t="str"/>
+      <x:c r="Q40" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3235.jpg</x:v>
+      </x:c>
       <x:c r="R40" s="12" t="str">
-        <x:v>pending</x:v>
+        <x:v>reference_photo</x:v>
       </x:c>
       <x:c r="S40" s="12" t="str">
         <x:v>Photo audit 2026-09-17: IMG_3235.jpg, top right. Orange-bordered two-record set. The visible ¥380 sticker is a shop price, not a confirmed purchase price.
-Earlier imported notes (retained as history; may contain superseded readings): Jacket shows ETP-60223~24 (parent ETP-60222~23). Orange-border 2LP group photo.</x:v>
+Earlier imported notes (retained as history; may contain superseded readings): Jacket shows ETP-60223~24 (parent ETP-60222~23). Orange-border 2LP group photo.
+2026-09-17 artwork update: user authorised a straightened crop of the original reference photo while a clean online match remains unavailable.</x:v>
       </x:c>
       <x:c r="T40" s="12" t="str">
         <x:v>Not visible in supplied photo</x:v>
@@ -3511,8 +4171,23 @@
       <x:c r="AD40" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="41" ht="90" customHeight="1">
+      <x:c r="AE40" s="12" t="str">
+        <x:v>A two-record Red Birds compilation issued as Golden Disk. The orange-bordered sleeve identifies catalogue ETP-60223–24; its release year remains unconfirmed.</x:v>
+      </x:c>
+      <x:c r="AF40" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3235.jpg</x:v>
+      </x:c>
+      <x:c r="AG40" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH40" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/2812156</x:v>
+      </x:c>
+      <x:c r="AI40" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="120" customHeight="1">
       <x:c r="A41" s="6" t="str">
         <x:v>40</x:v>
       </x:c>
@@ -3549,15 +4224,20 @@
       <x:c r="N41" s="6" t="str">
         <x:v>IMG_3235.jpg — bottom left</x:v>
       </x:c>
-      <x:c r="O41" s="6" t="str"/>
+      <x:c r="O41" s="6" t="str">
+        <x:v>40_reference_crop.jpg</x:v>
+      </x:c>
       <x:c r="P41" s="6" t="str"/>
-      <x:c r="Q41" s="12" t="str"/>
+      <x:c r="Q41" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3235.jpg</x:v>
+      </x:c>
       <x:c r="R41" s="12" t="str">
-        <x:v>pending</x:v>
+        <x:v>reference_photo</x:v>
       </x:c>
       <x:c r="S41" s="12" t="str">
         <x:v>Photo audit 2026-09-17: IMG_3235.jpg, bottom left. The sleeve reads 笹川鎮江 愛吟集 第2集. Smaller-format sleeve with moon and blossoms.
-Earlier imported notes (retained as history; may contain superseded readings): Moon &amp; sakura 愛吟集 第2集. Discogs SJX-10115 is 浜口庫之助 雨のピエロ — catalog collision; do not use. Jacket catalog unconfirmed on crop.</x:v>
+Earlier imported notes (retained as history; may contain superseded readings): Moon &amp; sakura 愛吟集 第2集. Discogs SJX-10115 is 浜口庫之助 雨のピエロ — catalog collision; do not use. Jacket catalog unconfirmed on crop.
+2026-09-17 artwork update: user authorised a straightened crop of the original reference photo while a clean online match remains unavailable.</x:v>
       </x:c>
       <x:c r="T41" s="12" t="str">
         <x:v>Not visible in supplied photo</x:v>
@@ -3578,8 +4258,23 @@
       <x:c r="AD41" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="42" ht="90" customHeight="1">
+      <x:c r="AE41" s="12" t="str">
+        <x:v>The second volume of Shizue Sasagawa’s Aiginshū, a collection of gin’ei vocal performances. The moon-and-blossom sleeve supplies the artist and volume identification; a release date and full programme remain unverified.</x:v>
+      </x:c>
+      <x:c r="AF41" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3235.jpg</x:v>
+      </x:c>
+      <x:c r="AG41" s="12" t="str">
+        <x:v>Original sleeve (collection note)</x:v>
+      </x:c>
+      <x:c r="AH41" s="12" t="str">
+        <x:v>https://nippon.zaidan.info/seikabutsu/2005/00403/contents/0002.htm</x:v>
+      </x:c>
+      <x:c r="AI41" s="12" t="str">
+        <x:v>Nippon Foundation article</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="120" customHeight="1">
       <x:c r="A42" s="6" t="str">
         <x:v>41</x:v>
       </x:c>
@@ -3653,11 +4348,26 @@
       <x:c r="AD42" s="12" t="str">
         <x:v>2026-09-17</x:v>
       </x:c>
+      <x:c r="AE42" s="12" t="str">
+        <x:v>A nagauta performance of Shinkyoku Urashima, divided into two parts across the record’s sides. The Columbia release credits Ijūrō Yoshimura and shamisen player Eijirō Kineya.</x:v>
+      </x:c>
+      <x:c r="AF42" s="12" t="str">
+        <x:v>https://www.discogs.com/release/13923247</x:v>
+      </x:c>
+      <x:c r="AG42" s="12" t="str">
+        <x:v>Discogs release and track listing</x:v>
+      </x:c>
+      <x:c r="AH42" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/2475755</x:v>
+      </x:c>
+      <x:c r="AI42" s="12" t="str">
+        <x:v>Ijūrō Yoshimura on Discogs</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R269d14054404472f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23c16bbbadd34bfe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11837,7 +12547,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0bfe17871ca4933"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8567bfd133c54917"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/data/record_collection.xlsx
+++ b/data/record_collection.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Albums" sheetId="1" r:id="Rf8931e66d2164752"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracks" sheetId="2" r:id="Rfe5492459f274665"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research_26_41" sheetId="3" r:id="R3224f335299f4653"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Albums" sheetId="1" r:id="R38957d92404a458b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracks" sheetId="2" r:id="R51338342e62445d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research_26_41" sheetId="3" r:id="R84901db09f274abc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -246,7 +246,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="AlbumsTable" displayName="AlbumsTable" ref="A1:AI42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="AlbumsTable" displayName="AlbumsTable" ref="A1:AI143" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="35">
     <x:tableColumn id="1" name="Collection ID"/>
     <x:tableColumn id="2" name="Artist (Japanese)"/>
@@ -4364,10 +4364,7629 @@
         <x:v>Ijūrō Yoshimura on Discogs</x:v>
       </x:c>
     </x:row>
+    <x:row r="43" ht="120" customHeight="1">
+      <x:c r="A43" s="12" t="str">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" s="12" t="str">
+        <x:v>堀江美都子</x:v>
+      </x:c>
+      <x:c r="C43" s="12" t="str">
+        <x:v>Mitsuko Horie</x:v>
+      </x:c>
+      <x:c r="D43" s="12" t="str">
+        <x:v>テレビ主題歌ヒット・アルバム 堀江美都子とともに</x:v>
+      </x:c>
+      <x:c r="E43" s="12" t="str">
+        <x:v>TV Theme Song Hit Album</x:v>
+      </x:c>
+      <x:c r="F43" s="12" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="G43" s="12" t="str"/>
+      <x:c r="H43" s="12" t="str"/>
+      <x:c r="I43" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J43" s="12" t="str"/>
+      <x:c r="K43" s="12" t="str"/>
+      <x:c r="L43" s="12" t="str"/>
+      <x:c r="M43" s="12" t="str"/>
+      <x:c r="N43" s="12" t="str">
+        <x:v>IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="O43" s="12" t="str">
+        <x:v>42_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P43" s="12" t="str"/>
+      <x:c r="Q43" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="R43" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S43" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3241.jpg. </x:v>
+      </x:c>
+      <x:c r="T43" s="12" t="str"/>
+      <x:c r="U43" s="12" t="str"/>
+      <x:c r="V43" s="12" t="str"/>
+      <x:c r="W43" s="12" t="str"/>
+      <x:c r="X43" s="12" t="str"/>
+      <x:c r="Y43" s="12" t="str"/>
+      <x:c r="Z43" s="12" t="str"/>
+      <x:c r="AA43" s="12" t="str"/>
+      <x:c r="AB43" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC43" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD43" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE43" s="12" t="str">
+        <x:v>Collection note: TV Theme Song Hit Album by Mitsuko Horie, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF43" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="AG43" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH43" s="12" t="str"/>
+      <x:c r="AI43" s="12" t="str"/>
+    </x:row>
+    <x:row r="44" ht="120" customHeight="1">
+      <x:c r="A44" s="12" t="str">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" s="12" t="str"/>
+      <x:c r="C44" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D44" s="12" t="str">
+        <x:v>ピンポンパン体操</x:v>
+      </x:c>
+      <x:c r="E44" s="12" t="str">
+        <x:v>Pin Pon Pan Taiso</x:v>
+      </x:c>
+      <x:c r="F44" s="12" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="G44" s="12" t="str"/>
+      <x:c r="H44" s="12" t="str"/>
+      <x:c r="I44" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J44" s="12" t="str"/>
+      <x:c r="K44" s="12" t="str"/>
+      <x:c r="L44" s="12" t="str"/>
+      <x:c r="M44" s="12" t="str"/>
+      <x:c r="N44" s="12" t="str">
+        <x:v>IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="O44" s="12" t="str">
+        <x:v>43_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P44" s="12" t="str"/>
+      <x:c r="Q44" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="R44" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S44" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3241.jpg. </x:v>
+      </x:c>
+      <x:c r="T44" s="12" t="str"/>
+      <x:c r="U44" s="12" t="str"/>
+      <x:c r="V44" s="12" t="str"/>
+      <x:c r="W44" s="12" t="str"/>
+      <x:c r="X44" s="12" t="str"/>
+      <x:c r="Y44" s="12" t="str"/>
+      <x:c r="Z44" s="12" t="str"/>
+      <x:c r="AA44" s="12" t="str"/>
+      <x:c r="AB44" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC44" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD44" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE44" s="12" t="str">
+        <x:v>Collection note: Pin Pon Pan Taiso by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF44" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="AG44" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH44" s="12" t="str"/>
+      <x:c r="AI44" s="12" t="str"/>
+    </x:row>
+    <x:row r="45" ht="120" customHeight="1">
+      <x:c r="A45" s="12" t="str">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" s="12" t="str"/>
+      <x:c r="C45" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D45" s="12" t="str">
+        <x:v>ゴールデンテレビまんが大行進 1 巨人の星</x:v>
+      </x:c>
+      <x:c r="E45" s="12" t="str">
+        <x:v>Golden TV Manga Daikoshin 1: Kyojin no Hoshi</x:v>
+      </x:c>
+      <x:c r="F45" s="12" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="G45" s="12" t="str"/>
+      <x:c r="H45" s="12" t="str"/>
+      <x:c r="I45" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J45" s="12" t="str"/>
+      <x:c r="K45" s="12" t="str"/>
+      <x:c r="L45" s="12" t="str"/>
+      <x:c r="M45" s="12" t="str"/>
+      <x:c r="N45" s="12" t="str">
+        <x:v>IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="O45" s="12" t="str">
+        <x:v>44_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P45" s="12" t="str"/>
+      <x:c r="Q45" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="R45" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S45" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3241.jpg. </x:v>
+      </x:c>
+      <x:c r="T45" s="12" t="str"/>
+      <x:c r="U45" s="12" t="str"/>
+      <x:c r="V45" s="12" t="str"/>
+      <x:c r="W45" s="12" t="str"/>
+      <x:c r="X45" s="12" t="str"/>
+      <x:c r="Y45" s="12" t="str"/>
+      <x:c r="Z45" s="12" t="str"/>
+      <x:c r="AA45" s="12" t="str"/>
+      <x:c r="AB45" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC45" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD45" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE45" s="12" t="str">
+        <x:v>Collection note: Golden TV Manga Daikoshin 1: Kyojin no Hoshi by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF45" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="AG45" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH45" s="12" t="str"/>
+      <x:c r="AI45" s="12" t="str"/>
+    </x:row>
+    <x:row r="46" ht="120" customHeight="1">
+      <x:c r="A46" s="12" t="str">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" s="12" t="str"/>
+      <x:c r="C46" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D46" s="12" t="str">
+        <x:v>みんなで変身</x:v>
+      </x:c>
+      <x:c r="E46" s="12" t="str">
+        <x:v>Minna de Henshin</x:v>
+      </x:c>
+      <x:c r="F46" s="12" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="G46" s="12" t="str"/>
+      <x:c r="H46" s="12" t="str"/>
+      <x:c r="I46" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J46" s="12" t="str"/>
+      <x:c r="K46" s="12" t="str"/>
+      <x:c r="L46" s="12" t="str"/>
+      <x:c r="M46" s="12" t="str"/>
+      <x:c r="N46" s="12" t="str">
+        <x:v>IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="O46" s="12" t="str">
+        <x:v>45_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P46" s="12" t="str"/>
+      <x:c r="Q46" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="R46" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S46" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3241.jpg. </x:v>
+      </x:c>
+      <x:c r="T46" s="12" t="str"/>
+      <x:c r="U46" s="12" t="str"/>
+      <x:c r="V46" s="12" t="str"/>
+      <x:c r="W46" s="12" t="str"/>
+      <x:c r="X46" s="12" t="str"/>
+      <x:c r="Y46" s="12" t="str"/>
+      <x:c r="Z46" s="12" t="str"/>
+      <x:c r="AA46" s="12" t="str"/>
+      <x:c r="AB46" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC46" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD46" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE46" s="12" t="str">
+        <x:v>Collection note: Minna de Henshin by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF46" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="AG46" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH46" s="12" t="str"/>
+      <x:c r="AI46" s="12" t="str"/>
+    </x:row>
+    <x:row r="47" ht="120" customHeight="1">
+      <x:c r="A47" s="12" t="str">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B47" s="12" t="str"/>
+      <x:c r="C47" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D47" s="12" t="str">
+        <x:v>野球狂の詩 オリジナル・サウンドトラック</x:v>
+      </x:c>
+      <x:c r="E47" s="12" t="str">
+        <x:v>Yakyukyo no Uta: Original Soundtrack</x:v>
+      </x:c>
+      <x:c r="F47" s="12" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="G47" s="12" t="str"/>
+      <x:c r="H47" s="12" t="str"/>
+      <x:c r="I47" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J47" s="12" t="str"/>
+      <x:c r="K47" s="12" t="str"/>
+      <x:c r="L47" s="12" t="str"/>
+      <x:c r="M47" s="12" t="str"/>
+      <x:c r="N47" s="12" t="str">
+        <x:v>IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="O47" s="12" t="str">
+        <x:v>46_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P47" s="12" t="str"/>
+      <x:c r="Q47" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="R47" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S47" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3241.jpg. </x:v>
+      </x:c>
+      <x:c r="T47" s="12" t="str"/>
+      <x:c r="U47" s="12" t="str"/>
+      <x:c r="V47" s="12" t="str"/>
+      <x:c r="W47" s="12" t="str"/>
+      <x:c r="X47" s="12" t="str"/>
+      <x:c r="Y47" s="12" t="str"/>
+      <x:c r="Z47" s="12" t="str"/>
+      <x:c r="AA47" s="12" t="str"/>
+      <x:c r="AB47" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC47" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD47" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE47" s="12" t="str">
+        <x:v>Collection note: Yakyukyo no Uta: Original Soundtrack by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF47" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="AG47" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH47" s="12" t="str"/>
+      <x:c r="AI47" s="12" t="str"/>
+    </x:row>
+    <x:row r="48" ht="120" customHeight="1">
+      <x:c r="A48" s="12" t="str">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B48" s="12" t="str">
+        <x:v>堀江美都子</x:v>
+      </x:c>
+      <x:c r="C48" s="12" t="str">
+        <x:v>Mitsuko Horie</x:v>
+      </x:c>
+      <x:c r="D48" s="12" t="str">
+        <x:v>テレビアニメーションの世界</x:v>
+      </x:c>
+      <x:c r="E48" s="12" t="str">
+        <x:v>The World of TV Animation</x:v>
+      </x:c>
+      <x:c r="F48" s="12" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="G48" s="12" t="str"/>
+      <x:c r="H48" s="12" t="str"/>
+      <x:c r="I48" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J48" s="12" t="str"/>
+      <x:c r="K48" s="12" t="str"/>
+      <x:c r="L48" s="12" t="str"/>
+      <x:c r="M48" s="12" t="str"/>
+      <x:c r="N48" s="12" t="str">
+        <x:v>IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="O48" s="12" t="str">
+        <x:v>47_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P48" s="12" t="str"/>
+      <x:c r="Q48" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="R48" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S48" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3241.jpg. </x:v>
+      </x:c>
+      <x:c r="T48" s="12" t="str"/>
+      <x:c r="U48" s="12" t="str"/>
+      <x:c r="V48" s="12" t="str"/>
+      <x:c r="W48" s="12" t="str"/>
+      <x:c r="X48" s="12" t="str"/>
+      <x:c r="Y48" s="12" t="str"/>
+      <x:c r="Z48" s="12" t="str"/>
+      <x:c r="AA48" s="12" t="str"/>
+      <x:c r="AB48" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC48" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD48" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE48" s="12" t="str">
+        <x:v>Collection note: The World of TV Animation by Mitsuko Horie, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF48" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="AG48" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH48" s="12" t="str"/>
+      <x:c r="AI48" s="12" t="str"/>
+    </x:row>
+    <x:row r="49" ht="120" customHeight="1">
+      <x:c r="A49" s="12" t="str">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B49" s="12" t="str">
+        <x:v>堀江美都子</x:v>
+      </x:c>
+      <x:c r="C49" s="12" t="str">
+        <x:v>Mitsuko Horie</x:v>
+      </x:c>
+      <x:c r="D49" s="12" t="str">
+        <x:v>ミッチの部屋</x:v>
+      </x:c>
+      <x:c r="E49" s="12" t="str">
+        <x:v>Micchi no Heya</x:v>
+      </x:c>
+      <x:c r="F49" s="12" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="G49" s="12" t="str"/>
+      <x:c r="H49" s="12" t="str"/>
+      <x:c r="I49" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J49" s="12" t="str"/>
+      <x:c r="K49" s="12" t="str"/>
+      <x:c r="L49" s="12" t="str"/>
+      <x:c r="M49" s="12" t="str"/>
+      <x:c r="N49" s="12" t="str">
+        <x:v>IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="O49" s="12" t="str">
+        <x:v>48_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P49" s="12" t="str"/>
+      <x:c r="Q49" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="R49" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S49" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3241.jpg. </x:v>
+      </x:c>
+      <x:c r="T49" s="12" t="str"/>
+      <x:c r="U49" s="12" t="str"/>
+      <x:c r="V49" s="12" t="str"/>
+      <x:c r="W49" s="12" t="str"/>
+      <x:c r="X49" s="12" t="str"/>
+      <x:c r="Y49" s="12" t="str"/>
+      <x:c r="Z49" s="12" t="str"/>
+      <x:c r="AA49" s="12" t="str"/>
+      <x:c r="AB49" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC49" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD49" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE49" s="12" t="str">
+        <x:v>Collection note: Micchi no Heya by Mitsuko Horie, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF49" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="AG49" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH49" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E5%A0%80%E6%B1%9F%E7%BE%8E%E9%83%BD%E5%AD%90/208472504?uo=4</x:v>
+      </x:c>
+      <x:c r="AI49" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="120" customHeight="1">
+      <x:c r="A50" s="12" t="str">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B50" s="12" t="str">
+        <x:v>川井憲次</x:v>
+      </x:c>
+      <x:c r="C50" s="12" t="str">
+        <x:v>Kenji Kawai</x:v>
+      </x:c>
+      <x:c r="D50" s="12" t="str">
+        <x:v>攻殻機動隊</x:v>
+      </x:c>
+      <x:c r="E50" s="12" t="str">
+        <x:v>Ghost in the Shell: Original Soundtrack</x:v>
+      </x:c>
+      <x:c r="F50" s="12" t="str"/>
+      <x:c r="G50" s="12" t="str"/>
+      <x:c r="H50" s="12" t="str"/>
+      <x:c r="I50" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J50" s="12" t="str"/>
+      <x:c r="K50" s="12" t="str"/>
+      <x:c r="L50" s="12" t="str"/>
+      <x:c r="M50" s="12" t="str"/>
+      <x:c r="N50" s="12" t="str">
+        <x:v>IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="O50" s="12" t="str">
+        <x:v>49_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P50" s="12" t="str"/>
+      <x:c r="Q50" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="R50" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S50" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3241.jpg. </x:v>
+      </x:c>
+      <x:c r="T50" s="12" t="str"/>
+      <x:c r="U50" s="12" t="str"/>
+      <x:c r="V50" s="12" t="str"/>
+      <x:c r="W50" s="12" t="str"/>
+      <x:c r="X50" s="12" t="str"/>
+      <x:c r="Y50" s="12" t="str"/>
+      <x:c r="Z50" s="12" t="str"/>
+      <x:c r="AA50" s="12" t="str"/>
+      <x:c r="AB50" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC50" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD50" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE50" s="12" t="str">
+        <x:v>Collection note: Ghost in the Shell: Original Soundtrack by Kenji Kawai, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF50" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3241.jpg</x:v>
+      </x:c>
+      <x:c r="AG50" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH50" s="12" t="str"/>
+      <x:c r="AI50" s="12" t="str"/>
+    </x:row>
+    <x:row r="51" ht="120" customHeight="1">
+      <x:c r="A51" s="12" t="str">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B51" s="12" t="str"/>
+      <x:c r="C51" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D51" s="12" t="str">
+        <x:v>ジャパニーズ・グラフィティ大百科</x:v>
+      </x:c>
+      <x:c r="E51" s="12" t="str">
+        <x:v>Jukebox 1</x:v>
+      </x:c>
+      <x:c r="F51" s="12" t="str"/>
+      <x:c r="G51" s="12" t="str"/>
+      <x:c r="H51" s="12" t="str"/>
+      <x:c r="I51" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J51" s="12" t="str"/>
+      <x:c r="K51" s="12" t="str"/>
+      <x:c r="L51" s="12" t="str"/>
+      <x:c r="M51" s="12" t="str"/>
+      <x:c r="N51" s="12" t="str">
+        <x:v>IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="O51" s="12" t="str">
+        <x:v>50_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P51" s="12" t="str"/>
+      <x:c r="Q51" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="R51" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S51" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3242.jpg. </x:v>
+      </x:c>
+      <x:c r="T51" s="12" t="str"/>
+      <x:c r="U51" s="12" t="str"/>
+      <x:c r="V51" s="12" t="str"/>
+      <x:c r="W51" s="12" t="str"/>
+      <x:c r="X51" s="12" t="str"/>
+      <x:c r="Y51" s="12" t="str"/>
+      <x:c r="Z51" s="12" t="str"/>
+      <x:c r="AA51" s="12" t="str"/>
+      <x:c r="AB51" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC51" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD51" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE51" s="12" t="str">
+        <x:v>Collection note: Jukebox 1 by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF51" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="AG51" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH51" s="12" t="str"/>
+      <x:c r="AI51" s="12" t="str"/>
+    </x:row>
+    <x:row r="52" ht="120" customHeight="1">
+      <x:c r="A52" s="12" t="str">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B52" s="12" t="str"/>
+      <x:c r="C52" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D52" s="12" t="str">
+        <x:v>歌謡曲大百科</x:v>
+      </x:c>
+      <x:c r="E52" s="12" t="str">
+        <x:v>Jukebox 2</x:v>
+      </x:c>
+      <x:c r="F52" s="12" t="str"/>
+      <x:c r="G52" s="12" t="str"/>
+      <x:c r="H52" s="12" t="str"/>
+      <x:c r="I52" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J52" s="12" t="str"/>
+      <x:c r="K52" s="12" t="str"/>
+      <x:c r="L52" s="12" t="str"/>
+      <x:c r="M52" s="12" t="str"/>
+      <x:c r="N52" s="12" t="str">
+        <x:v>IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="O52" s="12" t="str">
+        <x:v>51_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P52" s="12" t="str"/>
+      <x:c r="Q52" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="R52" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S52" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3242.jpg. </x:v>
+      </x:c>
+      <x:c r="T52" s="12" t="str"/>
+      <x:c r="U52" s="12" t="str"/>
+      <x:c r="V52" s="12" t="str"/>
+      <x:c r="W52" s="12" t="str"/>
+      <x:c r="X52" s="12" t="str"/>
+      <x:c r="Y52" s="12" t="str"/>
+      <x:c r="Z52" s="12" t="str"/>
+      <x:c r="AA52" s="12" t="str"/>
+      <x:c r="AB52" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC52" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD52" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE52" s="12" t="str">
+        <x:v>Collection note: Jukebox 2 by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF52" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="AG52" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH52" s="12" t="str"/>
+      <x:c r="AI52" s="12" t="str"/>
+    </x:row>
+    <x:row r="53" ht="120" customHeight="1">
+      <x:c r="A53" s="12" t="str">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B53" s="12" t="str"/>
+      <x:c r="C53" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D53" s="12" t="str">
+        <x:v>越路・ペギー・由紀・デューク</x:v>
+      </x:c>
+      <x:c r="E53" s="12" t="str">
+        <x:v>Jukebox 5</x:v>
+      </x:c>
+      <x:c r="F53" s="12" t="str"/>
+      <x:c r="G53" s="12" t="str"/>
+      <x:c r="H53" s="12" t="str"/>
+      <x:c r="I53" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J53" s="12" t="str"/>
+      <x:c r="K53" s="12" t="str"/>
+      <x:c r="L53" s="12" t="str"/>
+      <x:c r="M53" s="12" t="str"/>
+      <x:c r="N53" s="12" t="str">
+        <x:v>IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="O53" s="12" t="str">
+        <x:v>52_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P53" s="12" t="str"/>
+      <x:c r="Q53" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="R53" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S53" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3242.jpg. </x:v>
+      </x:c>
+      <x:c r="T53" s="12" t="str"/>
+      <x:c r="U53" s="12" t="str"/>
+      <x:c r="V53" s="12" t="str"/>
+      <x:c r="W53" s="12" t="str"/>
+      <x:c r="X53" s="12" t="str"/>
+      <x:c r="Y53" s="12" t="str"/>
+      <x:c r="Z53" s="12" t="str"/>
+      <x:c r="AA53" s="12" t="str"/>
+      <x:c r="AB53" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC53" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD53" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE53" s="12" t="str">
+        <x:v>Collection note: Jukebox 5 by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF53" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="AG53" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH53" s="12" t="str"/>
+      <x:c r="AI53" s="12" t="str"/>
+    </x:row>
+    <x:row r="54" ht="120" customHeight="1">
+      <x:c r="A54" s="12" t="str">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B54" s="12" t="str"/>
+      <x:c r="C54" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D54" s="12" t="str"/>
+      <x:c r="E54" s="12" t="str">
+        <x:v>Jukebox 6</x:v>
+      </x:c>
+      <x:c r="F54" s="12" t="str"/>
+      <x:c r="G54" s="12" t="str"/>
+      <x:c r="H54" s="12" t="str"/>
+      <x:c r="I54" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J54" s="12" t="str"/>
+      <x:c r="K54" s="12" t="str"/>
+      <x:c r="L54" s="12" t="str"/>
+      <x:c r="M54" s="12" t="str"/>
+      <x:c r="N54" s="12" t="str">
+        <x:v>IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="O54" s="12" t="str">
+        <x:v>53_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P54" s="12" t="str"/>
+      <x:c r="Q54" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="R54" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S54" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3242.jpg. </x:v>
+      </x:c>
+      <x:c r="T54" s="12" t="str"/>
+      <x:c r="U54" s="12" t="str"/>
+      <x:c r="V54" s="12" t="str"/>
+      <x:c r="W54" s="12" t="str"/>
+      <x:c r="X54" s="12" t="str"/>
+      <x:c r="Y54" s="12" t="str"/>
+      <x:c r="Z54" s="12" t="str"/>
+      <x:c r="AA54" s="12" t="str"/>
+      <x:c r="AB54" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC54" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD54" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE54" s="12" t="str">
+        <x:v>Collection note: Jukebox 6 by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF54" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="AG54" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH54" s="12" t="str"/>
+      <x:c r="AI54" s="12" t="str"/>
+    </x:row>
+    <x:row r="55" ht="120" customHeight="1">
+      <x:c r="A55" s="12" t="str">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B55" s="12" t="str"/>
+      <x:c r="C55" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D55" s="12" t="str">
+        <x:v>青春ポップス大百科</x:v>
+      </x:c>
+      <x:c r="E55" s="12" t="str">
+        <x:v>Jukebox 9</x:v>
+      </x:c>
+      <x:c r="F55" s="12" t="str"/>
+      <x:c r="G55" s="12" t="str"/>
+      <x:c r="H55" s="12" t="str"/>
+      <x:c r="I55" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J55" s="12" t="str"/>
+      <x:c r="K55" s="12" t="str"/>
+      <x:c r="L55" s="12" t="str"/>
+      <x:c r="M55" s="12" t="str"/>
+      <x:c r="N55" s="12" t="str">
+        <x:v>IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="O55" s="12" t="str">
+        <x:v>54_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P55" s="12" t="str"/>
+      <x:c r="Q55" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="R55" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S55" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3242.jpg. </x:v>
+      </x:c>
+      <x:c r="T55" s="12" t="str"/>
+      <x:c r="U55" s="12" t="str"/>
+      <x:c r="V55" s="12" t="str"/>
+      <x:c r="W55" s="12" t="str"/>
+      <x:c r="X55" s="12" t="str"/>
+      <x:c r="Y55" s="12" t="str"/>
+      <x:c r="Z55" s="12" t="str"/>
+      <x:c r="AA55" s="12" t="str"/>
+      <x:c r="AB55" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC55" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD55" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE55" s="12" t="str">
+        <x:v>Collection note: Jukebox 9 by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF55" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="AG55" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH55" s="12" t="str"/>
+      <x:c r="AI55" s="12" t="str"/>
+    </x:row>
+    <x:row r="56" ht="120" customHeight="1">
+      <x:c r="A56" s="12" t="str">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B56" s="12" t="str">
+        <x:v>五木ひろし</x:v>
+      </x:c>
+      <x:c r="C56" s="12" t="str">
+        <x:v>Hiroshi Itsuki</x:v>
+      </x:c>
+      <x:c r="D56" s="12" t="str">
+        <x:v>オリジナル名曲集 千曲川</x:v>
+      </x:c>
+      <x:c r="E56" s="12" t="str">
+        <x:v>Original Meikyokushu: Chikumagawa</x:v>
+      </x:c>
+      <x:c r="F56" s="12" t="str">
+        <x:v>Minoruphone</x:v>
+      </x:c>
+      <x:c r="G56" s="12" t="str"/>
+      <x:c r="H56" s="12" t="str"/>
+      <x:c r="I56" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J56" s="12" t="str"/>
+      <x:c r="K56" s="12" t="str"/>
+      <x:c r="L56" s="12" t="str"/>
+      <x:c r="M56" s="12" t="str"/>
+      <x:c r="N56" s="12" t="str">
+        <x:v>IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="O56" s="12" t="str">
+        <x:v>55_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P56" s="12" t="str"/>
+      <x:c r="Q56" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="R56" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S56" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3242.jpg. </x:v>
+      </x:c>
+      <x:c r="T56" s="12" t="str"/>
+      <x:c r="U56" s="12" t="str"/>
+      <x:c r="V56" s="12" t="str"/>
+      <x:c r="W56" s="12" t="str"/>
+      <x:c r="X56" s="12" t="str"/>
+      <x:c r="Y56" s="12" t="str"/>
+      <x:c r="Z56" s="12" t="str"/>
+      <x:c r="AA56" s="12" t="str"/>
+      <x:c r="AB56" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC56" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD56" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE56" s="12" t="str">
+        <x:v>Collection note: Original Meikyokushu: Chikumagawa by Hiroshi Itsuki, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF56" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="AG56" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH56" s="12" t="str"/>
+      <x:c r="AI56" s="12" t="str"/>
+    </x:row>
+    <x:row r="57" ht="120" customHeight="1">
+      <x:c r="A57" s="12" t="str">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B57" s="12" t="str"/>
+      <x:c r="C57" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D57" s="12" t="str">
+        <x:v>任侠演歌ベスト20</x:v>
+      </x:c>
+      <x:c r="E57" s="12" t="str">
+        <x:v>Ninkyo Enka Best 20</x:v>
+      </x:c>
+      <x:c r="F57" s="12" t="str">
+        <x:v>Crown</x:v>
+      </x:c>
+      <x:c r="G57" s="12" t="str"/>
+      <x:c r="H57" s="12" t="str"/>
+      <x:c r="I57" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J57" s="12" t="str"/>
+      <x:c r="K57" s="12" t="str"/>
+      <x:c r="L57" s="12" t="str"/>
+      <x:c r="M57" s="12" t="str"/>
+      <x:c r="N57" s="12" t="str">
+        <x:v>IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="O57" s="12" t="str">
+        <x:v>56_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P57" s="12" t="str"/>
+      <x:c r="Q57" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="R57" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S57" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3242.jpg. </x:v>
+      </x:c>
+      <x:c r="T57" s="12" t="str"/>
+      <x:c r="U57" s="12" t="str"/>
+      <x:c r="V57" s="12" t="str"/>
+      <x:c r="W57" s="12" t="str"/>
+      <x:c r="X57" s="12" t="str"/>
+      <x:c r="Y57" s="12" t="str"/>
+      <x:c r="Z57" s="12" t="str"/>
+      <x:c r="AA57" s="12" t="str"/>
+      <x:c r="AB57" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC57" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD57" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE57" s="12" t="str">
+        <x:v>Collection note: Various Artists compilation titled Ninkyo Enka Best 20. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF57" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="AG57" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH57" s="12" t="str"/>
+      <x:c r="AI57" s="12" t="str"/>
+    </x:row>
+    <x:row r="58" ht="120" customHeight="1">
+      <x:c r="A58" s="12" t="str">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B58" s="12" t="str">
+        <x:v>演奏者未確認</x:v>
+      </x:c>
+      <x:c r="C58" s="12" t="str">
+        <x:v>Performer to verify</x:v>
+      </x:c>
+      <x:c r="D58" s="12" t="str">
+        <x:v>演歌ギター全曲集</x:v>
+      </x:c>
+      <x:c r="E58" s="12" t="str">
+        <x:v>Enka Guitar Best Hit Album</x:v>
+      </x:c>
+      <x:c r="F58" s="12" t="str"/>
+      <x:c r="G58" s="12" t="str"/>
+      <x:c r="H58" s="12" t="str"/>
+      <x:c r="I58" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J58" s="12" t="str"/>
+      <x:c r="K58" s="12" t="str"/>
+      <x:c r="L58" s="12" t="str"/>
+      <x:c r="M58" s="12" t="str"/>
+      <x:c r="N58" s="12" t="str">
+        <x:v>IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="O58" s="12" t="str">
+        <x:v>57_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P58" s="12" t="str"/>
+      <x:c r="Q58" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="R58" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S58" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3242.jpg. </x:v>
+      </x:c>
+      <x:c r="T58" s="12" t="str"/>
+      <x:c r="U58" s="12" t="str"/>
+      <x:c r="V58" s="12" t="str"/>
+      <x:c r="W58" s="12" t="str"/>
+      <x:c r="X58" s="12" t="str"/>
+      <x:c r="Y58" s="12" t="str"/>
+      <x:c r="Z58" s="12" t="str"/>
+      <x:c r="AA58" s="12" t="str"/>
+      <x:c r="AB58" s="12" t="str">
+        <x:v>Performer identification needs a back-cover or label photo | Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC58" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD58" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE58" s="12" t="str">
+        <x:v>Collection note: Enka Guitar Best Hit Album. Identification is incomplete; the original reference photograph is retained for checking the sleeve and labels.</x:v>
+      </x:c>
+      <x:c r="AF58" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3242.jpg</x:v>
+      </x:c>
+      <x:c r="AG58" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH58" s="12" t="str"/>
+      <x:c r="AI58" s="12" t="str"/>
+    </x:row>
+    <x:row r="59" ht="120" customHeight="1">
+      <x:c r="A59" s="12" t="str">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B59" s="12" t="str">
+        <x:v>小畑実</x:v>
+      </x:c>
+      <x:c r="C59" s="12" t="str">
+        <x:v>Minoru Obata</x:v>
+      </x:c>
+      <x:c r="D59" s="12" t="str">
+        <x:v>勘太郎月夜唄</x:v>
+      </x:c>
+      <x:c r="E59" s="12" t="str">
+        <x:v>Kantaro Tsukiyouta</x:v>
+      </x:c>
+      <x:c r="F59" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G59" s="12" t="str"/>
+      <x:c r="H59" s="12" t="str"/>
+      <x:c r="I59" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J59" s="12" t="str"/>
+      <x:c r="K59" s="12" t="str"/>
+      <x:c r="L59" s="12" t="str"/>
+      <x:c r="M59" s="12" t="str"/>
+      <x:c r="N59" s="12" t="str">
+        <x:v>IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="O59" s="12" t="str">
+        <x:v>58_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P59" s="12" t="str"/>
+      <x:c r="Q59" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="R59" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S59" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3243.jpg. </x:v>
+      </x:c>
+      <x:c r="T59" s="12" t="str"/>
+      <x:c r="U59" s="12" t="str"/>
+      <x:c r="V59" s="12" t="str"/>
+      <x:c r="W59" s="12" t="str"/>
+      <x:c r="X59" s="12" t="str"/>
+      <x:c r="Y59" s="12" t="str"/>
+      <x:c r="Z59" s="12" t="str"/>
+      <x:c r="AA59" s="12" t="str"/>
+      <x:c r="AB59" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC59" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD59" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE59" s="12" t="str">
+        <x:v>Collection note: Kantaro Tsukiyouta by Minoru Obata, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF59" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="AG59" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH59" s="12" t="str"/>
+      <x:c r="AI59" s="12" t="str"/>
+    </x:row>
+    <x:row r="60" ht="120" customHeight="1">
+      <x:c r="A60" s="12" t="str">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B60" s="12" t="str">
+        <x:v>ディック・ミネ</x:v>
+      </x:c>
+      <x:c r="C60" s="12" t="str">
+        <x:v>Dick Mine</x:v>
+      </x:c>
+      <x:c r="D60" s="12" t="str">
+        <x:v>ディック・ミネ全集 若き日の歌声</x:v>
+      </x:c>
+      <x:c r="E60" s="12" t="str">
+        <x:v>Dick Mine Album: Wakaki Hi no Utagoe</x:v>
+      </x:c>
+      <x:c r="F60" s="12" t="str">
+        <x:v>Teichiku</x:v>
+      </x:c>
+      <x:c r="G60" s="12" t="str"/>
+      <x:c r="H60" s="12" t="str"/>
+      <x:c r="I60" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J60" s="12" t="str"/>
+      <x:c r="K60" s="12" t="str"/>
+      <x:c r="L60" s="12" t="str"/>
+      <x:c r="M60" s="12" t="str"/>
+      <x:c r="N60" s="12" t="str">
+        <x:v>IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="O60" s="12" t="str">
+        <x:v>59_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P60" s="12" t="str"/>
+      <x:c r="Q60" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="R60" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S60" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3243.jpg. </x:v>
+      </x:c>
+      <x:c r="T60" s="12" t="str"/>
+      <x:c r="U60" s="12" t="str"/>
+      <x:c r="V60" s="12" t="str"/>
+      <x:c r="W60" s="12" t="str"/>
+      <x:c r="X60" s="12" t="str"/>
+      <x:c r="Y60" s="12" t="str"/>
+      <x:c r="Z60" s="12" t="str"/>
+      <x:c r="AA60" s="12" t="str"/>
+      <x:c r="AB60" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC60" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD60" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE60" s="12" t="str">
+        <x:v>Collection note: Dick Mine Album: Wakaki Hi no Utagoe by Dick Mine, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF60" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="AG60" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH60" s="12" t="str"/>
+      <x:c r="AI60" s="12" t="str"/>
+    </x:row>
+    <x:row r="61" ht="120" customHeight="1">
+      <x:c r="A61" s="12" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B61" s="12" t="str"/>
+      <x:c r="C61" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D61" s="12" t="str">
+        <x:v>麦と兵隊／啼くな小鳩よ</x:v>
+      </x:c>
+      <x:c r="E61" s="12" t="str">
+        <x:v>Mugi to Heitai / Naku na Kobato yo</x:v>
+      </x:c>
+      <x:c r="F61" s="12" t="str">
+        <x:v>Teichiku</x:v>
+      </x:c>
+      <x:c r="G61" s="12" t="str"/>
+      <x:c r="H61" s="12" t="str"/>
+      <x:c r="I61" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J61" s="12" t="str"/>
+      <x:c r="K61" s="12" t="str"/>
+      <x:c r="L61" s="12" t="str"/>
+      <x:c r="M61" s="12" t="str"/>
+      <x:c r="N61" s="12" t="str">
+        <x:v>IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="O61" s="12" t="str">
+        <x:v>60_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P61" s="12" t="str"/>
+      <x:c r="Q61" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="R61" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S61" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3243.jpg. </x:v>
+      </x:c>
+      <x:c r="T61" s="12" t="str"/>
+      <x:c r="U61" s="12" t="str"/>
+      <x:c r="V61" s="12" t="str"/>
+      <x:c r="W61" s="12" t="str"/>
+      <x:c r="X61" s="12" t="str"/>
+      <x:c r="Y61" s="12" t="str"/>
+      <x:c r="Z61" s="12" t="str"/>
+      <x:c r="AA61" s="12" t="str"/>
+      <x:c r="AB61" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC61" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD61" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE61" s="12" t="str">
+        <x:v>Collection note: Mugi to Heitai / Naku na Kobato yo by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF61" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="AG61" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH61" s="12" t="str"/>
+      <x:c r="AI61" s="12" t="str"/>
+    </x:row>
+    <x:row r="62" ht="120" customHeight="1">
+      <x:c r="A62" s="12" t="str">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B62" s="12" t="str">
+        <x:v>春日八郎</x:v>
+      </x:c>
+      <x:c r="C62" s="12" t="str">
+        <x:v>Hachiro Kasuga</x:v>
+      </x:c>
+      <x:c r="D62" s="12" t="str">
+        <x:v>デラックス</x:v>
+      </x:c>
+      <x:c r="E62" s="12" t="str">
+        <x:v>Deluxe</x:v>
+      </x:c>
+      <x:c r="F62" s="12" t="str">
+        <x:v>King</x:v>
+      </x:c>
+      <x:c r="G62" s="12" t="str"/>
+      <x:c r="H62" s="12" t="str"/>
+      <x:c r="I62" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J62" s="12" t="str"/>
+      <x:c r="K62" s="12" t="str"/>
+      <x:c r="L62" s="12" t="str"/>
+      <x:c r="M62" s="12" t="str"/>
+      <x:c r="N62" s="12" t="str">
+        <x:v>IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="O62" s="12" t="str">
+        <x:v>61_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P62" s="12" t="str"/>
+      <x:c r="Q62" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="R62" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S62" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3243.jpg. </x:v>
+      </x:c>
+      <x:c r="T62" s="12" t="str"/>
+      <x:c r="U62" s="12" t="str"/>
+      <x:c r="V62" s="12" t="str"/>
+      <x:c r="W62" s="12" t="str"/>
+      <x:c r="X62" s="12" t="str"/>
+      <x:c r="Y62" s="12" t="str"/>
+      <x:c r="Z62" s="12" t="str"/>
+      <x:c r="AA62" s="12" t="str"/>
+      <x:c r="AB62" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC62" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD62" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE62" s="12" t="str">
+        <x:v>Collection note: Deluxe by Hachiro Kasuga, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF62" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="AG62" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH62" s="12" t="str"/>
+      <x:c r="AI62" s="12" t="str"/>
+    </x:row>
+    <x:row r="63" ht="120" customHeight="1">
+      <x:c r="A63" s="12" t="str">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B63" s="12" t="str">
+        <x:v>フランク永井</x:v>
+      </x:c>
+      <x:c r="C63" s="12" t="str">
+        <x:v>Frank Nagai</x:v>
+      </x:c>
+      <x:c r="D63" s="12" t="str">
+        <x:v>おまえに／おもいやり</x:v>
+      </x:c>
+      <x:c r="E63" s="12" t="str">
+        <x:v>Omae ni / Omoiyari</x:v>
+      </x:c>
+      <x:c r="F63" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G63" s="12" t="str"/>
+      <x:c r="H63" s="12" t="str"/>
+      <x:c r="I63" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J63" s="12" t="str"/>
+      <x:c r="K63" s="12" t="str"/>
+      <x:c r="L63" s="12" t="str"/>
+      <x:c r="M63" s="12" t="str"/>
+      <x:c r="N63" s="12" t="str">
+        <x:v>IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="O63" s="12" t="str">
+        <x:v>62_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P63" s="12" t="str"/>
+      <x:c r="Q63" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="R63" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S63" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3243.jpg. </x:v>
+      </x:c>
+      <x:c r="T63" s="12" t="str"/>
+      <x:c r="U63" s="12" t="str"/>
+      <x:c r="V63" s="12" t="str"/>
+      <x:c r="W63" s="12" t="str"/>
+      <x:c r="X63" s="12" t="str"/>
+      <x:c r="Y63" s="12" t="str"/>
+      <x:c r="Z63" s="12" t="str"/>
+      <x:c r="AA63" s="12" t="str"/>
+      <x:c r="AB63" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC63" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD63" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE63" s="12" t="str">
+        <x:v>Collection note: Omae ni / Omoiyari by Frank Nagai, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF63" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="AG63" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH63" s="12" t="str"/>
+      <x:c r="AI63" s="12" t="str"/>
+    </x:row>
+    <x:row r="64" ht="120" customHeight="1">
+      <x:c r="A64" s="12" t="str">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B64" s="12" t="str">
+        <x:v>灰田勝彦</x:v>
+      </x:c>
+      <x:c r="C64" s="12" t="str">
+        <x:v>Katsuhiko Haida</x:v>
+      </x:c>
+      <x:c r="D64" s="12" t="str">
+        <x:v>アルプスの牧場</x:v>
+      </x:c>
+      <x:c r="E64" s="12" t="str">
+        <x:v>Alps no Makiba</x:v>
+      </x:c>
+      <x:c r="F64" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G64" s="12" t="str"/>
+      <x:c r="H64" s="12" t="str"/>
+      <x:c r="I64" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J64" s="12" t="str"/>
+      <x:c r="K64" s="12" t="str"/>
+      <x:c r="L64" s="12" t="str"/>
+      <x:c r="M64" s="12" t="str"/>
+      <x:c r="N64" s="12" t="str">
+        <x:v>IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="O64" s="12" t="str">
+        <x:v>63_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P64" s="12" t="str"/>
+      <x:c r="Q64" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="R64" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S64" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3243.jpg. </x:v>
+      </x:c>
+      <x:c r="T64" s="12" t="str"/>
+      <x:c r="U64" s="12" t="str"/>
+      <x:c r="V64" s="12" t="str"/>
+      <x:c r="W64" s="12" t="str"/>
+      <x:c r="X64" s="12" t="str"/>
+      <x:c r="Y64" s="12" t="str"/>
+      <x:c r="Z64" s="12" t="str"/>
+      <x:c r="AA64" s="12" t="str"/>
+      <x:c r="AB64" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC64" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD64" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE64" s="12" t="str">
+        <x:v>Collection note: Alps no Makiba by Katsuhiko Haida, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF64" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="AG64" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH64" s="12" t="str"/>
+      <x:c r="AI64" s="12" t="str"/>
+    </x:row>
+    <x:row r="65" ht="120" customHeight="1">
+      <x:c r="A65" s="12" t="str">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B65" s="12" t="str">
+        <x:v>アーティスト未確認</x:v>
+      </x:c>
+      <x:c r="C65" s="12" t="str">
+        <x:v>Artist to verify</x:v>
+      </x:c>
+      <x:c r="D65" s="12" t="str"/>
+      <x:c r="E65" s="12" t="str">
+        <x:v>Untitled portrait sleeve (six-man group)</x:v>
+      </x:c>
+      <x:c r="F65" s="12" t="str"/>
+      <x:c r="G65" s="12" t="str"/>
+      <x:c r="H65" s="12" t="str"/>
+      <x:c r="I65" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J65" s="12" t="str"/>
+      <x:c r="K65" s="12" t="str"/>
+      <x:c r="L65" s="12" t="str"/>
+      <x:c r="M65" s="12" t="str"/>
+      <x:c r="N65" s="12" t="str">
+        <x:v>IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="O65" s="12" t="str">
+        <x:v>64_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P65" s="12" t="str"/>
+      <x:c r="Q65" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="R65" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S65" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3243.jpg. </x:v>
+      </x:c>
+      <x:c r="T65" s="12" t="str"/>
+      <x:c r="U65" s="12" t="str"/>
+      <x:c r="V65" s="12" t="str"/>
+      <x:c r="W65" s="12" t="str"/>
+      <x:c r="X65" s="12" t="str"/>
+      <x:c r="Y65" s="12" t="str"/>
+      <x:c r="Z65" s="12" t="str"/>
+      <x:c r="AA65" s="12" t="str"/>
+      <x:c r="AB65" s="12" t="str">
+        <x:v>Exact title needs a back-cover or label photo | Performer identification needs a back-cover or label photo | Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC65" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD65" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE65" s="12" t="str">
+        <x:v>Collection note: Untitled portrait sleeve (six-man group). Identification is incomplete; the original reference photograph is retained for checking the sleeve and labels.</x:v>
+      </x:c>
+      <x:c r="AF65" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="AG65" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH65" s="12" t="str"/>
+      <x:c r="AI65" s="12" t="str"/>
+    </x:row>
+    <x:row r="66" ht="120" customHeight="1">
+      <x:c r="A66" s="12" t="str">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B66" s="12" t="str">
+        <x:v>森進一</x:v>
+      </x:c>
+      <x:c r="C66" s="12" t="str">
+        <x:v>Shinichi Mori</x:v>
+      </x:c>
+      <x:c r="D66" s="12" t="str">
+        <x:v>熱唱の森進一 オン・ステージ</x:v>
+      </x:c>
+      <x:c r="E66" s="12" t="str">
+        <x:v>Shinichi Mori On Stage</x:v>
+      </x:c>
+      <x:c r="F66" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G66" s="12" t="str"/>
+      <x:c r="H66" s="12" t="str"/>
+      <x:c r="I66" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J66" s="12" t="str"/>
+      <x:c r="K66" s="12" t="str"/>
+      <x:c r="L66" s="12" t="str"/>
+      <x:c r="M66" s="12" t="str"/>
+      <x:c r="N66" s="12" t="str">
+        <x:v>IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="O66" s="12" t="str">
+        <x:v>65_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P66" s="12" t="str"/>
+      <x:c r="Q66" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="R66" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S66" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3243.jpg. </x:v>
+      </x:c>
+      <x:c r="T66" s="12" t="str"/>
+      <x:c r="U66" s="12" t="str"/>
+      <x:c r="V66" s="12" t="str"/>
+      <x:c r="W66" s="12" t="str"/>
+      <x:c r="X66" s="12" t="str"/>
+      <x:c r="Y66" s="12" t="str"/>
+      <x:c r="Z66" s="12" t="str"/>
+      <x:c r="AA66" s="12" t="str"/>
+      <x:c r="AB66" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC66" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD66" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE66" s="12" t="str">
+        <x:v>Collection note: Shinichi Mori compilation titled Shinichi Mori On Stage. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF66" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3243.jpg</x:v>
+      </x:c>
+      <x:c r="AG66" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH66" s="12" t="str"/>
+      <x:c r="AI66" s="12" t="str"/>
+    </x:row>
+    <x:row r="67" ht="120" customHeight="1">
+      <x:c r="A67" s="12" t="str">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B67" s="12" t="str">
+        <x:v>アーティスト未確認</x:v>
+      </x:c>
+      <x:c r="C67" s="12" t="str">
+        <x:v>Artist to verify</x:v>
+      </x:c>
+      <x:c r="D67" s="12" t="str"/>
+      <x:c r="E67" s="12" t="str">
+        <x:v>Title to verify (landscape sleeve with green obi)</x:v>
+      </x:c>
+      <x:c r="F67" s="12" t="str"/>
+      <x:c r="G67" s="12" t="str"/>
+      <x:c r="H67" s="12" t="str"/>
+      <x:c r="I67" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J67" s="12" t="str"/>
+      <x:c r="K67" s="12" t="str"/>
+      <x:c r="L67" s="12" t="str"/>
+      <x:c r="M67" s="12" t="str"/>
+      <x:c r="N67" s="12" t="str">
+        <x:v>IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="O67" s="12" t="str">
+        <x:v>66_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P67" s="12" t="str"/>
+      <x:c r="Q67" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="R67" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S67" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3244.jpg. </x:v>
+      </x:c>
+      <x:c r="T67" s="12" t="str"/>
+      <x:c r="U67" s="12" t="str"/>
+      <x:c r="V67" s="12" t="str"/>
+      <x:c r="W67" s="12" t="str"/>
+      <x:c r="X67" s="12" t="str"/>
+      <x:c r="Y67" s="12" t="str"/>
+      <x:c r="Z67" s="12" t="str"/>
+      <x:c r="AA67" s="12" t="str"/>
+      <x:c r="AB67" s="12" t="str">
+        <x:v>Exact title needs a back-cover or label photo | Performer identification needs a back-cover or label photo | Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC67" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD67" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE67" s="12" t="str">
+        <x:v>Collection note: Title to verify (landscape sleeve with green obi). Identification is incomplete; the original reference photograph is retained for checking the sleeve and labels.</x:v>
+      </x:c>
+      <x:c r="AF67" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="AG67" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH67" s="12" t="str"/>
+      <x:c r="AI67" s="12" t="str"/>
+    </x:row>
+    <x:row r="68" ht="120" customHeight="1">
+      <x:c r="A68" s="12" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B68" s="12" t="str">
+        <x:v>アーティスト未確認</x:v>
+      </x:c>
+      <x:c r="C68" s="12" t="str">
+        <x:v>Artist to verify</x:v>
+      </x:c>
+      <x:c r="D68" s="12" t="str"/>
+      <x:c r="E68" s="12" t="str">
+        <x:v>Title to verify (orange suit portrait)</x:v>
+      </x:c>
+      <x:c r="F68" s="12" t="str"/>
+      <x:c r="G68" s="12" t="str"/>
+      <x:c r="H68" s="12" t="str"/>
+      <x:c r="I68" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J68" s="12" t="str"/>
+      <x:c r="K68" s="12" t="str"/>
+      <x:c r="L68" s="12" t="str"/>
+      <x:c r="M68" s="12" t="str"/>
+      <x:c r="N68" s="12" t="str">
+        <x:v>IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="O68" s="12" t="str">
+        <x:v>67_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P68" s="12" t="str"/>
+      <x:c r="Q68" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="R68" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S68" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3244.jpg. </x:v>
+      </x:c>
+      <x:c r="T68" s="12" t="str"/>
+      <x:c r="U68" s="12" t="str"/>
+      <x:c r="V68" s="12" t="str"/>
+      <x:c r="W68" s="12" t="str"/>
+      <x:c r="X68" s="12" t="str"/>
+      <x:c r="Y68" s="12" t="str"/>
+      <x:c r="Z68" s="12" t="str"/>
+      <x:c r="AA68" s="12" t="str"/>
+      <x:c r="AB68" s="12" t="str">
+        <x:v>Exact title needs a back-cover or label photo | Performer identification needs a back-cover or label photo | Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC68" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD68" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE68" s="12" t="str">
+        <x:v>Collection note: Title to verify (orange suit portrait). Identification is incomplete; the original reference photograph is retained for checking the sleeve and labels.</x:v>
+      </x:c>
+      <x:c r="AF68" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="AG68" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH68" s="12" t="str"/>
+      <x:c r="AI68" s="12" t="str"/>
+    </x:row>
+    <x:row r="69" ht="120" customHeight="1">
+      <x:c r="A69" s="12" t="str">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B69" s="12" t="str">
+        <x:v>春日井梅鶯</x:v>
+      </x:c>
+      <x:c r="C69" s="12" t="str">
+        <x:v>Baio Kasugai</x:v>
+      </x:c>
+      <x:c r="D69" s="12" t="str">
+        <x:v>浪曲名人選 南部坂雪の別れ／仇討前夜</x:v>
+      </x:c>
+      <x:c r="E69" s="12" t="str">
+        <x:v>Rokyoku Meijinsen: Nanbuzaka Yuki no Wakare / Adauchi Zenya</x:v>
+      </x:c>
+      <x:c r="F69" s="12" t="str"/>
+      <x:c r="G69" s="12" t="str"/>
+      <x:c r="H69" s="12" t="str"/>
+      <x:c r="I69" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J69" s="12" t="str"/>
+      <x:c r="K69" s="12" t="str"/>
+      <x:c r="L69" s="12" t="str"/>
+      <x:c r="M69" s="12" t="str"/>
+      <x:c r="N69" s="12" t="str">
+        <x:v>IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="O69" s="12" t="str">
+        <x:v>68_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P69" s="12" t="str"/>
+      <x:c r="Q69" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="R69" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S69" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3244.jpg. </x:v>
+      </x:c>
+      <x:c r="T69" s="12" t="str"/>
+      <x:c r="U69" s="12" t="str"/>
+      <x:c r="V69" s="12" t="str"/>
+      <x:c r="W69" s="12" t="str"/>
+      <x:c r="X69" s="12" t="str"/>
+      <x:c r="Y69" s="12" t="str"/>
+      <x:c r="Z69" s="12" t="str"/>
+      <x:c r="AA69" s="12" t="str"/>
+      <x:c r="AB69" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC69" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD69" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE69" s="12" t="str">
+        <x:v>Collection note: Rokyoku Meijinsen: Nanbuzaka Yuki no Wakare / Adauchi Zenya by Baio Kasugai, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF69" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="AG69" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH69" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E6%98%A5%E6%97%A5%E4%BA%95%E6%A2%85%E9%B6%AF/918832927?uo=4</x:v>
+      </x:c>
+      <x:c r="AI69" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="120" customHeight="1">
+      <x:c r="A70" s="12" t="str">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B70" s="12" t="str">
+        <x:v>菅原洋一</x:v>
+      </x:c>
+      <x:c r="C70" s="12" t="str">
+        <x:v>Yoichi Sugawara</x:v>
+      </x:c>
+      <x:c r="D70" s="12" t="str">
+        <x:v>魅力のすべて</x:v>
+      </x:c>
+      <x:c r="E70" s="12" t="str">
+        <x:v>Miryoku no Subete</x:v>
+      </x:c>
+      <x:c r="F70" s="12" t="str">
+        <x:v>Polydor</x:v>
+      </x:c>
+      <x:c r="G70" s="12" t="str">
+        <x:v>MR-3054</x:v>
+      </x:c>
+      <x:c r="H70" s="12" t="str">
+        <x:v>1969</x:v>
+      </x:c>
+      <x:c r="I70" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J70" s="12" t="str"/>
+      <x:c r="K70" s="12" t="str"/>
+      <x:c r="L70" s="12" t="str"/>
+      <x:c r="M70" s="12" t="str"/>
+      <x:c r="N70" s="12" t="str">
+        <x:v>IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="O70" s="12" t="str">
+        <x:v>69_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P70" s="12" t="str"/>
+      <x:c r="Q70" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="R70" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S70" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3244.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Metadata source: https://www.snowrecords.jp/?pid=174712227</x:v>
+      </x:c>
+      <x:c r="T70" s="12" t="str"/>
+      <x:c r="U70" s="12" t="str"/>
+      <x:c r="V70" s="12" t="str"/>
+      <x:c r="W70" s="12" t="str"/>
+      <x:c r="X70" s="12" t="str"/>
+      <x:c r="Y70" s="12" t="str"/>
+      <x:c r="Z70" s="12" t="str"/>
+      <x:c r="AA70" s="12" t="str"/>
+      <x:c r="AB70" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC70" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD70" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE70" s="12" t="str">
+        <x:v>A Polydor collection of Yoichi Sugawara recordings, issued as MR-3054 in 1969. The photographed sleeve carries the title Miryoku no Subete.</x:v>
+      </x:c>
+      <x:c r="AF70" s="12" t="str">
+        <x:v>https://www.snowrecords.jp/?pid=174712227</x:v>
+      </x:c>
+      <x:c r="AG70" s="12" t="str">
+        <x:v>Snow Records release listing</x:v>
+      </x:c>
+      <x:c r="AH70" s="12" t="str"/>
+      <x:c r="AI70" s="12" t="str"/>
+    </x:row>
+    <x:row r="71" ht="120" customHeight="1">
+      <x:c r="A71" s="12" t="str">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B71" s="12" t="str">
+        <x:v>演奏者未確認</x:v>
+      </x:c>
+      <x:c r="C71" s="12" t="str">
+        <x:v>Performer to verify</x:v>
+      </x:c>
+      <x:c r="D71" s="12" t="str">
+        <x:v>スチールギターによる日本歌謡史 第3集 君恋し</x:v>
+      </x:c>
+      <x:c r="E71" s="12" t="str">
+        <x:v>Nihon Kayoshi Vol. 3: Kimi Koishi (Steel Guitar)</x:v>
+      </x:c>
+      <x:c r="F71" s="12" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="G71" s="12" t="str"/>
+      <x:c r="H71" s="12" t="str"/>
+      <x:c r="I71" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J71" s="12" t="str"/>
+      <x:c r="K71" s="12" t="str"/>
+      <x:c r="L71" s="12" t="str"/>
+      <x:c r="M71" s="12" t="str"/>
+      <x:c r="N71" s="12" t="str">
+        <x:v>IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="O71" s="12" t="str">
+        <x:v>70_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P71" s="12" t="str"/>
+      <x:c r="Q71" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="R71" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S71" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3244.jpg. </x:v>
+      </x:c>
+      <x:c r="T71" s="12" t="str"/>
+      <x:c r="U71" s="12" t="str"/>
+      <x:c r="V71" s="12" t="str"/>
+      <x:c r="W71" s="12" t="str"/>
+      <x:c r="X71" s="12" t="str"/>
+      <x:c r="Y71" s="12" t="str"/>
+      <x:c r="Z71" s="12" t="str"/>
+      <x:c r="AA71" s="12" t="str"/>
+      <x:c r="AB71" s="12" t="str">
+        <x:v>Performer identification needs a back-cover or label photo | Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC71" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD71" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE71" s="12" t="str">
+        <x:v>Collection note: Nihon Kayoshi Vol. 3: Kimi Koishi (Steel Guitar). Identification is incomplete; the original reference photograph is retained for checking the sleeve and labels.</x:v>
+      </x:c>
+      <x:c r="AF71" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="AG71" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH71" s="12" t="str"/>
+      <x:c r="AI71" s="12" t="str"/>
+    </x:row>
+    <x:row r="72" ht="120" customHeight="1">
+      <x:c r="A72" s="12" t="str">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B72" s="12" t="str">
+        <x:v>鶴田浩二</x:v>
+      </x:c>
+      <x:c r="C72" s="12" t="str">
+        <x:v>Koji Tsuruta</x:v>
+      </x:c>
+      <x:c r="D72" s="12" t="str">
+        <x:v>ベスト・コレクション’76</x:v>
+      </x:c>
+      <x:c r="E72" s="12" t="str">
+        <x:v>Best Collection '76</x:v>
+      </x:c>
+      <x:c r="F72" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G72" s="12" t="str">
+        <x:v>SJV-828~829</x:v>
+      </x:c>
+      <x:c r="H72" s="12" t="str">
+        <x:v>1976</x:v>
+      </x:c>
+      <x:c r="I72" s="12" t="str">
+        <x:v>2LP</x:v>
+      </x:c>
+      <x:c r="J72" s="12" t="str"/>
+      <x:c r="K72" s="12" t="str"/>
+      <x:c r="L72" s="12" t="str"/>
+      <x:c r="M72" s="12" t="str"/>
+      <x:c r="N72" s="12" t="str">
+        <x:v>IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="O72" s="12" t="str">
+        <x:v>71_retailer_front.jpg</x:v>
+      </x:c>
+      <x:c r="P72" s="12" t="str"/>
+      <x:c r="Q72" s="12" t="str">
+        <x:v>https://www.snowrecords.jp/?pid=121676306</x:v>
+      </x:c>
+      <x:c r="R72" s="12" t="str">
+        <x:v>retailer</x:v>
+      </x:c>
+      <x:c r="S72" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3244.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Metadata source: https://www.snowrecords.jp/?pid=121676306</x:v>
+      </x:c>
+      <x:c r="T72" s="12" t="str"/>
+      <x:c r="U72" s="12" t="str"/>
+      <x:c r="V72" s="12" t="str"/>
+      <x:c r="W72" s="12" t="str"/>
+      <x:c r="X72" s="12" t="str"/>
+      <x:c r="Y72" s="12" t="str"/>
+      <x:c r="Z72" s="12" t="str"/>
+      <x:c r="AA72" s="12" t="str"/>
+      <x:c r="AB72" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC72" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD72" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE72" s="12" t="str">
+        <x:v>Koji Tsuruta’s double-album Best Collection ’76, issued by Victor. The red portrait sleeve matches the SJV-828~829 edition.</x:v>
+      </x:c>
+      <x:c r="AF72" s="12" t="str">
+        <x:v>https://www.snowrecords.jp/?pid=121676306</x:v>
+      </x:c>
+      <x:c r="AG72" s="12" t="str">
+        <x:v>Snow Records release listing</x:v>
+      </x:c>
+      <x:c r="AH72" s="12" t="str"/>
+      <x:c r="AI72" s="12" t="str"/>
+    </x:row>
+    <x:row r="73" ht="120" customHeight="1">
+      <x:c r="A73" s="12" t="str">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B73" s="12" t="str">
+        <x:v>アーティスト未確認</x:v>
+      </x:c>
+      <x:c r="C73" s="12" t="str">
+        <x:v>Artist to verify</x:v>
+      </x:c>
+      <x:c r="D73" s="12" t="str"/>
+      <x:c r="E73" s="12" t="str">
+        <x:v>Title to verify (red background portrait)</x:v>
+      </x:c>
+      <x:c r="F73" s="12" t="str"/>
+      <x:c r="G73" s="12" t="str"/>
+      <x:c r="H73" s="12" t="str"/>
+      <x:c r="I73" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J73" s="12" t="str"/>
+      <x:c r="K73" s="12" t="str"/>
+      <x:c r="L73" s="12" t="str"/>
+      <x:c r="M73" s="12" t="str"/>
+      <x:c r="N73" s="12" t="str">
+        <x:v>IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="O73" s="12" t="str">
+        <x:v>72_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P73" s="12" t="str"/>
+      <x:c r="Q73" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="R73" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S73" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3244.jpg. </x:v>
+      </x:c>
+      <x:c r="T73" s="12" t="str"/>
+      <x:c r="U73" s="12" t="str"/>
+      <x:c r="V73" s="12" t="str"/>
+      <x:c r="W73" s="12" t="str"/>
+      <x:c r="X73" s="12" t="str"/>
+      <x:c r="Y73" s="12" t="str"/>
+      <x:c r="Z73" s="12" t="str"/>
+      <x:c r="AA73" s="12" t="str"/>
+      <x:c r="AB73" s="12" t="str">
+        <x:v>Exact title needs a back-cover or label photo | Performer identification needs a back-cover or label photo | Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC73" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD73" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE73" s="12" t="str">
+        <x:v>Collection note: Title to verify (red background portrait). Identification is incomplete; the original reference photograph is retained for checking the sleeve and labels.</x:v>
+      </x:c>
+      <x:c r="AF73" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="AG73" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH73" s="12" t="str"/>
+      <x:c r="AI73" s="12" t="str"/>
+    </x:row>
+    <x:row r="74" ht="120" customHeight="1">
+      <x:c r="A74" s="12" t="str">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B74" s="12" t="str">
+        <x:v>鶴田浩二</x:v>
+      </x:c>
+      <x:c r="C74" s="12" t="str">
+        <x:v>Koji Tsuruta</x:v>
+      </x:c>
+      <x:c r="D74" s="12" t="str">
+        <x:v>あゝ軍歌</x:v>
+      </x:c>
+      <x:c r="E74" s="12" t="str">
+        <x:v>Aa Gunka</x:v>
+      </x:c>
+      <x:c r="F74" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G74" s="12" t="str"/>
+      <x:c r="H74" s="12" t="str"/>
+      <x:c r="I74" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J74" s="12" t="str"/>
+      <x:c r="K74" s="12" t="str"/>
+      <x:c r="L74" s="12" t="str"/>
+      <x:c r="M74" s="12" t="str"/>
+      <x:c r="N74" s="12" t="str">
+        <x:v>IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="O74" s="12" t="str">
+        <x:v>73_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P74" s="12" t="str"/>
+      <x:c r="Q74" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="R74" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S74" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3244.jpg. </x:v>
+      </x:c>
+      <x:c r="T74" s="12" t="str"/>
+      <x:c r="U74" s="12" t="str"/>
+      <x:c r="V74" s="12" t="str"/>
+      <x:c r="W74" s="12" t="str"/>
+      <x:c r="X74" s="12" t="str"/>
+      <x:c r="Y74" s="12" t="str"/>
+      <x:c r="Z74" s="12" t="str"/>
+      <x:c r="AA74" s="12" t="str"/>
+      <x:c r="AB74" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC74" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD74" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE74" s="12" t="str">
+        <x:v>Collection note: Aa Gunka by Koji Tsuruta, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF74" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3244.jpg</x:v>
+      </x:c>
+      <x:c r="AG74" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH74" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E9%B6%B4%E7%94%B0%E6%B5%A9%E4%BA%8C/281413182?uo=4</x:v>
+      </x:c>
+      <x:c r="AI74" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="120" customHeight="1">
+      <x:c r="A75" s="12" t="str">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B75" s="12" t="str">
+        <x:v>内山田洋とクール・ファイブ</x:v>
+      </x:c>
+      <x:c r="C75" s="12" t="str">
+        <x:v>Hiroshi Uchiyamada &amp; Cool Five</x:v>
+      </x:c>
+      <x:c r="D75" s="12" t="str">
+        <x:v>愛の扉</x:v>
+      </x:c>
+      <x:c r="E75" s="12" t="str">
+        <x:v>Very Best: Ai no Tobira</x:v>
+      </x:c>
+      <x:c r="F75" s="12" t="str">
+        <x:v>RCA</x:v>
+      </x:c>
+      <x:c r="G75" s="12" t="str"/>
+      <x:c r="H75" s="12" t="str"/>
+      <x:c r="I75" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J75" s="12" t="str"/>
+      <x:c r="K75" s="12" t="str"/>
+      <x:c r="L75" s="12" t="str"/>
+      <x:c r="M75" s="12" t="str"/>
+      <x:c r="N75" s="12" t="str">
+        <x:v>IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="O75" s="12" t="str">
+        <x:v>74_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P75" s="12" t="str"/>
+      <x:c r="Q75" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="R75" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S75" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3245.jpg. </x:v>
+      </x:c>
+      <x:c r="T75" s="12" t="str"/>
+      <x:c r="U75" s="12" t="str"/>
+      <x:c r="V75" s="12" t="str"/>
+      <x:c r="W75" s="12" t="str"/>
+      <x:c r="X75" s="12" t="str"/>
+      <x:c r="Y75" s="12" t="str"/>
+      <x:c r="Z75" s="12" t="str"/>
+      <x:c r="AA75" s="12" t="str"/>
+      <x:c r="AB75" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC75" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD75" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE75" s="12" t="str">
+        <x:v>Collection note: Very Best: Ai no Tobira by Hiroshi Uchiyamada &amp; Cool Five, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF75" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="AG75" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH75" s="12" t="str"/>
+      <x:c r="AI75" s="12" t="str"/>
+    </x:row>
+    <x:row r="76" ht="120" customHeight="1">
+      <x:c r="A76" s="12" t="str">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B76" s="12" t="str">
+        <x:v>加山雄三</x:v>
+      </x:c>
+      <x:c r="C76" s="12" t="str">
+        <x:v>Yuzo Kayama</x:v>
+      </x:c>
+      <x:c r="D76" s="12" t="str">
+        <x:v>加山雄三通り</x:v>
+      </x:c>
+      <x:c r="E76" s="12" t="str">
+        <x:v>Kayama Yuzo Dori</x:v>
+      </x:c>
+      <x:c r="F76" s="12" t="str"/>
+      <x:c r="G76" s="12" t="str"/>
+      <x:c r="H76" s="12" t="str">
+        <x:v>1978</x:v>
+      </x:c>
+      <x:c r="I76" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J76" s="12" t="str"/>
+      <x:c r="K76" s="12" t="str"/>
+      <x:c r="L76" s="12" t="str"/>
+      <x:c r="M76" s="12" t="str"/>
+      <x:c r="N76" s="12" t="str">
+        <x:v>IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="O76" s="12" t="str">
+        <x:v>75_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P76" s="12" t="str"/>
+      <x:c r="Q76" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="R76" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S76" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3245.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Metadata source: https://www.kayamayuzo.com/release/?select=album&amp;y=1970</x:v>
+      </x:c>
+      <x:c r="T76" s="12" t="str"/>
+      <x:c r="U76" s="12" t="str"/>
+      <x:c r="V76" s="12" t="str"/>
+      <x:c r="W76" s="12" t="str"/>
+      <x:c r="X76" s="12" t="str"/>
+      <x:c r="Y76" s="12" t="str"/>
+      <x:c r="Z76" s="12" t="str"/>
+      <x:c r="AA76" s="12" t="str"/>
+      <x:c r="AB76" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC76" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD76" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE76" s="12" t="str">
+        <x:v>Released in June 1978, Kayama Yuzo Dori includes Koshinmaru, Space Mermaid and the title song. Its sleeve shows Kayama aboard a boat.</x:v>
+      </x:c>
+      <x:c r="AF76" s="12" t="str">
+        <x:v>https://www.kayamayuzo.com/release/?select=album&amp;y=1970</x:v>
+      </x:c>
+      <x:c r="AG76" s="12" t="str">
+        <x:v>Yuzo Kayama official discography</x:v>
+      </x:c>
+      <x:c r="AH76" s="12" t="str">
+        <x:v>https://www.kayamayuzo.com/</x:v>
+      </x:c>
+      <x:c r="AI76" s="12" t="str">
+        <x:v>Official artist website</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="120" customHeight="1">
+      <x:c r="A77" s="12" t="str">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B77" s="12" t="str">
+        <x:v>ツトム・ヤマシタ＆カム・トゥ・ジ・エッジ</x:v>
+      </x:c>
+      <x:c r="C77" s="12" t="str">
+        <x:v>Stomu Yamashta &amp; Come to the Edge</x:v>
+      </x:c>
+      <x:c r="D77" s="12" t="str"/>
+      <x:c r="E77" s="12" t="str">
+        <x:v>Floating Music</x:v>
+      </x:c>
+      <x:c r="F77" s="12" t="str"/>
+      <x:c r="G77" s="12" t="str"/>
+      <x:c r="H77" s="12" t="str">
+        <x:v>1972</x:v>
+      </x:c>
+      <x:c r="I77" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J77" s="12" t="str"/>
+      <x:c r="K77" s="12" t="str"/>
+      <x:c r="L77" s="12" t="str"/>
+      <x:c r="M77" s="12" t="str"/>
+      <x:c r="N77" s="12" t="str">
+        <x:v>IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="O77" s="12" t="str">
+        <x:v>76_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P77" s="12" t="str"/>
+      <x:c r="Q77" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="R77" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S77" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3245.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Metadata source: https://progrography.com/stomu-yamashta/stomu-yamashta-discography/</x:v>
+      </x:c>
+      <x:c r="T77" s="12" t="str"/>
+      <x:c r="U77" s="12" t="str"/>
+      <x:c r="V77" s="12" t="str"/>
+      <x:c r="W77" s="12" t="str"/>
+      <x:c r="X77" s="12" t="str"/>
+      <x:c r="Y77" s="12" t="str"/>
+      <x:c r="Z77" s="12" t="str"/>
+      <x:c r="AA77" s="12" t="str"/>
+      <x:c r="AB77" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC77" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD77" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE77" s="12" t="str">
+        <x:v>Floating Music pairs percussionist Stomu Yamashta with Come to the Edge. The 1972 album contains Poker Dice, Keep in Lane, Xingu and One Way.</x:v>
+      </x:c>
+      <x:c r="AF77" s="12" t="str">
+        <x:v>https://progrography.com/stomu-yamashta/stomu-yamashta-discography/</x:v>
+      </x:c>
+      <x:c r="AG77" s="12" t="str">
+        <x:v>Progrography discography</x:v>
+      </x:c>
+      <x:c r="AH77" s="12" t="str"/>
+      <x:c r="AI77" s="12" t="str"/>
+    </x:row>
+    <x:row r="78" ht="120" customHeight="1">
+      <x:c r="A78" s="12" t="str">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B78" s="12" t="str">
+        <x:v>ツトム・ヤマシタ</x:v>
+      </x:c>
+      <x:c r="C78" s="12" t="str">
+        <x:v>Stomu Yamashta</x:v>
+      </x:c>
+      <x:c r="D78" s="12" t="str"/>
+      <x:c r="E78" s="12" t="str">
+        <x:v>Red Buddha Theatre: The Man from the East</x:v>
+      </x:c>
+      <x:c r="F78" s="12" t="str"/>
+      <x:c r="G78" s="12" t="str"/>
+      <x:c r="H78" s="12" t="str">
+        <x:v>1973</x:v>
+      </x:c>
+      <x:c r="I78" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J78" s="12" t="str"/>
+      <x:c r="K78" s="12" t="str"/>
+      <x:c r="L78" s="12" t="str"/>
+      <x:c r="M78" s="12" t="str"/>
+      <x:c r="N78" s="12" t="str">
+        <x:v>IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="O78" s="12" t="str">
+        <x:v>77_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P78" s="12" t="str"/>
+      <x:c r="Q78" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="R78" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S78" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3245.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Metadata source: https://progrography.com/stomu-yamashta/stomu-yamashta-discography/</x:v>
+      </x:c>
+      <x:c r="T78" s="12" t="str"/>
+      <x:c r="U78" s="12" t="str"/>
+      <x:c r="V78" s="12" t="str"/>
+      <x:c r="W78" s="12" t="str"/>
+      <x:c r="X78" s="12" t="str"/>
+      <x:c r="Y78" s="12" t="str"/>
+      <x:c r="Z78" s="12" t="str"/>
+      <x:c r="AA78" s="12" t="str"/>
+      <x:c r="AB78" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC78" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD78" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE78" s="12" t="str">
+        <x:v>Music for The Man from the East, the Red Buddha Theatre production led by Stomu Yamashta. The soundtrack was first issued in 1973.</x:v>
+      </x:c>
+      <x:c r="AF78" s="12" t="str">
+        <x:v>https://progrography.com/stomu-yamashta/stomu-yamashta-discography/</x:v>
+      </x:c>
+      <x:c r="AG78" s="12" t="str">
+        <x:v>Progrography discography</x:v>
+      </x:c>
+      <x:c r="AH78" s="12" t="str"/>
+      <x:c r="AI78" s="12" t="str"/>
+    </x:row>
+    <x:row r="79" ht="120" customHeight="1">
+      <x:c r="A79" s="12" t="str">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B79" s="12" t="str">
+        <x:v>小林旭</x:v>
+      </x:c>
+      <x:c r="C79" s="12" t="str">
+        <x:v>Akira Kobayashi</x:v>
+      </x:c>
+      <x:c r="D79" s="12" t="str">
+        <x:v>ヒット・パレード 1</x:v>
+      </x:c>
+      <x:c r="E79" s="12" t="str">
+        <x:v>Hit Parade 1</x:v>
+      </x:c>
+      <x:c r="F79" s="12" t="str">
+        <x:v>Crown</x:v>
+      </x:c>
+      <x:c r="G79" s="12" t="str"/>
+      <x:c r="H79" s="12" t="str"/>
+      <x:c r="I79" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J79" s="12" t="str"/>
+      <x:c r="K79" s="12" t="str"/>
+      <x:c r="L79" s="12" t="str"/>
+      <x:c r="M79" s="12" t="str"/>
+      <x:c r="N79" s="12" t="str">
+        <x:v>IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="O79" s="12" t="str">
+        <x:v>78_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P79" s="12" t="str"/>
+      <x:c r="Q79" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="R79" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S79" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3245.jpg. </x:v>
+      </x:c>
+      <x:c r="T79" s="12" t="str"/>
+      <x:c r="U79" s="12" t="str"/>
+      <x:c r="V79" s="12" t="str"/>
+      <x:c r="W79" s="12" t="str"/>
+      <x:c r="X79" s="12" t="str"/>
+      <x:c r="Y79" s="12" t="str"/>
+      <x:c r="Z79" s="12" t="str"/>
+      <x:c r="AA79" s="12" t="str"/>
+      <x:c r="AB79" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC79" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD79" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE79" s="12" t="str">
+        <x:v>Collection note: Hit Parade 1 by Akira Kobayashi, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF79" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="AG79" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH79" s="12" t="str"/>
+      <x:c r="AI79" s="12" t="str"/>
+    </x:row>
+    <x:row r="80" ht="120" customHeight="1">
+      <x:c r="A80" s="12" t="str">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B80" s="12" t="str">
+        <x:v>石原裕次郎</x:v>
+      </x:c>
+      <x:c r="C80" s="12" t="str">
+        <x:v>Yujiro Ishihara</x:v>
+      </x:c>
+      <x:c r="D80" s="12" t="str">
+        <x:v>スクリーン・メモリー</x:v>
+      </x:c>
+      <x:c r="E80" s="12" t="str">
+        <x:v>Screen Memory: Best 20 Deluxe</x:v>
+      </x:c>
+      <x:c r="F80" s="12" t="str">
+        <x:v>Teichiku</x:v>
+      </x:c>
+      <x:c r="G80" s="12" t="str"/>
+      <x:c r="H80" s="12" t="str"/>
+      <x:c r="I80" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J80" s="12" t="str"/>
+      <x:c r="K80" s="12" t="str"/>
+      <x:c r="L80" s="12" t="str"/>
+      <x:c r="M80" s="12" t="str"/>
+      <x:c r="N80" s="12" t="str">
+        <x:v>IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="O80" s="12" t="str">
+        <x:v>79_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P80" s="12" t="str"/>
+      <x:c r="Q80" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="R80" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S80" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3245.jpg. </x:v>
+      </x:c>
+      <x:c r="T80" s="12" t="str"/>
+      <x:c r="U80" s="12" t="str"/>
+      <x:c r="V80" s="12" t="str"/>
+      <x:c r="W80" s="12" t="str"/>
+      <x:c r="X80" s="12" t="str"/>
+      <x:c r="Y80" s="12" t="str"/>
+      <x:c r="Z80" s="12" t="str"/>
+      <x:c r="AA80" s="12" t="str"/>
+      <x:c r="AB80" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC80" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD80" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE80" s="12" t="str">
+        <x:v>Collection note: Screen Memory: Best 20 Deluxe by Yujiro Ishihara, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF80" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="AG80" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH80" s="12" t="str"/>
+      <x:c r="AI80" s="12" t="str"/>
+    </x:row>
+    <x:row r="81" ht="120" customHeight="1">
+      <x:c r="A81" s="12" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B81" s="12" t="str">
+        <x:v>郷ひろみ</x:v>
+      </x:c>
+      <x:c r="C81" s="12" t="str">
+        <x:v>Hiromi Go</x:v>
+      </x:c>
+      <x:c r="D81" s="12" t="str"/>
+      <x:c r="E81" s="12" t="str">
+        <x:v>Hiromi Go (white-wall portrait sleeve)</x:v>
+      </x:c>
+      <x:c r="F81" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G81" s="12" t="str"/>
+      <x:c r="H81" s="12" t="str"/>
+      <x:c r="I81" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J81" s="12" t="str"/>
+      <x:c r="K81" s="12" t="str"/>
+      <x:c r="L81" s="12" t="str"/>
+      <x:c r="M81" s="12" t="str"/>
+      <x:c r="N81" s="12" t="str">
+        <x:v>IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="O81" s="12" t="str">
+        <x:v>80_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P81" s="12" t="str"/>
+      <x:c r="Q81" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="R81" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S81" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3245.jpg. </x:v>
+      </x:c>
+      <x:c r="T81" s="12" t="str"/>
+      <x:c r="U81" s="12" t="str"/>
+      <x:c r="V81" s="12" t="str"/>
+      <x:c r="W81" s="12" t="str"/>
+      <x:c r="X81" s="12" t="str"/>
+      <x:c r="Y81" s="12" t="str"/>
+      <x:c r="Z81" s="12" t="str"/>
+      <x:c r="AA81" s="12" t="str"/>
+      <x:c r="AB81" s="12" t="str">
+        <x:v>Exact title needs a back-cover or label photo | Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC81" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD81" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE81" s="12" t="str">
+        <x:v>Collection note: Hiromi Go (white-wall portrait sleeve). Identification is incomplete; the original reference photograph is retained for checking the sleeve and labels.</x:v>
+      </x:c>
+      <x:c r="AF81" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="AG81" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH81" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E9%83%B7-%E3%81%B2%E3%82%8D%E3%81%BF/988624744?uo=4</x:v>
+      </x:c>
+      <x:c r="AI81" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="120" customHeight="1">
+      <x:c r="A82" s="12" t="str">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B82" s="12" t="str">
+        <x:v>さだまさし</x:v>
+      </x:c>
+      <x:c r="C82" s="12" t="str">
+        <x:v>Masashi Sada</x:v>
+      </x:c>
+      <x:c r="D82" s="12" t="str">
+        <x:v>帰去来</x:v>
+      </x:c>
+      <x:c r="E82" s="12" t="str">
+        <x:v>Kikyorai</x:v>
+      </x:c>
+      <x:c r="F82" s="12" t="str">
+        <x:v>Warner-Pioneer</x:v>
+      </x:c>
+      <x:c r="G82" s="12" t="str"/>
+      <x:c r="H82" s="12" t="str">
+        <x:v>1976</x:v>
+      </x:c>
+      <x:c r="I82" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J82" s="12" t="str"/>
+      <x:c r="K82" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L82" s="12" t="str"/>
+      <x:c r="M82" s="12" t="str"/>
+      <x:c r="N82" s="12" t="str">
+        <x:v>IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="O82" s="12" t="str">
+        <x:v>81_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P82" s="12" t="str"/>
+      <x:c r="Q82" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E5%B8%B0%E5%8E%BB%E6%9D%A5/321150745?uo=4</x:v>
+      </x:c>
+      <x:c r="R82" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S82" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3245.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T82" s="12" t="str"/>
+      <x:c r="U82" s="12" t="str"/>
+      <x:c r="V82" s="12" t="str"/>
+      <x:c r="W82" s="12" t="str"/>
+      <x:c r="X82" s="12" t="str"/>
+      <x:c r="Y82" s="12" t="str"/>
+      <x:c r="Z82" s="12" t="str"/>
+      <x:c r="AA82" s="12" t="str"/>
+      <x:c r="AB82" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC82" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD82" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE82" s="12" t="str">
+        <x:v>Collection note: Kikyorai by Masashi Sada, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF82" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="AG82" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH82" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E3%81%95%E3%81%A0%E3%81%BE%E3%81%95%E3%81%97/74490576?uo=4</x:v>
+      </x:c>
+      <x:c r="AI82" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="120" customHeight="1">
+      <x:c r="A83" s="12" t="str">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B83" s="12" t="str">
+        <x:v>かぐや姫</x:v>
+      </x:c>
+      <x:c r="C83" s="12" t="str">
+        <x:v>Kaguyahime</x:v>
+      </x:c>
+      <x:c r="D83" s="12" t="str">
+        <x:v>レッツ・ゴー！かぐや姫</x:v>
+      </x:c>
+      <x:c r="E83" s="12" t="str">
+        <x:v>Let's Go Kaguyahime</x:v>
+      </x:c>
+      <x:c r="F83" s="12" t="str">
+        <x:v>Panam</x:v>
+      </x:c>
+      <x:c r="G83" s="12" t="str"/>
+      <x:c r="H83" s="12" t="str"/>
+      <x:c r="I83" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J83" s="12" t="str"/>
+      <x:c r="K83" s="12" t="str"/>
+      <x:c r="L83" s="12" t="str"/>
+      <x:c r="M83" s="12" t="str"/>
+      <x:c r="N83" s="12" t="str">
+        <x:v>IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="O83" s="12" t="str">
+        <x:v>82_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P83" s="12" t="str"/>
+      <x:c r="Q83" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="R83" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S83" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3245.jpg. </x:v>
+      </x:c>
+      <x:c r="T83" s="12" t="str"/>
+      <x:c r="U83" s="12" t="str"/>
+      <x:c r="V83" s="12" t="str"/>
+      <x:c r="W83" s="12" t="str"/>
+      <x:c r="X83" s="12" t="str"/>
+      <x:c r="Y83" s="12" t="str"/>
+      <x:c r="Z83" s="12" t="str"/>
+      <x:c r="AA83" s="12" t="str"/>
+      <x:c r="AB83" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC83" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD83" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE83" s="12" t="str">
+        <x:v>Collection note: Let's Go Kaguyahime by Kaguyahime, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF83" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3245.jpg</x:v>
+      </x:c>
+      <x:c r="AG83" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH83" s="12" t="str"/>
+      <x:c r="AI83" s="12" t="str"/>
+    </x:row>
+    <x:row r="84" ht="120" customHeight="1">
+      <x:c r="A84" s="12" t="str">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B84" s="12" t="str">
+        <x:v>渡辺真知子</x:v>
+      </x:c>
+      <x:c r="C84" s="12" t="str">
+        <x:v>Machiko Watanabe</x:v>
+      </x:c>
+      <x:c r="D84" s="12" t="str"/>
+      <x:c r="E84" s="12" t="str">
+        <x:v>Feel Free</x:v>
+      </x:c>
+      <x:c r="F84" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G84" s="12" t="str"/>
+      <x:c r="H84" s="12" t="str">
+        <x:v>1981</x:v>
+      </x:c>
+      <x:c r="I84" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J84" s="12" t="str"/>
+      <x:c r="K84" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L84" s="12" t="str"/>
+      <x:c r="M84" s="12" t="str"/>
+      <x:c r="N84" s="12" t="str">
+        <x:v>IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="O84" s="12" t="str">
+        <x:v>83_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P84" s="12" t="str"/>
+      <x:c r="Q84" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/feel-free/1537075926?uo=4</x:v>
+      </x:c>
+      <x:c r="R84" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S84" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3246.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="T84" s="12" t="str"/>
+      <x:c r="U84" s="12" t="str"/>
+      <x:c r="V84" s="12" t="str"/>
+      <x:c r="W84" s="12" t="str"/>
+      <x:c r="X84" s="12" t="str"/>
+      <x:c r="Y84" s="12" t="str"/>
+      <x:c r="Z84" s="12" t="str"/>
+      <x:c r="AA84" s="12" t="str"/>
+      <x:c r="AB84" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC84" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD84" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE84" s="12" t="str">
+        <x:v>Machiko Watanabe’s 1981 album includes Feel Free, Koi no Freeway and See Through.</x:v>
+      </x:c>
+      <x:c r="AF84" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AG84" s="12" t="str">
+        <x:v>FMPJ artist discography</x:v>
+      </x:c>
+      <x:c r="AH84" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AI84" s="12" t="str">
+        <x:v>Artist profile and discography</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="120" customHeight="1">
+      <x:c r="A85" s="12" t="str">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B85" s="12" t="str">
+        <x:v>渡辺真知子</x:v>
+      </x:c>
+      <x:c r="C85" s="12" t="str">
+        <x:v>Machiko Watanabe</x:v>
+      </x:c>
+      <x:c r="D85" s="12" t="str">
+        <x:v>フォグ・ランプ</x:v>
+      </x:c>
+      <x:c r="E85" s="12" t="str">
+        <x:v>Fog Lamp</x:v>
+      </x:c>
+      <x:c r="F85" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G85" s="12" t="str"/>
+      <x:c r="H85" s="12" t="str">
+        <x:v>1978</x:v>
+      </x:c>
+      <x:c r="I85" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J85" s="12" t="str"/>
+      <x:c r="K85" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L85" s="12" t="str"/>
+      <x:c r="M85" s="12" t="str">
+        <x:v>One of two separately owned physical copies, confirmed by the owner. Each copy has its own collection ID and reference photograph.</x:v>
+      </x:c>
+      <x:c r="N85" s="12" t="str">
+        <x:v>IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="O85" s="12" t="str">
+        <x:v>84_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P85" s="12" t="str"/>
+      <x:c r="Q85" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E3%83%95%E3%82%A9%E3%82%B0-%E3%83%A9%E3%83%B3%E3%83%97/1536768852?uo=4</x:v>
+      </x:c>
+      <x:c r="R85" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S85" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3246.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="T85" s="12" t="str"/>
+      <x:c r="U85" s="12" t="str"/>
+      <x:c r="V85" s="12" t="str"/>
+      <x:c r="W85" s="12" t="str"/>
+      <x:c r="X85" s="12" t="str"/>
+      <x:c r="Y85" s="12" t="str"/>
+      <x:c r="Z85" s="12" t="str"/>
+      <x:c r="AA85" s="12" t="str"/>
+      <x:c r="AB85" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC85" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD85" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE85" s="12" t="str">
+        <x:v>Released in November 1978, Fog Lamp includes Blue, Konya wa Odotte and its title track.</x:v>
+      </x:c>
+      <x:c r="AF85" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AG85" s="12" t="str">
+        <x:v>FMPJ artist discography</x:v>
+      </x:c>
+      <x:c r="AH85" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AI85" s="12" t="str">
+        <x:v>Artist profile and discography</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="120" customHeight="1">
+      <x:c r="A86" s="12" t="str">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B86" s="12" t="str">
+        <x:v>渡辺真知子</x:v>
+      </x:c>
+      <x:c r="C86" s="12" t="str">
+        <x:v>Machiko Watanabe</x:v>
+      </x:c>
+      <x:c r="D86" s="12" t="str">
+        <x:v>ライブラ</x:v>
+      </x:c>
+      <x:c r="E86" s="12" t="str">
+        <x:v>Libra</x:v>
+      </x:c>
+      <x:c r="F86" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G86" s="12" t="str"/>
+      <x:c r="H86" s="12" t="str">
+        <x:v>1980</x:v>
+      </x:c>
+      <x:c r="I86" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J86" s="12" t="str"/>
+      <x:c r="K86" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L86" s="12" t="str"/>
+      <x:c r="M86" s="12" t="str"/>
+      <x:c r="N86" s="12" t="str">
+        <x:v>IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="O86" s="12" t="str">
+        <x:v>85_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P86" s="12" t="str"/>
+      <x:c r="Q86" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/libra/1537075581?uo=4</x:v>
+      </x:c>
+      <x:c r="R86" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S86" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3246.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="T86" s="12" t="str"/>
+      <x:c r="U86" s="12" t="str"/>
+      <x:c r="V86" s="12" t="str"/>
+      <x:c r="W86" s="12" t="str"/>
+      <x:c r="X86" s="12" t="str"/>
+      <x:c r="Y86" s="12" t="str"/>
+      <x:c r="Z86" s="12" t="str"/>
+      <x:c r="AA86" s="12" t="str"/>
+      <x:c r="AB86" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC86" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD86" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE86" s="12" t="str">
+        <x:v>Libra was released in August 1980. Its ten songs include Kuchibiru yo, Atsuku Kimi o Katare and Hold Me Tight.</x:v>
+      </x:c>
+      <x:c r="AF86" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AG86" s="12" t="str">
+        <x:v>FMPJ artist discography</x:v>
+      </x:c>
+      <x:c r="AH86" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AI86" s="12" t="str">
+        <x:v>Artist profile and discography</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="120" customHeight="1">
+      <x:c r="A87" s="12" t="str">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B87" s="12" t="str">
+        <x:v>西城秀樹</x:v>
+      </x:c>
+      <x:c r="C87" s="12" t="str">
+        <x:v>Hideki Saijo</x:v>
+      </x:c>
+      <x:c r="D87" s="12" t="str"/>
+      <x:c r="E87" s="12" t="str">
+        <x:v>The Best</x:v>
+      </x:c>
+      <x:c r="F87" s="12" t="str">
+        <x:v>RCA</x:v>
+      </x:c>
+      <x:c r="G87" s="12" t="str"/>
+      <x:c r="H87" s="12" t="str"/>
+      <x:c r="I87" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J87" s="12" t="str"/>
+      <x:c r="K87" s="12" t="str"/>
+      <x:c r="L87" s="12" t="str"/>
+      <x:c r="M87" s="12" t="str"/>
+      <x:c r="N87" s="12" t="str">
+        <x:v>IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="O87" s="12" t="str">
+        <x:v>86_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P87" s="12" t="str"/>
+      <x:c r="Q87" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="R87" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S87" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3246.jpg. </x:v>
+      </x:c>
+      <x:c r="T87" s="12" t="str"/>
+      <x:c r="U87" s="12" t="str"/>
+      <x:c r="V87" s="12" t="str"/>
+      <x:c r="W87" s="12" t="str"/>
+      <x:c r="X87" s="12" t="str"/>
+      <x:c r="Y87" s="12" t="str"/>
+      <x:c r="Z87" s="12" t="str"/>
+      <x:c r="AA87" s="12" t="str"/>
+      <x:c r="AB87" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC87" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD87" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE87" s="12" t="str">
+        <x:v>Collection note: The Best by Hideki Saijo, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF87" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="AG87" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH87" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E8%A5%BF%E5%9F%8E%E7%A7%80%E6%A8%B9/76038174?uo=4</x:v>
+      </x:c>
+      <x:c r="AI87" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="120" customHeight="1">
+      <x:c r="A88" s="12" t="str">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B88" s="12" t="str">
+        <x:v>キャンディーズ</x:v>
+      </x:c>
+      <x:c r="C88" s="12" t="str">
+        <x:v>Candies</x:v>
+      </x:c>
+      <x:c r="D88" s="12" t="str">
+        <x:v>キャンディーズのすべて</x:v>
+      </x:c>
+      <x:c r="E88" s="12" t="str">
+        <x:v>Candies no Subete</x:v>
+      </x:c>
+      <x:c r="F88" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G88" s="12" t="str"/>
+      <x:c r="H88" s="12" t="str"/>
+      <x:c r="I88" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J88" s="12" t="str"/>
+      <x:c r="K88" s="12" t="str"/>
+      <x:c r="L88" s="12" t="str"/>
+      <x:c r="M88" s="12" t="str"/>
+      <x:c r="N88" s="12" t="str">
+        <x:v>IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="O88" s="12" t="str">
+        <x:v>87_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P88" s="12" t="str"/>
+      <x:c r="Q88" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="R88" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S88" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3246.jpg. </x:v>
+      </x:c>
+      <x:c r="T88" s="12" t="str"/>
+      <x:c r="U88" s="12" t="str"/>
+      <x:c r="V88" s="12" t="str"/>
+      <x:c r="W88" s="12" t="str"/>
+      <x:c r="X88" s="12" t="str"/>
+      <x:c r="Y88" s="12" t="str"/>
+      <x:c r="Z88" s="12" t="str"/>
+      <x:c r="AA88" s="12" t="str"/>
+      <x:c r="AB88" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC88" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD88" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE88" s="12" t="str">
+        <x:v>Collection note: Candies compilation titled Candies no Subete. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF88" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="AG88" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH88" s="12" t="str"/>
+      <x:c r="AI88" s="12" t="str"/>
+    </x:row>
+    <x:row r="89" ht="120" customHeight="1">
+      <x:c r="A89" s="12" t="str">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B89" s="12" t="str">
+        <x:v>太田裕美</x:v>
+      </x:c>
+      <x:c r="C89" s="12" t="str">
+        <x:v>Hiromi Ota</x:v>
+      </x:c>
+      <x:c r="D89" s="12" t="str">
+        <x:v>太田裕美のすべて</x:v>
+      </x:c>
+      <x:c r="E89" s="12" t="str">
+        <x:v>Hiromi Ota no Subete</x:v>
+      </x:c>
+      <x:c r="F89" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G89" s="12" t="str"/>
+      <x:c r="H89" s="12" t="str"/>
+      <x:c r="I89" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J89" s="12" t="str"/>
+      <x:c r="K89" s="12" t="str"/>
+      <x:c r="L89" s="12" t="str"/>
+      <x:c r="M89" s="12" t="str"/>
+      <x:c r="N89" s="12" t="str">
+        <x:v>IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="O89" s="12" t="str">
+        <x:v>88_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P89" s="12" t="str"/>
+      <x:c r="Q89" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="R89" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S89" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3246.jpg. </x:v>
+      </x:c>
+      <x:c r="T89" s="12" t="str"/>
+      <x:c r="U89" s="12" t="str"/>
+      <x:c r="V89" s="12" t="str"/>
+      <x:c r="W89" s="12" t="str"/>
+      <x:c r="X89" s="12" t="str"/>
+      <x:c r="Y89" s="12" t="str"/>
+      <x:c r="Z89" s="12" t="str"/>
+      <x:c r="AA89" s="12" t="str"/>
+      <x:c r="AB89" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC89" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD89" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE89" s="12" t="str">
+        <x:v>Collection note: Hiromi Ota compilation titled Hiromi Ota no Subete. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF89" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="AG89" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH89" s="12" t="str"/>
+      <x:c r="AI89" s="12" t="str"/>
+    </x:row>
+    <x:row r="90" ht="120" customHeight="1">
+      <x:c r="A90" s="12" t="str">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B90" s="12" t="str">
+        <x:v>荒井由実</x:v>
+      </x:c>
+      <x:c r="C90" s="12" t="str">
+        <x:v>Yumi Arai</x:v>
+      </x:c>
+      <x:c r="D90" s="12" t="str">
+        <x:v>14番目の月</x:v>
+      </x:c>
+      <x:c r="E90" s="12" t="str">
+        <x:v>The 14th Moon</x:v>
+      </x:c>
+      <x:c r="F90" s="12" t="str">
+        <x:v>Express</x:v>
+      </x:c>
+      <x:c r="G90" s="12" t="str"/>
+      <x:c r="H90" s="12" t="str">
+        <x:v>1976</x:v>
+      </x:c>
+      <x:c r="I90" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J90" s="12" t="str"/>
+      <x:c r="K90" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L90" s="12" t="str"/>
+      <x:c r="M90" s="12" t="str"/>
+      <x:c r="N90" s="12" t="str">
+        <x:v>IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="O90" s="12" t="str">
+        <x:v>89_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P90" s="12" t="str"/>
+      <x:c r="Q90" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/the-14th-moon-jyuyon-banme-no-tsuki/1436012327?uo=4</x:v>
+      </x:c>
+      <x:c r="R90" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S90" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3246.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T90" s="12" t="str"/>
+      <x:c r="U90" s="12" t="str"/>
+      <x:c r="V90" s="12" t="str"/>
+      <x:c r="W90" s="12" t="str"/>
+      <x:c r="X90" s="12" t="str"/>
+      <x:c r="Y90" s="12" t="str"/>
+      <x:c r="Z90" s="12" t="str"/>
+      <x:c r="AA90" s="12" t="str"/>
+      <x:c r="AB90" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC90" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD90" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE90" s="12" t="str">
+        <x:v>Collection note: The 14th Moon by Yumi Arai, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF90" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="AG90" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH90" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E8%8D%92%E4%BA%95%E7%94%B1%E5%AE%9F/81316604?uo=4</x:v>
+      </x:c>
+      <x:c r="AI90" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="120" customHeight="1">
+      <x:c r="A91" s="12" t="str">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B91" s="12" t="str">
+        <x:v>ピンク・レディー</x:v>
+      </x:c>
+      <x:c r="C91" s="12" t="str">
+        <x:v>Pink Lady</x:v>
+      </x:c>
+      <x:c r="D91" s="12" t="str">
+        <x:v>ベスト・ヒット・アルバム</x:v>
+      </x:c>
+      <x:c r="E91" s="12" t="str">
+        <x:v>Best Hit Album</x:v>
+      </x:c>
+      <x:c r="F91" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G91" s="12" t="str"/>
+      <x:c r="H91" s="12" t="str">
+        <x:v>1977</x:v>
+      </x:c>
+      <x:c r="I91" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J91" s="12" t="str"/>
+      <x:c r="K91" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L91" s="12" t="str"/>
+      <x:c r="M91" s="12" t="str"/>
+      <x:c r="N91" s="12" t="str">
+        <x:v>IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="O91" s="12" t="str">
+        <x:v>90_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P91" s="12" t="str"/>
+      <x:c r="Q91" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/best-hits-album/1635931425?uo=4</x:v>
+      </x:c>
+      <x:c r="R91" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S91" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3246.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T91" s="12" t="str"/>
+      <x:c r="U91" s="12" t="str"/>
+      <x:c r="V91" s="12" t="str"/>
+      <x:c r="W91" s="12" t="str"/>
+      <x:c r="X91" s="12" t="str"/>
+      <x:c r="Y91" s="12" t="str"/>
+      <x:c r="Z91" s="12" t="str"/>
+      <x:c r="AA91" s="12" t="str"/>
+      <x:c r="AB91" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC91" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD91" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE91" s="12" t="str">
+        <x:v>Collection note: Pink Lady compilation titled Best Hit Album. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF91" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="AG91" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH91" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E3%83%94%E3%83%B3%E3%82%AF-%E3%83%AC%E3%83%87%E3%82%A3%E3%83%BC/207003566?uo=4</x:v>
+      </x:c>
+      <x:c r="AI91" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="120" customHeight="1">
+      <x:c r="A92" s="12" t="str">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B92" s="12" t="str">
+        <x:v>渡辺真知子</x:v>
+      </x:c>
+      <x:c r="C92" s="12" t="str">
+        <x:v>Machiko Watanabe</x:v>
+      </x:c>
+      <x:c r="D92" s="12" t="str">
+        <x:v>メモリーズ</x:v>
+      </x:c>
+      <x:c r="E92" s="12" t="str">
+        <x:v>Memories</x:v>
+      </x:c>
+      <x:c r="F92" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G92" s="12" t="str"/>
+      <x:c r="H92" s="12" t="str">
+        <x:v>1979</x:v>
+      </x:c>
+      <x:c r="I92" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J92" s="12" t="str"/>
+      <x:c r="K92" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L92" s="12" t="str"/>
+      <x:c r="M92" s="12" t="str"/>
+      <x:c r="N92" s="12" t="str">
+        <x:v>IMG_3246.jpg</x:v>
+      </x:c>
+      <x:c r="O92" s="12" t="str">
+        <x:v>91_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P92" s="12" t="str"/>
+      <x:c r="Q92" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E3%83%A1%E3%83%A2%E3%83%AA%E3%83%BC%E3%82%BA/1536776760?uo=4</x:v>
+      </x:c>
+      <x:c r="R92" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S92" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3246.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="T92" s="12" t="str"/>
+      <x:c r="U92" s="12" t="str"/>
+      <x:c r="V92" s="12" t="str"/>
+      <x:c r="W92" s="12" t="str"/>
+      <x:c r="X92" s="12" t="str"/>
+      <x:c r="Y92" s="12" t="str"/>
+      <x:c r="Z92" s="12" t="str"/>
+      <x:c r="AA92" s="12" t="str"/>
+      <x:c r="AB92" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC92" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD92" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE92" s="12" t="str">
+        <x:v>Memories was released in December 1979 and includes Water Taxi, Marionette and Ashita e alongside the title song.</x:v>
+      </x:c>
+      <x:c r="AF92" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AG92" s="12" t="str">
+        <x:v>FMPJ artist discography</x:v>
+      </x:c>
+      <x:c r="AH92" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AI92" s="12" t="str">
+        <x:v>Artist profile and discography</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="120" customHeight="1">
+      <x:c r="A93" s="12" t="str">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B93" s="12" t="str">
+        <x:v>石野真子</x:v>
+      </x:c>
+      <x:c r="C93" s="12" t="str">
+        <x:v>Mako Ishino</x:v>
+      </x:c>
+      <x:c r="D93" s="12" t="str">
+        <x:v>ベスト・ヒット・アルバム</x:v>
+      </x:c>
+      <x:c r="E93" s="12" t="str">
+        <x:v>Best Hit Album</x:v>
+      </x:c>
+      <x:c r="F93" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G93" s="12" t="str">
+        <x:v>GX-45</x:v>
+      </x:c>
+      <x:c r="H93" s="12" t="str">
+        <x:v>1979</x:v>
+      </x:c>
+      <x:c r="I93" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J93" s="12" t="str"/>
+      <x:c r="K93" s="12" t="str"/>
+      <x:c r="L93" s="12" t="str"/>
+      <x:c r="M93" s="12" t="str"/>
+      <x:c r="N93" s="12" t="str">
+        <x:v>IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="O93" s="12" t="str">
+        <x:v>92_retailer_front.jpg</x:v>
+      </x:c>
+      <x:c r="P93" s="12" t="str"/>
+      <x:c r="Q93" s="12" t="str">
+        <x:v>https://ticro.com/en/products/i00001481</x:v>
+      </x:c>
+      <x:c r="R93" s="12" t="str">
+        <x:v>retailer</x:v>
+      </x:c>
+      <x:c r="S93" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3247.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Metadata source: https://ticro.com/en/products/i00001481</x:v>
+      </x:c>
+      <x:c r="T93" s="12" t="str"/>
+      <x:c r="U93" s="12" t="str"/>
+      <x:c r="V93" s="12" t="str"/>
+      <x:c r="W93" s="12" t="str"/>
+      <x:c r="X93" s="12" t="str"/>
+      <x:c r="Y93" s="12" t="str"/>
+      <x:c r="Z93" s="12" t="str"/>
+      <x:c r="AA93" s="12" t="str"/>
+      <x:c r="AB93" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC93" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD93" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE93" s="12" t="str">
+        <x:v>A fourteen-song Mako Ishino compilation including Nichiyobi wa Stranger and Okami Nanka Kowakunai. Victor issued this Best Hit Album in 1979.</x:v>
+      </x:c>
+      <x:c r="AF93" s="12" t="str">
+        <x:v>https://ticro.com/en/products/i00001481</x:v>
+      </x:c>
+      <x:c r="AG93" s="12" t="str">
+        <x:v>Ticro Market release listing</x:v>
+      </x:c>
+      <x:c r="AH93" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E7%9F%B3%E9%87%8E%E7%9C%9F%E5%AD%90/278910774?uo=4</x:v>
+      </x:c>
+      <x:c r="AI93" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="120" customHeight="1">
+      <x:c r="A94" s="12" t="str">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B94" s="12" t="str">
+        <x:v>浅田美代子</x:v>
+      </x:c>
+      <x:c r="C94" s="12" t="str">
+        <x:v>Miyoko Asada</x:v>
+      </x:c>
+      <x:c r="D94" s="12" t="str"/>
+      <x:c r="E94" s="12" t="str">
+        <x:v>The Best</x:v>
+      </x:c>
+      <x:c r="F94" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G94" s="12" t="str"/>
+      <x:c r="H94" s="12" t="str"/>
+      <x:c r="I94" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J94" s="12" t="str"/>
+      <x:c r="K94" s="12" t="str"/>
+      <x:c r="L94" s="12" t="str"/>
+      <x:c r="M94" s="12" t="str"/>
+      <x:c r="N94" s="12" t="str">
+        <x:v>IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="O94" s="12" t="str">
+        <x:v>93_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P94" s="12" t="str"/>
+      <x:c r="Q94" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="R94" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S94" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3247.jpg. </x:v>
+      </x:c>
+      <x:c r="T94" s="12" t="str"/>
+      <x:c r="U94" s="12" t="str"/>
+      <x:c r="V94" s="12" t="str"/>
+      <x:c r="W94" s="12" t="str"/>
+      <x:c r="X94" s="12" t="str"/>
+      <x:c r="Y94" s="12" t="str"/>
+      <x:c r="Z94" s="12" t="str"/>
+      <x:c r="AA94" s="12" t="str"/>
+      <x:c r="AB94" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC94" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD94" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE94" s="12" t="str">
+        <x:v>Collection note: Miyoko Asada compilation titled The Best. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF94" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="AG94" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH94" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E6%B5%85%E7%94%B0-%E7%BE%8E%E4%BB%A3%E5%AD%90/1156806444?uo=4</x:v>
+      </x:c>
+      <x:c r="AI94" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="120" customHeight="1">
+      <x:c r="A95" s="12" t="str">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B95" s="12" t="str">
+        <x:v>渡辺真知子</x:v>
+      </x:c>
+      <x:c r="C95" s="12" t="str">
+        <x:v>Machiko Watanabe</x:v>
+      </x:c>
+      <x:c r="D95" s="12" t="str">
+        <x:v>唇よ、熱く君を語れ</x:v>
+      </x:c>
+      <x:c r="E95" s="12" t="str">
+        <x:v>The Best: Kuchibiru yo, Atsuku Kimi o Katare</x:v>
+      </x:c>
+      <x:c r="F95" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G95" s="12" t="str"/>
+      <x:c r="H95" s="12" t="str"/>
+      <x:c r="I95" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J95" s="12" t="str"/>
+      <x:c r="K95" s="12" t="str"/>
+      <x:c r="L95" s="12" t="str"/>
+      <x:c r="M95" s="12" t="str"/>
+      <x:c r="N95" s="12" t="str">
+        <x:v>IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="O95" s="12" t="str">
+        <x:v>94_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P95" s="12" t="str"/>
+      <x:c r="Q95" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="R95" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S95" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3247.jpg. </x:v>
+      </x:c>
+      <x:c r="T95" s="12" t="str"/>
+      <x:c r="U95" s="12" t="str"/>
+      <x:c r="V95" s="12" t="str"/>
+      <x:c r="W95" s="12" t="str"/>
+      <x:c r="X95" s="12" t="str"/>
+      <x:c r="Y95" s="12" t="str"/>
+      <x:c r="Z95" s="12" t="str"/>
+      <x:c r="AA95" s="12" t="str"/>
+      <x:c r="AB95" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC95" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD95" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE95" s="12" t="str">
+        <x:v>Collection note: Machiko Watanabe compilation titled The Best: Kuchibiru yo, Atsuku Kimi o Katare. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF95" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="AG95" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH95" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AI95" s="12" t="str">
+        <x:v>Artist profile and discography</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="120" customHeight="1">
+      <x:c r="A96" s="12" t="str">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B96" s="12" t="str">
+        <x:v>渡辺真知子</x:v>
+      </x:c>
+      <x:c r="C96" s="12" t="str">
+        <x:v>Machiko Watanabe</x:v>
+      </x:c>
+      <x:c r="D96" s="12" t="str"/>
+      <x:c r="E96" s="12" t="str">
+        <x:v>Welcome to Yokosuka: Into My Heart</x:v>
+      </x:c>
+      <x:c r="F96" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G96" s="12" t="str"/>
+      <x:c r="H96" s="12" t="str">
+        <x:v>1983</x:v>
+      </x:c>
+      <x:c r="I96" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J96" s="12" t="str"/>
+      <x:c r="K96" s="12" t="str"/>
+      <x:c r="L96" s="12" t="str"/>
+      <x:c r="M96" s="12" t="str"/>
+      <x:c r="N96" s="12" t="str">
+        <x:v>IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="O96" s="12" t="str">
+        <x:v>95_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P96" s="12" t="str"/>
+      <x:c r="Q96" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/welcome-to-yokosuka-into-my-heart/1537076631?uo=4</x:v>
+      </x:c>
+      <x:c r="R96" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S96" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3247.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Metadata source: https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="T96" s="12" t="str"/>
+      <x:c r="U96" s="12" t="str"/>
+      <x:c r="V96" s="12" t="str"/>
+      <x:c r="W96" s="12" t="str"/>
+      <x:c r="X96" s="12" t="str"/>
+      <x:c r="Y96" s="12" t="str"/>
+      <x:c r="Z96" s="12" t="str"/>
+      <x:c r="AA96" s="12" t="str"/>
+      <x:c r="AB96" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC96" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD96" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE96" s="12" t="str">
+        <x:v>Released in January 1983, Welcome to Yokosuka includes Honky Tonk Memory, Chukagai de Kanpai and Sailing Night.</x:v>
+      </x:c>
+      <x:c r="AF96" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AG96" s="12" t="str">
+        <x:v>FMPJ artist discography</x:v>
+      </x:c>
+      <x:c r="AH96" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AI96" s="12" t="str">
+        <x:v>Artist profile and discography</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="120" customHeight="1">
+      <x:c r="A97" s="12" t="str">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B97" s="12" t="str">
+        <x:v>渡辺真知子</x:v>
+      </x:c>
+      <x:c r="C97" s="12" t="str">
+        <x:v>Machiko Watanabe</x:v>
+      </x:c>
+      <x:c r="D97" s="12" t="str">
+        <x:v>海につれていって</x:v>
+      </x:c>
+      <x:c r="E97" s="12" t="str">
+        <x:v>Umi ni Tsurete Itte</x:v>
+      </x:c>
+      <x:c r="F97" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G97" s="12" t="str"/>
+      <x:c r="H97" s="12" t="str">
+        <x:v>1978</x:v>
+      </x:c>
+      <x:c r="I97" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J97" s="12" t="str"/>
+      <x:c r="K97" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L97" s="12" t="str"/>
+      <x:c r="M97" s="12" t="str">
+        <x:v>One of two separately owned physical copies, confirmed by the owner. Each copy has its own collection ID and reference photograph.</x:v>
+      </x:c>
+      <x:c r="N97" s="12" t="str">
+        <x:v>IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="O97" s="12" t="str">
+        <x:v>96_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P97" s="12" t="str"/>
+      <x:c r="Q97" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E6%B5%B7%E3%81%AB%E3%81%A4%E3%82%8C%E3%81%A6%E3%81%84%E3%81%A3%E3%81%A6/1536768424?uo=4</x:v>
+      </x:c>
+      <x:c r="R97" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S97" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3247.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="T97" s="12" t="str"/>
+      <x:c r="U97" s="12" t="str"/>
+      <x:c r="V97" s="12" t="str"/>
+      <x:c r="W97" s="12" t="str"/>
+      <x:c r="X97" s="12" t="str"/>
+      <x:c r="Y97" s="12" t="str"/>
+      <x:c r="Z97" s="12" t="str"/>
+      <x:c r="AA97" s="12" t="str"/>
+      <x:c r="AB97" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC97" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD97" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE97" s="12" t="str">
+        <x:v>Machiko Watanabe’s May 1978 album includes her early hits Mayoi Michi and Kamome ga Tonda Hi.</x:v>
+      </x:c>
+      <x:c r="AF97" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AG97" s="12" t="str">
+        <x:v>FMPJ artist discography</x:v>
+      </x:c>
+      <x:c r="AH97" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AI97" s="12" t="str">
+        <x:v>Artist profile and discography</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="120" customHeight="1">
+      <x:c r="A98" s="12" t="str">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B98" s="12" t="str">
+        <x:v>石川秀美</x:v>
+      </x:c>
+      <x:c r="C98" s="12" t="str">
+        <x:v>Hidemi Ishikawa</x:v>
+      </x:c>
+      <x:c r="D98" s="12" t="str">
+        <x:v>ペパーミント</x:v>
+      </x:c>
+      <x:c r="E98" s="12" t="str">
+        <x:v>Peppermint</x:v>
+      </x:c>
+      <x:c r="F98" s="12" t="str">
+        <x:v>RVC</x:v>
+      </x:c>
+      <x:c r="G98" s="12" t="str"/>
+      <x:c r="H98" s="12" t="str"/>
+      <x:c r="I98" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J98" s="12" t="str"/>
+      <x:c r="K98" s="12" t="str"/>
+      <x:c r="L98" s="12" t="str"/>
+      <x:c r="M98" s="12" t="str"/>
+      <x:c r="N98" s="12" t="str">
+        <x:v>IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="O98" s="12" t="str">
+        <x:v>97_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P98" s="12" t="str"/>
+      <x:c r="Q98" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="R98" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S98" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3247.jpg. </x:v>
+      </x:c>
+      <x:c r="T98" s="12" t="str"/>
+      <x:c r="U98" s="12" t="str"/>
+      <x:c r="V98" s="12" t="str"/>
+      <x:c r="W98" s="12" t="str"/>
+      <x:c r="X98" s="12" t="str"/>
+      <x:c r="Y98" s="12" t="str"/>
+      <x:c r="Z98" s="12" t="str"/>
+      <x:c r="AA98" s="12" t="str"/>
+      <x:c r="AB98" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC98" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD98" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE98" s="12" t="str">
+        <x:v>Collection note: Peppermint by Hidemi Ishikawa, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF98" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="AG98" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH98" s="12" t="str"/>
+      <x:c r="AI98" s="12" t="str"/>
+    </x:row>
+    <x:row r="99" ht="120" customHeight="1">
+      <x:c r="A99" s="12" t="str">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B99" s="12" t="str">
+        <x:v>渡辺真知子</x:v>
+      </x:c>
+      <x:c r="C99" s="12" t="str">
+        <x:v>Machiko Watanabe</x:v>
+      </x:c>
+      <x:c r="D99" s="12" t="str">
+        <x:v>遠く離れて</x:v>
+      </x:c>
+      <x:c r="E99" s="12" t="str">
+        <x:v>Tooku Hanarete</x:v>
+      </x:c>
+      <x:c r="F99" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G99" s="12" t="str"/>
+      <x:c r="H99" s="12" t="str">
+        <x:v>1979</x:v>
+      </x:c>
+      <x:c r="I99" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J99" s="12" t="str"/>
+      <x:c r="K99" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L99" s="12" t="str"/>
+      <x:c r="M99" s="12" t="str"/>
+      <x:c r="N99" s="12" t="str">
+        <x:v>IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="O99" s="12" t="str">
+        <x:v>98_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P99" s="12" t="str"/>
+      <x:c r="Q99" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E9%81%A0%E3%81%8F%E9%9B%A2%E3%82%8C%E3%81%A6/1536776658?uo=4</x:v>
+      </x:c>
+      <x:c r="R99" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S99" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3247.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="T99" s="12" t="str"/>
+      <x:c r="U99" s="12" t="str"/>
+      <x:c r="V99" s="12" t="str"/>
+      <x:c r="W99" s="12" t="str"/>
+      <x:c r="X99" s="12" t="str"/>
+      <x:c r="Y99" s="12" t="str"/>
+      <x:c r="Z99" s="12" t="str"/>
+      <x:c r="AA99" s="12" t="str"/>
+      <x:c r="AB99" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC99" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD99" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE99" s="12" t="str">
+        <x:v>Released in June 1979, Tooku Hanarete includes Uminari, Kuko and Wine to Anata to.</x:v>
+      </x:c>
+      <x:c r="AF99" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AG99" s="12" t="str">
+        <x:v>FMPJ artist discography</x:v>
+      </x:c>
+      <x:c r="AH99" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AI99" s="12" t="str">
+        <x:v>Artist profile and discography</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="120" customHeight="1">
+      <x:c r="A100" s="12" t="str">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B100" s="12" t="str">
+        <x:v>石川セリ</x:v>
+      </x:c>
+      <x:c r="C100" s="12" t="str">
+        <x:v>Seri Ishikawa</x:v>
+      </x:c>
+      <x:c r="D100" s="12" t="str">
+        <x:v>ときどき私は…</x:v>
+      </x:c>
+      <x:c r="E100" s="12" t="str">
+        <x:v>Tokidoki Watashi wa…</x:v>
+      </x:c>
+      <x:c r="F100" s="12" t="str">
+        <x:v>Philips</x:v>
+      </x:c>
+      <x:c r="G100" s="12" t="str">
+        <x:v>FX-6047</x:v>
+      </x:c>
+      <x:c r="H100" s="12" t="str">
+        <x:v>1976</x:v>
+      </x:c>
+      <x:c r="I100" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J100" s="12" t="str"/>
+      <x:c r="K100" s="12" t="str"/>
+      <x:c r="L100" s="12" t="str"/>
+      <x:c r="M100" s="12" t="str"/>
+      <x:c r="N100" s="12" t="str">
+        <x:v>IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="O100" s="12" t="str">
+        <x:v>99_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P100" s="12" t="str"/>
+      <x:c r="Q100" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="R100" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S100" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3247.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Metadata source: https://www.universal-music.co.jp/ishikawa-seri/discography/cat/album/page/2/</x:v>
+      </x:c>
+      <x:c r="T100" s="12" t="str"/>
+      <x:c r="U100" s="12" t="str"/>
+      <x:c r="V100" s="12" t="str"/>
+      <x:c r="W100" s="12" t="str"/>
+      <x:c r="X100" s="12" t="str"/>
+      <x:c r="Y100" s="12" t="str"/>
+      <x:c r="Z100" s="12" t="str"/>
+      <x:c r="AA100" s="12" t="str"/>
+      <x:c r="AB100" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC100" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD100" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE100" s="12" t="str">
+        <x:v>Seri Ishikawa’s Tokidoki Watashi wa… was originally released in January 1976. The photographed Philips LP is FX-6047.</x:v>
+      </x:c>
+      <x:c r="AF100" s="12" t="str">
+        <x:v>https://www.universal-music.co.jp/ishikawa-seri/discography/cat/album/page/2/</x:v>
+      </x:c>
+      <x:c r="AG100" s="12" t="str">
+        <x:v>Universal Music discography</x:v>
+      </x:c>
+      <x:c r="AH100" s="12" t="str"/>
+      <x:c r="AI100" s="12" t="str"/>
+    </x:row>
+    <x:row r="101" ht="120" customHeight="1">
+      <x:c r="A101" s="12" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B101" s="12" t="str">
+        <x:v>TUBE</x:v>
+      </x:c>
+      <x:c r="C101" s="12" t="str">
+        <x:v>TUBE</x:v>
+      </x:c>
+      <x:c r="D101" s="12" t="str"/>
+      <x:c r="E101" s="12" t="str">
+        <x:v>The Season in the Sun</x:v>
+      </x:c>
+      <x:c r="F101" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G101" s="12" t="str"/>
+      <x:c r="H101" s="12" t="str">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="I101" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J101" s="12" t="str"/>
+      <x:c r="K101" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L101" s="12" t="str"/>
+      <x:c r="M101" s="12" t="str"/>
+      <x:c r="N101" s="12" t="str">
+        <x:v>IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="O101" s="12" t="str">
+        <x:v>100_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P101" s="12" t="str"/>
+      <x:c r="Q101" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/the-season-in-the-sun/1535481258?uo=4</x:v>
+      </x:c>
+      <x:c r="R101" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S101" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3247.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T101" s="12" t="str"/>
+      <x:c r="U101" s="12" t="str"/>
+      <x:c r="V101" s="12" t="str"/>
+      <x:c r="W101" s="12" t="str"/>
+      <x:c r="X101" s="12" t="str"/>
+      <x:c r="Y101" s="12" t="str"/>
+      <x:c r="Z101" s="12" t="str"/>
+      <x:c r="AA101" s="12" t="str"/>
+      <x:c r="AB101" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC101" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD101" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE101" s="12" t="str">
+        <x:v>Collection note: The Season in the Sun by TUBE, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF101" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3247.jpg</x:v>
+      </x:c>
+      <x:c r="AG101" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH101" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/tube/572380409?uo=4</x:v>
+      </x:c>
+      <x:c r="AI101" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="120" customHeight="1">
+      <x:c r="A102" s="12" t="str">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B102" s="12" t="str">
+        <x:v>杉山清貴＆オメガトライブ</x:v>
+      </x:c>
+      <x:c r="C102" s="12" t="str">
+        <x:v>S. Kiyotaka &amp; Omega Tribe</x:v>
+      </x:c>
+      <x:c r="D102" s="12" t="str"/>
+      <x:c r="E102" s="12" t="str">
+        <x:v>First Finale</x:v>
+      </x:c>
+      <x:c r="F102" s="12" t="str">
+        <x:v>Vap</x:v>
+      </x:c>
+      <x:c r="G102" s="12" t="str"/>
+      <x:c r="H102" s="12" t="str">
+        <x:v>1985</x:v>
+      </x:c>
+      <x:c r="I102" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J102" s="12" t="str"/>
+      <x:c r="K102" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L102" s="12" t="str"/>
+      <x:c r="M102" s="12" t="str"/>
+      <x:c r="N102" s="12" t="str">
+        <x:v>IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="O102" s="12" t="str">
+        <x:v>101_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P102" s="12" t="str"/>
+      <x:c r="Q102" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/first-finale/678093493?uo=4</x:v>
+      </x:c>
+      <x:c r="R102" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S102" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3248.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T102" s="12" t="str"/>
+      <x:c r="U102" s="12" t="str"/>
+      <x:c r="V102" s="12" t="str"/>
+      <x:c r="W102" s="12" t="str"/>
+      <x:c r="X102" s="12" t="str"/>
+      <x:c r="Y102" s="12" t="str"/>
+      <x:c r="Z102" s="12" t="str"/>
+      <x:c r="AA102" s="12" t="str"/>
+      <x:c r="AB102" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC102" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD102" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE102" s="12" t="str">
+        <x:v>Collection note: First Finale by S. Kiyotaka &amp; Omega Tribe, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF102" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="AG102" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH102" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E6%9D%89%E5%B1%B1%E6%B8%85%E8%B2%B4-%E3%82%AA%E3%83%A1%E3%82%AC%E3%83%88%E3%83%A9%E3%82%A4%E3%83%96/1611738774?uo=4</x:v>
+      </x:c>
+      <x:c r="AI102" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="120" customHeight="1">
+      <x:c r="A103" s="12" t="str">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B103" s="12" t="str">
+        <x:v>荒井由実</x:v>
+      </x:c>
+      <x:c r="C103" s="12" t="str">
+        <x:v>Yumi Arai</x:v>
+      </x:c>
+      <x:c r="D103" s="12" t="str">
+        <x:v>コバルト・アワー</x:v>
+      </x:c>
+      <x:c r="E103" s="12" t="str">
+        <x:v>Cobalt Hour</x:v>
+      </x:c>
+      <x:c r="F103" s="12" t="str">
+        <x:v>Express</x:v>
+      </x:c>
+      <x:c r="G103" s="12" t="str"/>
+      <x:c r="H103" s="12" t="str">
+        <x:v>1975</x:v>
+      </x:c>
+      <x:c r="I103" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J103" s="12" t="str"/>
+      <x:c r="K103" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L103" s="12" t="str"/>
+      <x:c r="M103" s="12" t="str">
+        <x:v>One of two separately owned physical copies, confirmed by the owner. Each copy has its own collection ID and reference photograph.</x:v>
+      </x:c>
+      <x:c r="N103" s="12" t="str">
+        <x:v>IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="O103" s="12" t="str">
+        <x:v>102_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P103" s="12" t="str"/>
+      <x:c r="Q103" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/cobalt-hour/1436010473?uo=4</x:v>
+      </x:c>
+      <x:c r="R103" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S103" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3248.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T103" s="12" t="str"/>
+      <x:c r="U103" s="12" t="str"/>
+      <x:c r="V103" s="12" t="str"/>
+      <x:c r="W103" s="12" t="str"/>
+      <x:c r="X103" s="12" t="str"/>
+      <x:c r="Y103" s="12" t="str"/>
+      <x:c r="Z103" s="12" t="str"/>
+      <x:c r="AA103" s="12" t="str"/>
+      <x:c r="AB103" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC103" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD103" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE103" s="12" t="str">
+        <x:v>Collection note: Cobalt Hour by Yumi Arai, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF103" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="AG103" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH103" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E8%8D%92%E4%BA%95%E7%94%B1%E5%AE%9F/81316604?uo=4</x:v>
+      </x:c>
+      <x:c r="AI103" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="120" customHeight="1">
+      <x:c r="A104" s="12" t="str">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B104" s="12" t="str">
+        <x:v>松任谷由実</x:v>
+      </x:c>
+      <x:c r="C104" s="12" t="str">
+        <x:v>Yumi Matsutoya</x:v>
+      </x:c>
+      <x:c r="D104" s="12" t="str">
+        <x:v>紅雀</x:v>
+      </x:c>
+      <x:c r="E104" s="12" t="str">
+        <x:v>Benisuzume</x:v>
+      </x:c>
+      <x:c r="F104" s="12" t="str">
+        <x:v>Express</x:v>
+      </x:c>
+      <x:c r="G104" s="12" t="str"/>
+      <x:c r="H104" s="12" t="str">
+        <x:v>1978</x:v>
+      </x:c>
+      <x:c r="I104" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J104" s="12" t="str"/>
+      <x:c r="K104" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L104" s="12" t="str"/>
+      <x:c r="M104" s="12" t="str"/>
+      <x:c r="N104" s="12" t="str">
+        <x:v>IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="O104" s="12" t="str">
+        <x:v>103_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P104" s="12" t="str"/>
+      <x:c r="Q104" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/linnet-beni-suzume/1436012400?uo=4</x:v>
+      </x:c>
+      <x:c r="R104" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S104" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3248.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T104" s="12" t="str"/>
+      <x:c r="U104" s="12" t="str"/>
+      <x:c r="V104" s="12" t="str"/>
+      <x:c r="W104" s="12" t="str"/>
+      <x:c r="X104" s="12" t="str"/>
+      <x:c r="Y104" s="12" t="str"/>
+      <x:c r="Z104" s="12" t="str"/>
+      <x:c r="AA104" s="12" t="str"/>
+      <x:c r="AB104" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC104" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD104" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE104" s="12" t="str">
+        <x:v>Collection note: Benisuzume by Yumi Matsutoya, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF104" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="AG104" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH104" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E6%9D%BE%E4%BB%BB%E8%B0%B7%E7%94%B1%E5%AE%9F/76458419?uo=4</x:v>
+      </x:c>
+      <x:c r="AI104" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="120" customHeight="1">
+      <x:c r="A105" s="12" t="str">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B105" s="12" t="str">
+        <x:v>堀ちえみ</x:v>
+      </x:c>
+      <x:c r="C105" s="12" t="str">
+        <x:v>Chiemi Hori</x:v>
+      </x:c>
+      <x:c r="D105" s="12" t="str">
+        <x:v>best～生まれた時から～</x:v>
+      </x:c>
+      <x:c r="E105" s="12" t="str">
+        <x:v>Best: Umareta Toki kara</x:v>
+      </x:c>
+      <x:c r="F105" s="12" t="str">
+        <x:v>Canyon</x:v>
+      </x:c>
+      <x:c r="G105" s="12" t="str">
+        <x:v>C40A-0398</x:v>
+      </x:c>
+      <x:c r="H105" s="12" t="str">
+        <x:v>1985</x:v>
+      </x:c>
+      <x:c r="I105" s="12" t="str">
+        <x:v>2LP</x:v>
+      </x:c>
+      <x:c r="J105" s="12" t="str"/>
+      <x:c r="K105" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L105" s="12" t="str"/>
+      <x:c r="M105" s="12" t="str"/>
+      <x:c r="N105" s="12" t="str">
+        <x:v>IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="O105" s="12" t="str">
+        <x:v>104_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P105" s="12" t="str"/>
+      <x:c r="Q105" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/best-%E7%94%9F%E3%81%BE%E3%82%8C%E3%81%9F%E6%99%82%E3%81%8B%E3%82%89/1669411490?uo=4</x:v>
+      </x:c>
+      <x:c r="R105" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S105" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3248.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://omimi.biz/index.php/products/detail/59521</x:v>
+      </x:c>
+      <x:c r="T105" s="12" t="str"/>
+      <x:c r="U105" s="12" t="str"/>
+      <x:c r="V105" s="12" t="str"/>
+      <x:c r="W105" s="12" t="str"/>
+      <x:c r="X105" s="12" t="str"/>
+      <x:c r="Y105" s="12" t="str"/>
+      <x:c r="Z105" s="12" t="str"/>
+      <x:c r="AA105" s="12" t="str"/>
+      <x:c r="AB105" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC105" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD105" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE105" s="12" t="str">
+        <x:v>A 1985 two-LP Chiemi Hori compilation on Canyon, bringing together 24 recordings under the title Best: Umareta Toki kara.</x:v>
+      </x:c>
+      <x:c r="AF105" s="12" t="str">
+        <x:v>https://omimi.biz/index.php/products/detail/59521</x:v>
+      </x:c>
+      <x:c r="AG105" s="12" t="str">
+        <x:v>Omimi release listing</x:v>
+      </x:c>
+      <x:c r="AH105" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E5%A0%80%E3%81%A1%E3%81%88%E3%81%BF/274440716?uo=4</x:v>
+      </x:c>
+      <x:c r="AI105" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="120" customHeight="1">
+      <x:c r="A106" s="12" t="str">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B106" s="12" t="str"/>
+      <x:c r="C106" s="12" t="str">
+        <x:v>Various Artists</x:v>
+      </x:c>
+      <x:c r="D106" s="12" t="str">
+        <x:v>メリー・クリスマス・フォー・ユー</x:v>
+      </x:c>
+      <x:c r="E106" s="12" t="str">
+        <x:v>Merry Xmas for You</x:v>
+      </x:c>
+      <x:c r="F106" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G106" s="12" t="str"/>
+      <x:c r="H106" s="12" t="str"/>
+      <x:c r="I106" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J106" s="12" t="str"/>
+      <x:c r="K106" s="12" t="str"/>
+      <x:c r="L106" s="12" t="str"/>
+      <x:c r="M106" s="12" t="str"/>
+      <x:c r="N106" s="12" t="str">
+        <x:v>IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="O106" s="12" t="str">
+        <x:v>105_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P106" s="12" t="str"/>
+      <x:c r="Q106" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="R106" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S106" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3248.jpg. </x:v>
+      </x:c>
+      <x:c r="T106" s="12" t="str"/>
+      <x:c r="U106" s="12" t="str"/>
+      <x:c r="V106" s="12" t="str"/>
+      <x:c r="W106" s="12" t="str"/>
+      <x:c r="X106" s="12" t="str"/>
+      <x:c r="Y106" s="12" t="str"/>
+      <x:c r="Z106" s="12" t="str"/>
+      <x:c r="AA106" s="12" t="str"/>
+      <x:c r="AB106" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC106" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD106" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE106" s="12" t="str">
+        <x:v>Collection note: Merry Xmas for You by Various Artists, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF106" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="AG106" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH106" s="12" t="str"/>
+      <x:c r="AI106" s="12" t="str"/>
+    </x:row>
+    <x:row r="107" ht="120" customHeight="1">
+      <x:c r="A107" s="12" t="str">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B107" s="12" t="str">
+        <x:v>キャンディーズ</x:v>
+      </x:c>
+      <x:c r="C107" s="12" t="str">
+        <x:v>Candies</x:v>
+      </x:c>
+      <x:c r="D107" s="12" t="str">
+        <x:v>キャンディ・レーベル</x:v>
+      </x:c>
+      <x:c r="E107" s="12" t="str">
+        <x:v>Candy Label</x:v>
+      </x:c>
+      <x:c r="F107" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G107" s="12" t="str"/>
+      <x:c r="H107" s="12" t="str"/>
+      <x:c r="I107" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J107" s="12" t="str"/>
+      <x:c r="K107" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L107" s="12" t="str"/>
+      <x:c r="M107" s="12" t="str"/>
+      <x:c r="N107" s="12" t="str">
+        <x:v>IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="O107" s="12" t="str">
+        <x:v>106_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P107" s="12" t="str"/>
+      <x:c r="Q107" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E3%82%AD%E3%83%A3%E3%83%B3%E3%83%87%E3%82%A3-%E3%83%AC%E3%83%BC%E3%83%99%E3%83%AB/1536934035?uo=4</x:v>
+      </x:c>
+      <x:c r="R107" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S107" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3248.jpg. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T107" s="12" t="str"/>
+      <x:c r="U107" s="12" t="str"/>
+      <x:c r="V107" s="12" t="str"/>
+      <x:c r="W107" s="12" t="str"/>
+      <x:c r="X107" s="12" t="str"/>
+      <x:c r="Y107" s="12" t="str"/>
+      <x:c r="Z107" s="12" t="str"/>
+      <x:c r="AA107" s="12" t="str"/>
+      <x:c r="AB107" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC107" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD107" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE107" s="12" t="str">
+        <x:v>Collection note: Candy Label by Candies, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF107" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="AG107" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH107" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E3%82%AD%E3%83%A3%E3%83%B3%E3%83%87%E3%82%A3%E3%83%BC%E3%82%BA/555222297?uo=4</x:v>
+      </x:c>
+      <x:c r="AI107" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="120" customHeight="1">
+      <x:c r="A108" s="12" t="str">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B108" s="12" t="str">
+        <x:v>松任谷由実</x:v>
+      </x:c>
+      <x:c r="C108" s="12" t="str">
+        <x:v>Yumi Matsutoya</x:v>
+      </x:c>
+      <x:c r="D108" s="12" t="str">
+        <x:v>ダイアモンドダストが消えぬまに</x:v>
+      </x:c>
+      <x:c r="E108" s="12" t="str">
+        <x:v>Before the Diamond Dust Fades</x:v>
+      </x:c>
+      <x:c r="F108" s="12" t="str">
+        <x:v>Express</x:v>
+      </x:c>
+      <x:c r="G108" s="12" t="str"/>
+      <x:c r="H108" s="12" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I108" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J108" s="12" t="str"/>
+      <x:c r="K108" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L108" s="12" t="str"/>
+      <x:c r="M108" s="12" t="str"/>
+      <x:c r="N108" s="12" t="str">
+        <x:v>IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="O108" s="12" t="str">
+        <x:v>107_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P108" s="12" t="str"/>
+      <x:c r="Q108" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/before-the-diamond-dust-fades-diamond-dust-ga-kienu-ma-ni/1436009867?uo=4</x:v>
+      </x:c>
+      <x:c r="R108" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S108" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3248.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T108" s="12" t="str"/>
+      <x:c r="U108" s="12" t="str"/>
+      <x:c r="V108" s="12" t="str"/>
+      <x:c r="W108" s="12" t="str"/>
+      <x:c r="X108" s="12" t="str"/>
+      <x:c r="Y108" s="12" t="str"/>
+      <x:c r="Z108" s="12" t="str"/>
+      <x:c r="AA108" s="12" t="str"/>
+      <x:c r="AB108" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC108" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD108" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE108" s="12" t="str">
+        <x:v>Collection note: Before the Diamond Dust Fades by Yumi Matsutoya, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF108" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="AG108" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH108" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E6%9D%BE%E4%BB%BB%E8%B0%B7%E7%94%B1%E5%AE%9F/76458419?uo=4</x:v>
+      </x:c>
+      <x:c r="AI108" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="120" customHeight="1">
+      <x:c r="A109" s="12" t="str">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B109" s="12" t="str">
+        <x:v>ピンク・レディー</x:v>
+      </x:c>
+      <x:c r="C109" s="12" t="str">
+        <x:v>Pink Lady</x:v>
+      </x:c>
+      <x:c r="D109" s="12" t="str">
+        <x:v>活動大写真</x:v>
+      </x:c>
+      <x:c r="E109" s="12" t="str">
+        <x:v>Katsudo Daishashin</x:v>
+      </x:c>
+      <x:c r="F109" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G109" s="12" t="str"/>
+      <x:c r="H109" s="12" t="str">
+        <x:v>1978</x:v>
+      </x:c>
+      <x:c r="I109" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J109" s="12" t="str"/>
+      <x:c r="K109" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L109" s="12" t="str"/>
+      <x:c r="M109" s="12" t="str"/>
+      <x:c r="N109" s="12" t="str">
+        <x:v>IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="O109" s="12" t="str">
+        <x:v>108_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P109" s="12" t="str"/>
+      <x:c r="Q109" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/katsudo-daishashin-original-soundtrack/1489145538?uo=4</x:v>
+      </x:c>
+      <x:c r="R109" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S109" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3248.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T109" s="12" t="str"/>
+      <x:c r="U109" s="12" t="str"/>
+      <x:c r="V109" s="12" t="str"/>
+      <x:c r="W109" s="12" t="str"/>
+      <x:c r="X109" s="12" t="str"/>
+      <x:c r="Y109" s="12" t="str"/>
+      <x:c r="Z109" s="12" t="str"/>
+      <x:c r="AA109" s="12" t="str"/>
+      <x:c r="AB109" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC109" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD109" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE109" s="12" t="str">
+        <x:v>Collection note: Katsudo Daishashin by Pink Lady, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF109" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="AG109" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH109" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E3%83%94%E3%83%B3%E3%82%AF-%E3%83%AC%E3%83%87%E3%82%A3%E3%83%BC/207003566?uo=4</x:v>
+      </x:c>
+      <x:c r="AI109" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="120" customHeight="1">
+      <x:c r="A110" s="12" t="str">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B110" s="12" t="str">
+        <x:v>松任谷由実</x:v>
+      </x:c>
+      <x:c r="C110" s="12" t="str">
+        <x:v>Yumi Matsutoya</x:v>
+      </x:c>
+      <x:c r="D110" s="12" t="str"/>
+      <x:c r="E110" s="12" t="str">
+        <x:v>Voyager</x:v>
+      </x:c>
+      <x:c r="F110" s="12" t="str">
+        <x:v>Express</x:v>
+      </x:c>
+      <x:c r="G110" s="12" t="str"/>
+      <x:c r="H110" s="12" t="str">
+        <x:v>1983</x:v>
+      </x:c>
+      <x:c r="I110" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J110" s="12" t="str"/>
+      <x:c r="K110" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L110" s="12" t="str"/>
+      <x:c r="M110" s="12" t="str"/>
+      <x:c r="N110" s="12" t="str">
+        <x:v>IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="O110" s="12" t="str">
+        <x:v>109_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P110" s="12" t="str"/>
+      <x:c r="Q110" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/voyager/1436012984?uo=4</x:v>
+      </x:c>
+      <x:c r="R110" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S110" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3248.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T110" s="12" t="str"/>
+      <x:c r="U110" s="12" t="str"/>
+      <x:c r="V110" s="12" t="str"/>
+      <x:c r="W110" s="12" t="str"/>
+      <x:c r="X110" s="12" t="str"/>
+      <x:c r="Y110" s="12" t="str"/>
+      <x:c r="Z110" s="12" t="str"/>
+      <x:c r="AA110" s="12" t="str"/>
+      <x:c r="AB110" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC110" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD110" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE110" s="12" t="str">
+        <x:v>Collection note: Voyager by Yumi Matsutoya, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF110" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3248.jpg</x:v>
+      </x:c>
+      <x:c r="AG110" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH110" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E6%9D%BE%E4%BB%BB%E8%B0%B7%E7%94%B1%E5%AE%9F/76458419?uo=4</x:v>
+      </x:c>
+      <x:c r="AI110" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="120" customHeight="1">
+      <x:c r="A111" s="12" t="str">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B111" s="12" t="str">
+        <x:v>渡辺真知子</x:v>
+      </x:c>
+      <x:c r="C111" s="12" t="str">
+        <x:v>Machiko Watanabe</x:v>
+      </x:c>
+      <x:c r="D111" s="12" t="str">
+        <x:v>フォグ・ランプ</x:v>
+      </x:c>
+      <x:c r="E111" s="12" t="str">
+        <x:v>Fog Lamp</x:v>
+      </x:c>
+      <x:c r="F111" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G111" s="12" t="str"/>
+      <x:c r="H111" s="12" t="str">
+        <x:v>1978</x:v>
+      </x:c>
+      <x:c r="I111" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J111" s="12" t="str"/>
+      <x:c r="K111" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L111" s="12" t="str"/>
+      <x:c r="M111" s="12" t="str">
+        <x:v>One of two separately owned physical copies, confirmed by the owner. Each copy has its own collection ID and reference photograph.</x:v>
+      </x:c>
+      <x:c r="N111" s="12" t="str">
+        <x:v>IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="O111" s="12" t="str">
+        <x:v>110_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P111" s="12" t="str"/>
+      <x:c r="Q111" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E3%83%95%E3%82%A9%E3%82%B0-%E3%83%A9%E3%83%B3%E3%83%97/1536768852?uo=4</x:v>
+      </x:c>
+      <x:c r="R111" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S111" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3249.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="T111" s="12" t="str"/>
+      <x:c r="U111" s="12" t="str"/>
+      <x:c r="V111" s="12" t="str"/>
+      <x:c r="W111" s="12" t="str"/>
+      <x:c r="X111" s="12" t="str"/>
+      <x:c r="Y111" s="12" t="str"/>
+      <x:c r="Z111" s="12" t="str"/>
+      <x:c r="AA111" s="12" t="str"/>
+      <x:c r="AB111" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC111" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD111" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE111" s="12" t="str">
+        <x:v>Released in November 1978, Fog Lamp includes Blue, Konya wa Odotte and its title track.</x:v>
+      </x:c>
+      <x:c r="AF111" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AG111" s="12" t="str">
+        <x:v>FMPJ artist discography</x:v>
+      </x:c>
+      <x:c r="AH111" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AI111" s="12" t="str">
+        <x:v>Artist profile and discography</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="120" customHeight="1">
+      <x:c r="A112" s="12" t="str">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B112" s="12" t="str">
+        <x:v>山口百恵</x:v>
+      </x:c>
+      <x:c r="C112" s="12" t="str">
+        <x:v>Momoe Yamaguchi</x:v>
+      </x:c>
+      <x:c r="D112" s="12" t="str">
+        <x:v>春告鳥</x:v>
+      </x:c>
+      <x:c r="E112" s="12" t="str">
+        <x:v>Haru Tsugedori</x:v>
+      </x:c>
+      <x:c r="F112" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G112" s="12" t="str"/>
+      <x:c r="H112" s="12" t="str"/>
+      <x:c r="I112" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J112" s="12" t="str"/>
+      <x:c r="K112" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L112" s="12" t="str"/>
+      <x:c r="M112" s="12" t="str"/>
+      <x:c r="N112" s="12" t="str">
+        <x:v>IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="O112" s="12" t="str">
+        <x:v>111_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P112" s="12" t="str"/>
+      <x:c r="Q112" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E6%98%A5%E5%91%8A%E9%B3%A5/1536753841?uo=4</x:v>
+      </x:c>
+      <x:c r="R112" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S112" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3249.jpg. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T112" s="12" t="str"/>
+      <x:c r="U112" s="12" t="str"/>
+      <x:c r="V112" s="12" t="str"/>
+      <x:c r="W112" s="12" t="str"/>
+      <x:c r="X112" s="12" t="str"/>
+      <x:c r="Y112" s="12" t="str"/>
+      <x:c r="Z112" s="12" t="str"/>
+      <x:c r="AA112" s="12" t="str"/>
+      <x:c r="AB112" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC112" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD112" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE112" s="12" t="str">
+        <x:v>Collection note: Haru Tsugedori by Momoe Yamaguchi, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF112" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="AG112" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH112" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E5%B1%B1%E5%8F%A3%E7%99%BE%E6%81%B5/580769634?uo=4</x:v>
+      </x:c>
+      <x:c r="AI112" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="120" customHeight="1">
+      <x:c r="A113" s="12" t="str">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B113" s="12" t="str">
+        <x:v>岩崎宏美</x:v>
+      </x:c>
+      <x:c r="C113" s="12" t="str">
+        <x:v>Hiromi Iwasaki</x:v>
+      </x:c>
+      <x:c r="D113" s="12" t="str">
+        <x:v>ファンタジー</x:v>
+      </x:c>
+      <x:c r="E113" s="12" t="str">
+        <x:v>Fantasy</x:v>
+      </x:c>
+      <x:c r="F113" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G113" s="12" t="str"/>
+      <x:c r="H113" s="12" t="str"/>
+      <x:c r="I113" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J113" s="12" t="str"/>
+      <x:c r="K113" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L113" s="12" t="str"/>
+      <x:c r="M113" s="12" t="str"/>
+      <x:c r="N113" s="12" t="str">
+        <x:v>IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="O113" s="12" t="str">
+        <x:v>112_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P113" s="12" t="str"/>
+      <x:c r="Q113" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/fantasy/251327399?uo=4</x:v>
+      </x:c>
+      <x:c r="R113" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S113" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3249.jpg. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T113" s="12" t="str"/>
+      <x:c r="U113" s="12" t="str"/>
+      <x:c r="V113" s="12" t="str"/>
+      <x:c r="W113" s="12" t="str"/>
+      <x:c r="X113" s="12" t="str"/>
+      <x:c r="Y113" s="12" t="str"/>
+      <x:c r="Z113" s="12" t="str"/>
+      <x:c r="AA113" s="12" t="str"/>
+      <x:c r="AB113" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC113" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD113" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE113" s="12" t="str">
+        <x:v>Collection note: Fantasy by Hiromi Iwasaki, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF113" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="AG113" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH113" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E5%B2%A9%E5%B4%8E%E5%AE%8F%E7%BE%8E/218734580?uo=4</x:v>
+      </x:c>
+      <x:c r="AI113" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="120" customHeight="1">
+      <x:c r="A114" s="12" t="str">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B114" s="12" t="str">
+        <x:v>渡辺真知子</x:v>
+      </x:c>
+      <x:c r="C114" s="12" t="str">
+        <x:v>Machiko Watanabe</x:v>
+      </x:c>
+      <x:c r="D114" s="12" t="str">
+        <x:v>海につれていって</x:v>
+      </x:c>
+      <x:c r="E114" s="12" t="str">
+        <x:v>Umi ni Tsurete Itte</x:v>
+      </x:c>
+      <x:c r="F114" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G114" s="12" t="str"/>
+      <x:c r="H114" s="12" t="str">
+        <x:v>1978</x:v>
+      </x:c>
+      <x:c r="I114" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J114" s="12" t="str"/>
+      <x:c r="K114" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L114" s="12" t="str"/>
+      <x:c r="M114" s="12" t="str">
+        <x:v>One of two separately owned physical copies, confirmed by the owner. Each copy has its own collection ID and reference photograph.</x:v>
+      </x:c>
+      <x:c r="N114" s="12" t="str">
+        <x:v>IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="O114" s="12" t="str">
+        <x:v>113_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P114" s="12" t="str"/>
+      <x:c r="Q114" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E6%B5%B7%E3%81%AB%E3%81%A4%E3%82%8C%E3%81%A6%E3%81%84%E3%81%A3%E3%81%A6/1536768424?uo=4</x:v>
+      </x:c>
+      <x:c r="R114" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S114" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3249.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="T114" s="12" t="str"/>
+      <x:c r="U114" s="12" t="str"/>
+      <x:c r="V114" s="12" t="str"/>
+      <x:c r="W114" s="12" t="str"/>
+      <x:c r="X114" s="12" t="str"/>
+      <x:c r="Y114" s="12" t="str"/>
+      <x:c r="Z114" s="12" t="str"/>
+      <x:c r="AA114" s="12" t="str"/>
+      <x:c r="AB114" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC114" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD114" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE114" s="12" t="str">
+        <x:v>Machiko Watanabe’s May 1978 album includes her early hits Mayoi Michi and Kamome ga Tonda Hi.</x:v>
+      </x:c>
+      <x:c r="AF114" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AG114" s="12" t="str">
+        <x:v>FMPJ artist discography</x:v>
+      </x:c>
+      <x:c r="AH114" s="12" t="str">
+        <x:v>https://www.kiokunokiroku.jp/artist/000416</x:v>
+      </x:c>
+      <x:c r="AI114" s="12" t="str">
+        <x:v>Artist profile and discography</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="120" customHeight="1">
+      <x:c r="A115" s="12" t="str">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B115" s="12" t="str">
+        <x:v>サーカス</x:v>
+      </x:c>
+      <x:c r="C115" s="12" t="str">
+        <x:v>Circus</x:v>
+      </x:c>
+      <x:c r="D115" s="12" t="str">
+        <x:v>ベスト・ヒット・サーカス</x:v>
+      </x:c>
+      <x:c r="E115" s="12" t="str">
+        <x:v>Best Hits Circus</x:v>
+      </x:c>
+      <x:c r="F115" s="12" t="str">
+        <x:v>Alfa</x:v>
+      </x:c>
+      <x:c r="G115" s="12" t="str"/>
+      <x:c r="H115" s="12" t="str"/>
+      <x:c r="I115" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J115" s="12" t="str"/>
+      <x:c r="K115" s="12" t="str"/>
+      <x:c r="L115" s="12" t="str"/>
+      <x:c r="M115" s="12" t="str"/>
+      <x:c r="N115" s="12" t="str">
+        <x:v>IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="O115" s="12" t="str">
+        <x:v>114_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P115" s="12" t="str"/>
+      <x:c r="Q115" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="R115" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S115" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3249.jpg. </x:v>
+      </x:c>
+      <x:c r="T115" s="12" t="str"/>
+      <x:c r="U115" s="12" t="str"/>
+      <x:c r="V115" s="12" t="str"/>
+      <x:c r="W115" s="12" t="str"/>
+      <x:c r="X115" s="12" t="str"/>
+      <x:c r="Y115" s="12" t="str"/>
+      <x:c r="Z115" s="12" t="str"/>
+      <x:c r="AA115" s="12" t="str"/>
+      <x:c r="AB115" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC115" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD115" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE115" s="12" t="str">
+        <x:v>Collection note: Circus compilation titled Best Hits Circus. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF115" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="AG115" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH115" s="12" t="str"/>
+      <x:c r="AI115" s="12" t="str"/>
+    </x:row>
+    <x:row r="116" ht="120" customHeight="1">
+      <x:c r="A116" s="12" t="str">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B116" s="12" t="str">
+        <x:v>安部恭弘</x:v>
+      </x:c>
+      <x:c r="C116" s="12" t="str">
+        <x:v>Yasuhiro Abe</x:v>
+      </x:c>
+      <x:c r="D116" s="12" t="str">
+        <x:v>モデラート</x:v>
+      </x:c>
+      <x:c r="E116" s="12" t="str">
+        <x:v>Moderato</x:v>
+      </x:c>
+      <x:c r="F116" s="12" t="str"/>
+      <x:c r="G116" s="12" t="str"/>
+      <x:c r="H116" s="12" t="str">
+        <x:v>1984</x:v>
+      </x:c>
+      <x:c r="I116" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J116" s="12" t="str"/>
+      <x:c r="K116" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L116" s="12" t="str"/>
+      <x:c r="M116" s="12" t="str"/>
+      <x:c r="N116" s="12" t="str">
+        <x:v>IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="O116" s="12" t="str">
+        <x:v>115_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P116" s="12" t="str"/>
+      <x:c r="Q116" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/moderato/720346864?uo=4</x:v>
+      </x:c>
+      <x:c r="R116" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S116" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3249.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T116" s="12" t="str"/>
+      <x:c r="U116" s="12" t="str"/>
+      <x:c r="V116" s="12" t="str"/>
+      <x:c r="W116" s="12" t="str"/>
+      <x:c r="X116" s="12" t="str"/>
+      <x:c r="Y116" s="12" t="str"/>
+      <x:c r="Z116" s="12" t="str"/>
+      <x:c r="AA116" s="12" t="str"/>
+      <x:c r="AB116" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC116" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD116" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE116" s="12" t="str">
+        <x:v>Collection note: Moderato by Yasuhiro Abe, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF116" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="AG116" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH116" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E5%AE%89%E9%83%A8%E6%81%AD%E5%BC%98/193508408?uo=4</x:v>
+      </x:c>
+      <x:c r="AI116" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="120" customHeight="1">
+      <x:c r="A117" s="12" t="str">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B117" s="12" t="str">
+        <x:v>阿川泰子</x:v>
+      </x:c>
+      <x:c r="C117" s="12" t="str">
+        <x:v>Yasuko Agawa</x:v>
+      </x:c>
+      <x:c r="D117" s="12" t="str">
+        <x:v>ジャーニー</x:v>
+      </x:c>
+      <x:c r="E117" s="12" t="str">
+        <x:v>Journey</x:v>
+      </x:c>
+      <x:c r="F117" s="12" t="str"/>
+      <x:c r="G117" s="12" t="str"/>
+      <x:c r="H117" s="12" t="str"/>
+      <x:c r="I117" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J117" s="12" t="str"/>
+      <x:c r="K117" s="12" t="str">
+        <x:v>Jazz</x:v>
+      </x:c>
+      <x:c r="L117" s="12" t="str"/>
+      <x:c r="M117" s="12" t="str"/>
+      <x:c r="N117" s="12" t="str">
+        <x:v>IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="O117" s="12" t="str">
+        <x:v>116_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P117" s="12" t="str"/>
+      <x:c r="Q117" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/journey-yasuko-love-bird/333475060?uo=4</x:v>
+      </x:c>
+      <x:c r="R117" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S117" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3249.jpg. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T117" s="12" t="str"/>
+      <x:c r="U117" s="12" t="str"/>
+      <x:c r="V117" s="12" t="str"/>
+      <x:c r="W117" s="12" t="str"/>
+      <x:c r="X117" s="12" t="str"/>
+      <x:c r="Y117" s="12" t="str"/>
+      <x:c r="Z117" s="12" t="str"/>
+      <x:c r="AA117" s="12" t="str"/>
+      <x:c r="AB117" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC117" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD117" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE117" s="12" t="str">
+        <x:v>Collection note: Journey by Yasuko Agawa, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF117" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="AG117" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH117" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E9%98%BF%E5%B7%9D%E6%B3%B0%E5%AD%90/271055240?uo=4</x:v>
+      </x:c>
+      <x:c r="AI117" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="120" customHeight="1">
+      <x:c r="A118" s="12" t="str">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B118" s="12" t="str">
+        <x:v>荒井由実</x:v>
+      </x:c>
+      <x:c r="C118" s="12" t="str">
+        <x:v>Yumi Arai</x:v>
+      </x:c>
+      <x:c r="D118" s="12" t="str">
+        <x:v>コバルト・アワー</x:v>
+      </x:c>
+      <x:c r="E118" s="12" t="str">
+        <x:v>Cobalt Hour</x:v>
+      </x:c>
+      <x:c r="F118" s="12" t="str">
+        <x:v>Express</x:v>
+      </x:c>
+      <x:c r="G118" s="12" t="str"/>
+      <x:c r="H118" s="12" t="str">
+        <x:v>1975</x:v>
+      </x:c>
+      <x:c r="I118" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J118" s="12" t="str"/>
+      <x:c r="K118" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L118" s="12" t="str"/>
+      <x:c r="M118" s="12" t="str">
+        <x:v>One of two separately owned physical copies, confirmed by the owner. Each copy has its own collection ID and reference photograph.</x:v>
+      </x:c>
+      <x:c r="N118" s="12" t="str">
+        <x:v>IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="O118" s="12" t="str">
+        <x:v>117_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P118" s="12" t="str"/>
+      <x:c r="Q118" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/cobalt-hour/1436010473?uo=4</x:v>
+      </x:c>
+      <x:c r="R118" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S118" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3249.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T118" s="12" t="str"/>
+      <x:c r="U118" s="12" t="str"/>
+      <x:c r="V118" s="12" t="str"/>
+      <x:c r="W118" s="12" t="str"/>
+      <x:c r="X118" s="12" t="str"/>
+      <x:c r="Y118" s="12" t="str"/>
+      <x:c r="Z118" s="12" t="str"/>
+      <x:c r="AA118" s="12" t="str"/>
+      <x:c r="AB118" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC118" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD118" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE118" s="12" t="str">
+        <x:v>Collection note: Cobalt Hour by Yumi Arai, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF118" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="AG118" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH118" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E8%8D%92%E4%BA%95%E7%94%B1%E5%AE%9F/81316604?uo=4</x:v>
+      </x:c>
+      <x:c r="AI118" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="120" customHeight="1">
+      <x:c r="A119" s="12" t="str">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B119" s="12" t="str">
+        <x:v>シュガー</x:v>
+      </x:c>
+      <x:c r="C119" s="12" t="str">
+        <x:v>Sugar</x:v>
+      </x:c>
+      <x:c r="D119" s="12" t="str">
+        <x:v>シュガー・ドリーム</x:v>
+      </x:c>
+      <x:c r="E119" s="12" t="str">
+        <x:v>Sugar Dream</x:v>
+      </x:c>
+      <x:c r="F119" s="12" t="str"/>
+      <x:c r="G119" s="12" t="str"/>
+      <x:c r="H119" s="12" t="str"/>
+      <x:c r="I119" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J119" s="12" t="str"/>
+      <x:c r="K119" s="12" t="str"/>
+      <x:c r="L119" s="12" t="str"/>
+      <x:c r="M119" s="12" t="str"/>
+      <x:c r="N119" s="12" t="str">
+        <x:v>IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="O119" s="12" t="str">
+        <x:v>118_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P119" s="12" t="str"/>
+      <x:c r="Q119" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="R119" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S119" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3249.jpg. </x:v>
+      </x:c>
+      <x:c r="T119" s="12" t="str"/>
+      <x:c r="U119" s="12" t="str"/>
+      <x:c r="V119" s="12" t="str"/>
+      <x:c r="W119" s="12" t="str"/>
+      <x:c r="X119" s="12" t="str"/>
+      <x:c r="Y119" s="12" t="str"/>
+      <x:c r="Z119" s="12" t="str"/>
+      <x:c r="AA119" s="12" t="str"/>
+      <x:c r="AB119" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC119" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD119" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE119" s="12" t="str">
+        <x:v>Collection note: Sugar Dream by Sugar, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF119" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3249.jpg</x:v>
+      </x:c>
+      <x:c r="AG119" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH119" s="12" t="str"/>
+      <x:c r="AI119" s="12" t="str"/>
+    </x:row>
+    <x:row r="120" ht="120" customHeight="1">
+      <x:c r="A120" s="12" t="str">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B120" s="12" t="str">
+        <x:v>松原みき</x:v>
+      </x:c>
+      <x:c r="C120" s="12" t="str">
+        <x:v>Miki Matsubara</x:v>
+      </x:c>
+      <x:c r="D120" s="12" t="str">
+        <x:v>デジャ・ヴ</x:v>
+      </x:c>
+      <x:c r="E120" s="12" t="str">
+        <x:v>Deja Vu</x:v>
+      </x:c>
+      <x:c r="F120" s="12" t="str"/>
+      <x:c r="G120" s="12" t="str"/>
+      <x:c r="H120" s="12" t="str"/>
+      <x:c r="I120" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J120" s="12" t="str"/>
+      <x:c r="K120" s="12" t="str"/>
+      <x:c r="L120" s="12" t="str"/>
+      <x:c r="M120" s="12" t="str"/>
+      <x:c r="N120" s="12" t="str">
+        <x:v>IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="O120" s="12" t="str">
+        <x:v>119_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P120" s="12" t="str"/>
+      <x:c r="Q120" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="R120" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S120" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3250.jpg. </x:v>
+      </x:c>
+      <x:c r="T120" s="12" t="str"/>
+      <x:c r="U120" s="12" t="str"/>
+      <x:c r="V120" s="12" t="str"/>
+      <x:c r="W120" s="12" t="str"/>
+      <x:c r="X120" s="12" t="str"/>
+      <x:c r="Y120" s="12" t="str"/>
+      <x:c r="Z120" s="12" t="str"/>
+      <x:c r="AA120" s="12" t="str"/>
+      <x:c r="AB120" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC120" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD120" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE120" s="12" t="str">
+        <x:v>Collection note: Deja Vu by Miki Matsubara, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF120" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="AG120" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH120" s="12" t="str"/>
+      <x:c r="AI120" s="12" t="str"/>
+    </x:row>
+    <x:row r="121" ht="120" customHeight="1">
+      <x:c r="A121" s="12" t="str">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B121" s="12" t="str">
+        <x:v>アンリ菅野</x:v>
+      </x:c>
+      <x:c r="C121" s="12" t="str">
+        <x:v>Anli Sugano</x:v>
+      </x:c>
+      <x:c r="D121" s="12" t="str">
+        <x:v>ラヴ・スケッチ</x:v>
+      </x:c>
+      <x:c r="E121" s="12" t="str">
+        <x:v>Love Sketch</x:v>
+      </x:c>
+      <x:c r="F121" s="12" t="str"/>
+      <x:c r="G121" s="12" t="str"/>
+      <x:c r="H121" s="12" t="str"/>
+      <x:c r="I121" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J121" s="12" t="str"/>
+      <x:c r="K121" s="12" t="str"/>
+      <x:c r="L121" s="12" t="str"/>
+      <x:c r="M121" s="12" t="str"/>
+      <x:c r="N121" s="12" t="str">
+        <x:v>IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="O121" s="12" t="str">
+        <x:v>120_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P121" s="12" t="str"/>
+      <x:c r="Q121" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="R121" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S121" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3250.jpg. </x:v>
+      </x:c>
+      <x:c r="T121" s="12" t="str"/>
+      <x:c r="U121" s="12" t="str"/>
+      <x:c r="V121" s="12" t="str"/>
+      <x:c r="W121" s="12" t="str"/>
+      <x:c r="X121" s="12" t="str"/>
+      <x:c r="Y121" s="12" t="str"/>
+      <x:c r="Z121" s="12" t="str"/>
+      <x:c r="AA121" s="12" t="str"/>
+      <x:c r="AB121" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC121" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD121" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE121" s="12" t="str">
+        <x:v>Collection note: Love Sketch by Anli Sugano, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF121" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="AG121" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH121" s="12" t="str"/>
+      <x:c r="AI121" s="12" t="str"/>
+    </x:row>
+    <x:row r="122" ht="120" customHeight="1">
+      <x:c r="A122" s="12" t="str">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B122" s="12" t="str">
+        <x:v>マリムラ・ケイ</x:v>
+      </x:c>
+      <x:c r="C122" s="12" t="str">
+        <x:v>Kei Marimura</x:v>
+      </x:c>
+      <x:c r="D122" s="12" t="str"/>
+      <x:c r="E122" s="12" t="str">
+        <x:v>Elegance</x:v>
+      </x:c>
+      <x:c r="F122" s="12" t="str"/>
+      <x:c r="G122" s="12" t="str"/>
+      <x:c r="H122" s="12" t="str"/>
+      <x:c r="I122" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J122" s="12" t="str"/>
+      <x:c r="K122" s="12" t="str"/>
+      <x:c r="L122" s="12" t="str"/>
+      <x:c r="M122" s="12" t="str"/>
+      <x:c r="N122" s="12" t="str">
+        <x:v>IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="O122" s="12" t="str">
+        <x:v>121_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P122" s="12" t="str"/>
+      <x:c r="Q122" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="R122" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S122" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3250.jpg. </x:v>
+      </x:c>
+      <x:c r="T122" s="12" t="str"/>
+      <x:c r="U122" s="12" t="str"/>
+      <x:c r="V122" s="12" t="str"/>
+      <x:c r="W122" s="12" t="str"/>
+      <x:c r="X122" s="12" t="str"/>
+      <x:c r="Y122" s="12" t="str"/>
+      <x:c r="Z122" s="12" t="str"/>
+      <x:c r="AA122" s="12" t="str"/>
+      <x:c r="AB122" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC122" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD122" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE122" s="12" t="str">
+        <x:v>Collection note: Elegance by Kei Marimura, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF122" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="AG122" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH122" s="12" t="str"/>
+      <x:c r="AI122" s="12" t="str"/>
+    </x:row>
+    <x:row r="123" ht="120" customHeight="1">
+      <x:c r="A123" s="12" t="str">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B123" s="12" t="str">
+        <x:v>マリムラ・ケイ</x:v>
+      </x:c>
+      <x:c r="C123" s="12" t="str">
+        <x:v>Kei Marimura</x:v>
+      </x:c>
+      <x:c r="D123" s="12" t="str"/>
+      <x:c r="E123" s="12" t="str">
+        <x:v>The Man I Love</x:v>
+      </x:c>
+      <x:c r="F123" s="12" t="str"/>
+      <x:c r="G123" s="12" t="str"/>
+      <x:c r="H123" s="12" t="str"/>
+      <x:c r="I123" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J123" s="12" t="str"/>
+      <x:c r="K123" s="12" t="str"/>
+      <x:c r="L123" s="12" t="str"/>
+      <x:c r="M123" s="12" t="str"/>
+      <x:c r="N123" s="12" t="str">
+        <x:v>IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="O123" s="12" t="str">
+        <x:v>122_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P123" s="12" t="str"/>
+      <x:c r="Q123" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="R123" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S123" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3250.jpg. </x:v>
+      </x:c>
+      <x:c r="T123" s="12" t="str"/>
+      <x:c r="U123" s="12" t="str"/>
+      <x:c r="V123" s="12" t="str"/>
+      <x:c r="W123" s="12" t="str"/>
+      <x:c r="X123" s="12" t="str"/>
+      <x:c r="Y123" s="12" t="str"/>
+      <x:c r="Z123" s="12" t="str"/>
+      <x:c r="AA123" s="12" t="str"/>
+      <x:c r="AB123" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC123" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD123" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE123" s="12" t="str">
+        <x:v>Collection note: The Man I Love by Kei Marimura, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF123" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="AG123" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH123" s="12" t="str"/>
+      <x:c r="AI123" s="12" t="str"/>
+    </x:row>
+    <x:row r="124" ht="120" customHeight="1">
+      <x:c r="A124" s="12" t="str">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B124" s="12" t="str">
+        <x:v>笠井紀美子</x:v>
+      </x:c>
+      <x:c r="C124" s="12" t="str">
+        <x:v>Kimiko Kasai</x:v>
+      </x:c>
+      <x:c r="D124" s="12" t="str"/>
+      <x:c r="E124" s="12" t="str">
+        <x:v>We Can Fall in Love</x:v>
+      </x:c>
+      <x:c r="F124" s="12" t="str"/>
+      <x:c r="G124" s="12" t="str"/>
+      <x:c r="H124" s="12" t="str">
+        <x:v>1976</x:v>
+      </x:c>
+      <x:c r="I124" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J124" s="12" t="str"/>
+      <x:c r="K124" s="12" t="str">
+        <x:v>Jazz</x:v>
+      </x:c>
+      <x:c r="L124" s="12" t="str"/>
+      <x:c r="M124" s="12" t="str"/>
+      <x:c r="N124" s="12" t="str">
+        <x:v>IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="O124" s="12" t="str">
+        <x:v>123_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P124" s="12" t="str"/>
+      <x:c r="Q124" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/we-can-fall-in-love/6791567989?uo=4</x:v>
+      </x:c>
+      <x:c r="R124" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S124" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3250.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T124" s="12" t="str"/>
+      <x:c r="U124" s="12" t="str"/>
+      <x:c r="V124" s="12" t="str"/>
+      <x:c r="W124" s="12" t="str"/>
+      <x:c r="X124" s="12" t="str"/>
+      <x:c r="Y124" s="12" t="str"/>
+      <x:c r="Z124" s="12" t="str"/>
+      <x:c r="AA124" s="12" t="str"/>
+      <x:c r="AB124" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC124" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD124" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE124" s="12" t="str">
+        <x:v>Collection note: We Can Fall in Love by Kimiko Kasai, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF124" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="AG124" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH124" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E7%AC%A0%E4%BA%95%E7%B4%80%E7%BE%8E%E5%AD%90/393034466?uo=4</x:v>
+      </x:c>
+      <x:c r="AI124" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="120" customHeight="1">
+      <x:c r="A125" s="12" t="str">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B125" s="12" t="str">
+        <x:v>山本達彦</x:v>
+      </x:c>
+      <x:c r="C125" s="12" t="str">
+        <x:v>Tatsuhiko Yamamoto</x:v>
+      </x:c>
+      <x:c r="D125" s="12" t="str"/>
+      <x:c r="E125" s="12" t="str">
+        <x:v>Faces: Tatsuhiko Singles</x:v>
+      </x:c>
+      <x:c r="F125" s="12" t="str"/>
+      <x:c r="G125" s="12" t="str"/>
+      <x:c r="H125" s="12" t="str"/>
+      <x:c r="I125" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J125" s="12" t="str"/>
+      <x:c r="K125" s="12" t="str"/>
+      <x:c r="L125" s="12" t="str"/>
+      <x:c r="M125" s="12" t="str"/>
+      <x:c r="N125" s="12" t="str">
+        <x:v>IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="O125" s="12" t="str">
+        <x:v>124_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P125" s="12" t="str"/>
+      <x:c r="Q125" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="R125" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S125" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3250.jpg. </x:v>
+      </x:c>
+      <x:c r="T125" s="12" t="str"/>
+      <x:c r="U125" s="12" t="str"/>
+      <x:c r="V125" s="12" t="str"/>
+      <x:c r="W125" s="12" t="str"/>
+      <x:c r="X125" s="12" t="str"/>
+      <x:c r="Y125" s="12" t="str"/>
+      <x:c r="Z125" s="12" t="str"/>
+      <x:c r="AA125" s="12" t="str"/>
+      <x:c r="AB125" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC125" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD125" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE125" s="12" t="str">
+        <x:v>Collection note: Faces: Tatsuhiko Singles by Tatsuhiko Yamamoto, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF125" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="AG125" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH125" s="12" t="str"/>
+      <x:c r="AI125" s="12" t="str"/>
+    </x:row>
+    <x:row r="126" ht="120" customHeight="1">
+      <x:c r="A126" s="12" t="str">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B126" s="12" t="str">
+        <x:v>山下達郎</x:v>
+      </x:c>
+      <x:c r="C126" s="12" t="str">
+        <x:v>Tatsuro Yamashita</x:v>
+      </x:c>
+      <x:c r="D126" s="12" t="str"/>
+      <x:c r="E126" s="12" t="str">
+        <x:v>Greatest Hits! Of Tatsuro Yamashita</x:v>
+      </x:c>
+      <x:c r="F126" s="12" t="str"/>
+      <x:c r="G126" s="12" t="str"/>
+      <x:c r="H126" s="12" t="str"/>
+      <x:c r="I126" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J126" s="12" t="str"/>
+      <x:c r="K126" s="12" t="str"/>
+      <x:c r="L126" s="12" t="str"/>
+      <x:c r="M126" s="12" t="str"/>
+      <x:c r="N126" s="12" t="str">
+        <x:v>IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="O126" s="12" t="str">
+        <x:v>125_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P126" s="12" t="str"/>
+      <x:c r="Q126" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="R126" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S126" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3250.jpg. </x:v>
+      </x:c>
+      <x:c r="T126" s="12" t="str"/>
+      <x:c r="U126" s="12" t="str"/>
+      <x:c r="V126" s="12" t="str"/>
+      <x:c r="W126" s="12" t="str"/>
+      <x:c r="X126" s="12" t="str"/>
+      <x:c r="Y126" s="12" t="str"/>
+      <x:c r="Z126" s="12" t="str"/>
+      <x:c r="AA126" s="12" t="str"/>
+      <x:c r="AB126" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC126" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD126" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE126" s="12" t="str">
+        <x:v>Collection note: Greatest Hits! Of Tatsuro Yamashita by Tatsuro Yamashita, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF126" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="AG126" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH126" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E5%B1%B1%E4%B8%8B%E9%81%94%E9%83%8E/74493141?uo=4</x:v>
+      </x:c>
+      <x:c r="AI126" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="120" customHeight="1">
+      <x:c r="A127" s="12" t="str">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B127" s="12" t="str">
+        <x:v>荒井由実</x:v>
+      </x:c>
+      <x:c r="C127" s="12" t="str">
+        <x:v>Yumi Arai</x:v>
+      </x:c>
+      <x:c r="D127" s="12" t="str">
+        <x:v>ミスリム</x:v>
+      </x:c>
+      <x:c r="E127" s="12" t="str">
+        <x:v>Misslim</x:v>
+      </x:c>
+      <x:c r="F127" s="12" t="str">
+        <x:v>Express</x:v>
+      </x:c>
+      <x:c r="G127" s="12" t="str"/>
+      <x:c r="H127" s="12" t="str">
+        <x:v>1974</x:v>
+      </x:c>
+      <x:c r="I127" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J127" s="12" t="str"/>
+      <x:c r="K127" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L127" s="12" t="str"/>
+      <x:c r="M127" s="12" t="str"/>
+      <x:c r="N127" s="12" t="str">
+        <x:v>IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="O127" s="12" t="str">
+        <x:v>126_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P127" s="12" t="str"/>
+      <x:c r="Q127" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/misslim/1436010441?uo=4</x:v>
+      </x:c>
+      <x:c r="R127" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S127" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3250.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T127" s="12" t="str"/>
+      <x:c r="U127" s="12" t="str"/>
+      <x:c r="V127" s="12" t="str"/>
+      <x:c r="W127" s="12" t="str"/>
+      <x:c r="X127" s="12" t="str"/>
+      <x:c r="Y127" s="12" t="str"/>
+      <x:c r="Z127" s="12" t="str"/>
+      <x:c r="AA127" s="12" t="str"/>
+      <x:c r="AB127" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC127" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD127" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE127" s="12" t="str">
+        <x:v>Collection note: Misslim by Yumi Arai, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF127" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="AG127" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH127" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E8%8D%92%E4%BA%95%E7%94%B1%E5%AE%9F/81316604?uo=4</x:v>
+      </x:c>
+      <x:c r="AI127" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="120" customHeight="1">
+      <x:c r="A128" s="12" t="str">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B128" s="12" t="str">
+        <x:v>石黒ケイ</x:v>
+      </x:c>
+      <x:c r="C128" s="12" t="str">
+        <x:v>Kei Ishiguro</x:v>
+      </x:c>
+      <x:c r="D128" s="12" t="str">
+        <x:v>アドリブ</x:v>
+      </x:c>
+      <x:c r="E128" s="12" t="str">
+        <x:v>Adlib</x:v>
+      </x:c>
+      <x:c r="F128" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G128" s="12" t="str"/>
+      <x:c r="H128" s="12" t="str">
+        <x:v>1980</x:v>
+      </x:c>
+      <x:c r="I128" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J128" s="12" t="str"/>
+      <x:c r="K128" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L128" s="12" t="str"/>
+      <x:c r="M128" s="12" t="str"/>
+      <x:c r="N128" s="12" t="str">
+        <x:v>IMG_3250.jpg</x:v>
+      </x:c>
+      <x:c r="O128" s="12" t="str">
+        <x:v>127_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P128" s="12" t="str"/>
+      <x:c r="Q128" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/adlib/1304789616?uo=4</x:v>
+      </x:c>
+      <x:c r="R128" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S128" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3250.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://www.hmv.co.jp/news/article/1008120060/</x:v>
+      </x:c>
+      <x:c r="T128" s="12" t="str"/>
+      <x:c r="U128" s="12" t="str"/>
+      <x:c r="V128" s="12" t="str"/>
+      <x:c r="W128" s="12" t="str"/>
+      <x:c r="X128" s="12" t="str"/>
+      <x:c r="Y128" s="12" t="str"/>
+      <x:c r="Z128" s="12" t="str"/>
+      <x:c r="AA128" s="12" t="str"/>
+      <x:c r="AB128" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC128" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD128" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE128" s="12" t="str">
+        <x:v>Kei Ishiguro’s fourth album, Adlib, was released in 1980. The sessions feature jazz musicians including saxophonist Art Pepper.</x:v>
+      </x:c>
+      <x:c r="AF128" s="12" t="str">
+        <x:v>https://www.hmv.co.jp/news/article/1008120060/</x:v>
+      </x:c>
+      <x:c r="AG128" s="12" t="str">
+        <x:v>HMV album feature</x:v>
+      </x:c>
+      <x:c r="AH128" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E7%9F%B3%E9%BB%92%E3%82%B1%E3%82%A4/75313854?uo=4</x:v>
+      </x:c>
+      <x:c r="AI128" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="120" customHeight="1">
+      <x:c r="A129" s="12" t="str">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B129" s="12" t="str">
+        <x:v>杏里</x:v>
+      </x:c>
+      <x:c r="C129" s="12" t="str">
+        <x:v>Anri</x:v>
+      </x:c>
+      <x:c r="D129" s="12" t="str">
+        <x:v>思いきりアメリカン</x:v>
+      </x:c>
+      <x:c r="E129" s="12" t="str">
+        <x:v>Omoikiri American: I Love Poppin' World, Anri</x:v>
+      </x:c>
+      <x:c r="F129" s="12" t="str"/>
+      <x:c r="G129" s="12" t="str"/>
+      <x:c r="H129" s="12" t="str">
+        <x:v>1982</x:v>
+      </x:c>
+      <x:c r="I129" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J129" s="12" t="str"/>
+      <x:c r="K129" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L129" s="12" t="str"/>
+      <x:c r="M129" s="12" t="str"/>
+      <x:c r="N129" s="12" t="str">
+        <x:v>IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="O129" s="12" t="str">
+        <x:v>128_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P129" s="12" t="str"/>
+      <x:c r="Q129" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E6%80%9D%E3%81%84%E3%81%8D%E3%82%8A%E3%82%A2%E3%83%A1%E3%83%AA%E3%82%AB%E3%83%B3i-love-poping-world-anri/844393212?uo=4</x:v>
+      </x:c>
+      <x:c r="R129" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S129" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3251.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T129" s="12" t="str"/>
+      <x:c r="U129" s="12" t="str"/>
+      <x:c r="V129" s="12" t="str"/>
+      <x:c r="W129" s="12" t="str"/>
+      <x:c r="X129" s="12" t="str"/>
+      <x:c r="Y129" s="12" t="str"/>
+      <x:c r="Z129" s="12" t="str"/>
+      <x:c r="AA129" s="12" t="str"/>
+      <x:c r="AB129" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC129" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD129" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE129" s="12" t="str">
+        <x:v>Collection note: Omoikiri American: I Love Poppin' World, Anri by Anri, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF129" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="AG129" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH129" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E6%9D%8F%E9%87%8C/141989016?uo=4</x:v>
+      </x:c>
+      <x:c r="AI129" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="120" customHeight="1">
+      <x:c r="A130" s="12" t="str">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B130" s="12" t="str">
+        <x:v>ハイ・ファイ・セット</x:v>
+      </x:c>
+      <x:c r="C130" s="12" t="str">
+        <x:v>Hi-Fi Set</x:v>
+      </x:c>
+      <x:c r="D130" s="12" t="str">
+        <x:v>ファッショナブル・ラヴァー</x:v>
+      </x:c>
+      <x:c r="E130" s="12" t="str">
+        <x:v>Fashionable Lover</x:v>
+      </x:c>
+      <x:c r="F130" s="12" t="str">
+        <x:v>Express</x:v>
+      </x:c>
+      <x:c r="G130" s="12" t="str"/>
+      <x:c r="H130" s="12" t="str"/>
+      <x:c r="I130" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J130" s="12" t="str"/>
+      <x:c r="K130" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L130" s="12" t="str"/>
+      <x:c r="M130" s="12" t="str"/>
+      <x:c r="N130" s="12" t="str">
+        <x:v>IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="O130" s="12" t="str">
+        <x:v>129_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P130" s="12" t="str"/>
+      <x:c r="Q130" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E3%83%95%E3%82%A1%E3%83%83%E3%82%B7%E3%83%A7%E3%83%8A%E3%83%96%E3%83%AB-%E3%83%A9%E3%83%B4%E3%82%A1%E3%83%BC/1536764651?uo=4</x:v>
+      </x:c>
+      <x:c r="R130" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S130" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3251.jpg. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T130" s="12" t="str"/>
+      <x:c r="U130" s="12" t="str"/>
+      <x:c r="V130" s="12" t="str"/>
+      <x:c r="W130" s="12" t="str"/>
+      <x:c r="X130" s="12" t="str"/>
+      <x:c r="Y130" s="12" t="str"/>
+      <x:c r="Z130" s="12" t="str"/>
+      <x:c r="AA130" s="12" t="str"/>
+      <x:c r="AB130" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC130" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD130" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE130" s="12" t="str">
+        <x:v>Collection note: Fashionable Lover by Hi-Fi Set, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF130" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="AG130" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH130" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E3%83%8F%E3%82%A4-%E3%83%95%E3%82%A1%E3%82%A4-%E3%82%BB%E3%83%83%E3%83%88/74568160?uo=4</x:v>
+      </x:c>
+      <x:c r="AI130" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="120" customHeight="1">
+      <x:c r="A131" s="12" t="str">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B131" s="12" t="str">
+        <x:v>藤圭子</x:v>
+      </x:c>
+      <x:c r="C131" s="12" t="str">
+        <x:v>Keiko Fuji</x:v>
+      </x:c>
+      <x:c r="D131" s="12" t="str">
+        <x:v>演歌の旅 緋牡丹博徒</x:v>
+      </x:c>
+      <x:c r="E131" s="12" t="str">
+        <x:v>Enka no Tabi: Hibotan Bakuto</x:v>
+      </x:c>
+      <x:c r="F131" s="12" t="str">
+        <x:v>RCA</x:v>
+      </x:c>
+      <x:c r="G131" s="12" t="str"/>
+      <x:c r="H131" s="12" t="str"/>
+      <x:c r="I131" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J131" s="12" t="str"/>
+      <x:c r="K131" s="12" t="str"/>
+      <x:c r="L131" s="12" t="str"/>
+      <x:c r="M131" s="12" t="str"/>
+      <x:c r="N131" s="12" t="str">
+        <x:v>IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="O131" s="12" t="str">
+        <x:v>130_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P131" s="12" t="str"/>
+      <x:c r="Q131" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="R131" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S131" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3251.jpg. </x:v>
+      </x:c>
+      <x:c r="T131" s="12" t="str"/>
+      <x:c r="U131" s="12" t="str"/>
+      <x:c r="V131" s="12" t="str"/>
+      <x:c r="W131" s="12" t="str"/>
+      <x:c r="X131" s="12" t="str"/>
+      <x:c r="Y131" s="12" t="str"/>
+      <x:c r="Z131" s="12" t="str"/>
+      <x:c r="AA131" s="12" t="str"/>
+      <x:c r="AB131" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC131" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD131" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE131" s="12" t="str">
+        <x:v>Collection note: Enka no Tabi: Hibotan Bakuto by Keiko Fuji, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF131" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="AG131" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH131" s="12" t="str">
+        <x:v>https://www.discogs.com/artist/1070643</x:v>
+      </x:c>
+      <x:c r="AI131" s="12" t="str">
+        <x:v>Discogs artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="120" customHeight="1">
+      <x:c r="A132" s="12" t="str">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B132" s="12" t="str">
+        <x:v>和田アキ子</x:v>
+      </x:c>
+      <x:c r="C132" s="12" t="str">
+        <x:v>Akiko Wada</x:v>
+      </x:c>
+      <x:c r="D132" s="12" t="str"/>
+      <x:c r="E132" s="12" t="str">
+        <x:v>Akiko Wada (green blouse portrait sleeve)</x:v>
+      </x:c>
+      <x:c r="F132" s="12" t="str">
+        <x:v>RCA</x:v>
+      </x:c>
+      <x:c r="G132" s="12" t="str"/>
+      <x:c r="H132" s="12" t="str"/>
+      <x:c r="I132" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J132" s="12" t="str"/>
+      <x:c r="K132" s="12" t="str"/>
+      <x:c r="L132" s="12" t="str"/>
+      <x:c r="M132" s="12" t="str"/>
+      <x:c r="N132" s="12" t="str">
+        <x:v>IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="O132" s="12" t="str">
+        <x:v>131_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P132" s="12" t="str"/>
+      <x:c r="Q132" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="R132" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S132" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3251.jpg. </x:v>
+      </x:c>
+      <x:c r="T132" s="12" t="str"/>
+      <x:c r="U132" s="12" t="str"/>
+      <x:c r="V132" s="12" t="str"/>
+      <x:c r="W132" s="12" t="str"/>
+      <x:c r="X132" s="12" t="str"/>
+      <x:c r="Y132" s="12" t="str"/>
+      <x:c r="Z132" s="12" t="str"/>
+      <x:c r="AA132" s="12" t="str"/>
+      <x:c r="AB132" s="12" t="str">
+        <x:v>Exact title needs a back-cover or label photo | Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC132" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD132" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE132" s="12" t="str">
+        <x:v>Collection note: Akiko Wada (green blouse portrait sleeve). Identification is incomplete; the original reference photograph is retained for checking the sleeve and labels.</x:v>
+      </x:c>
+      <x:c r="AF132" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="AG132" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH132" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E5%92%8C%E7%94%B0%E3%82%A2%E3%82%AD%E5%AD%90/79156915?uo=4</x:v>
+      </x:c>
+      <x:c r="AI132" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="120" customHeight="1">
+      <x:c r="A133" s="12" t="str">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B133" s="12" t="str">
+        <x:v>キャンディーズ</x:v>
+      </x:c>
+      <x:c r="C133" s="12" t="str">
+        <x:v>Candies</x:v>
+      </x:c>
+      <x:c r="D133" s="12" t="str"/>
+      <x:c r="E133" s="12" t="str">
+        <x:v>The Best</x:v>
+      </x:c>
+      <x:c r="F133" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G133" s="12" t="str"/>
+      <x:c r="H133" s="12" t="str"/>
+      <x:c r="I133" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J133" s="12" t="str"/>
+      <x:c r="K133" s="12" t="str"/>
+      <x:c r="L133" s="12" t="str"/>
+      <x:c r="M133" s="12" t="str"/>
+      <x:c r="N133" s="12" t="str">
+        <x:v>IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="O133" s="12" t="str">
+        <x:v>132_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P133" s="12" t="str"/>
+      <x:c r="Q133" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="R133" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S133" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3251.jpg. </x:v>
+      </x:c>
+      <x:c r="T133" s="12" t="str"/>
+      <x:c r="U133" s="12" t="str"/>
+      <x:c r="V133" s="12" t="str"/>
+      <x:c r="W133" s="12" t="str"/>
+      <x:c r="X133" s="12" t="str"/>
+      <x:c r="Y133" s="12" t="str"/>
+      <x:c r="Z133" s="12" t="str"/>
+      <x:c r="AA133" s="12" t="str"/>
+      <x:c r="AB133" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC133" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD133" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE133" s="12" t="str">
+        <x:v>Collection note: Candies compilation titled The Best. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF133" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="AG133" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH133" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E3%82%AD%E3%83%A3%E3%83%B3%E3%83%87%E3%82%A3%E3%83%BC%E3%82%BA/555222297?uo=4</x:v>
+      </x:c>
+      <x:c r="AI133" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="120" customHeight="1">
+      <x:c r="A134" s="12" t="str">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B134" s="12" t="str">
+        <x:v>木之内みどり</x:v>
+      </x:c>
+      <x:c r="C134" s="12" t="str">
+        <x:v>Midori Kinouchi</x:v>
+      </x:c>
+      <x:c r="D134" s="12" t="str">
+        <x:v>全曲集</x:v>
+      </x:c>
+      <x:c r="E134" s="12" t="str">
+        <x:v>Best 24: Zenkyokushu</x:v>
+      </x:c>
+      <x:c r="F134" s="12" t="str"/>
+      <x:c r="G134" s="12" t="str"/>
+      <x:c r="H134" s="12" t="str"/>
+      <x:c r="I134" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J134" s="12" t="str"/>
+      <x:c r="K134" s="12" t="str"/>
+      <x:c r="L134" s="12" t="str"/>
+      <x:c r="M134" s="12" t="str"/>
+      <x:c r="N134" s="12" t="str">
+        <x:v>IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="O134" s="12" t="str">
+        <x:v>133_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P134" s="12" t="str"/>
+      <x:c r="Q134" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="R134" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S134" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3251.jpg. </x:v>
+      </x:c>
+      <x:c r="T134" s="12" t="str"/>
+      <x:c r="U134" s="12" t="str"/>
+      <x:c r="V134" s="12" t="str"/>
+      <x:c r="W134" s="12" t="str"/>
+      <x:c r="X134" s="12" t="str"/>
+      <x:c r="Y134" s="12" t="str"/>
+      <x:c r="Z134" s="12" t="str"/>
+      <x:c r="AA134" s="12" t="str"/>
+      <x:c r="AB134" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC134" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD134" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE134" s="12" t="str">
+        <x:v>Collection note: Midori Kinouchi compilation titled Best 24: Zenkyokushu. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF134" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="AG134" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH134" s="12" t="str"/>
+      <x:c r="AI134" s="12" t="str"/>
+    </x:row>
+    <x:row r="135" ht="120" customHeight="1">
+      <x:c r="A135" s="12" t="str">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B135" s="12" t="str">
+        <x:v>南沙織</x:v>
+      </x:c>
+      <x:c r="C135" s="12" t="str">
+        <x:v>Saori Minami</x:v>
+      </x:c>
+      <x:c r="D135" s="12" t="str">
+        <x:v>THE BEST /again 南沙織</x:v>
+      </x:c>
+      <x:c r="E135" s="12" t="str">
+        <x:v>The Best / Again</x:v>
+      </x:c>
+      <x:c r="F135" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G135" s="12" t="str"/>
+      <x:c r="H135" s="12" t="str">
+        <x:v>1981</x:v>
+      </x:c>
+      <x:c r="I135" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J135" s="12" t="str"/>
+      <x:c r="K135" s="12" t="str"/>
+      <x:c r="L135" s="12" t="str"/>
+      <x:c r="M135" s="12" t="str"/>
+      <x:c r="N135" s="12" t="str">
+        <x:v>IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="O135" s="12" t="str">
+        <x:v>134_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P135" s="12" t="str"/>
+      <x:c r="Q135" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="R135" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S135" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3251.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Metadata source: https://www.sonymusic.co.jp/Music/Info/cynthia/disco/album/a39.html</x:v>
+      </x:c>
+      <x:c r="T135" s="12" t="str"/>
+      <x:c r="U135" s="12" t="str"/>
+      <x:c r="V135" s="12" t="str"/>
+      <x:c r="W135" s="12" t="str"/>
+      <x:c r="X135" s="12" t="str"/>
+      <x:c r="Y135" s="12" t="str"/>
+      <x:c r="Z135" s="12" t="str"/>
+      <x:c r="AA135" s="12" t="str"/>
+      <x:c r="AB135" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC135" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD135" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE135" s="12" t="str">
+        <x:v>Released in November 1981, The Best / Again collects fourteen Saori Minami songs, including 17-sai, Irozuku Machi and the Japanese version of Goodbye Girl.</x:v>
+      </x:c>
+      <x:c r="AF135" s="12" t="str">
+        <x:v>https://www.sonymusic.co.jp/Music/Info/cynthia/disco/album/a39.html</x:v>
+      </x:c>
+      <x:c r="AG135" s="12" t="str">
+        <x:v>Sony Music official discography</x:v>
+      </x:c>
+      <x:c r="AH135" s="12" t="str">
+        <x:v>https://www.sonymusic.co.jp/Music/Info/cynthia/</x:v>
+      </x:c>
+      <x:c r="AI135" s="12" t="str">
+        <x:v>Sony Music artist profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="120" customHeight="1">
+      <x:c r="A136" s="12" t="str">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B136" s="12" t="str">
+        <x:v>吉田拓郎</x:v>
+      </x:c>
+      <x:c r="C136" s="12" t="str">
+        <x:v>Takuro Yoshida</x:v>
+      </x:c>
+      <x:c r="D136" s="12" t="str">
+        <x:v>王様達のハイキング・イン・武道館</x:v>
+      </x:c>
+      <x:c r="E136" s="12" t="str">
+        <x:v>Live '82: Osamatachi no Hiking in Budokan</x:v>
+      </x:c>
+      <x:c r="F136" s="12" t="str"/>
+      <x:c r="G136" s="12" t="str"/>
+      <x:c r="H136" s="12" t="str"/>
+      <x:c r="I136" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J136" s="12" t="str"/>
+      <x:c r="K136" s="12" t="str"/>
+      <x:c r="L136" s="12" t="str"/>
+      <x:c r="M136" s="12" t="str"/>
+      <x:c r="N136" s="12" t="str">
+        <x:v>IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="O136" s="12" t="str">
+        <x:v>135_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P136" s="12" t="str"/>
+      <x:c r="Q136" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="R136" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S136" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3251.jpg. </x:v>
+      </x:c>
+      <x:c r="T136" s="12" t="str"/>
+      <x:c r="U136" s="12" t="str"/>
+      <x:c r="V136" s="12" t="str"/>
+      <x:c r="W136" s="12" t="str"/>
+      <x:c r="X136" s="12" t="str"/>
+      <x:c r="Y136" s="12" t="str"/>
+      <x:c r="Z136" s="12" t="str"/>
+      <x:c r="AA136" s="12" t="str"/>
+      <x:c r="AB136" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC136" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD136" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE136" s="12" t="str">
+        <x:v>Collection note: Live '82: Osamatachi no Hiking in Budokan by Takuro Yoshida, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF136" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3251.jpg</x:v>
+      </x:c>
+      <x:c r="AG136" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH136" s="12" t="str"/>
+      <x:c r="AI136" s="12" t="str"/>
+    </x:row>
+    <x:row r="137" ht="120" customHeight="1">
+      <x:c r="A137" s="12" t="str">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B137" s="12" t="str">
+        <x:v>丸山圭子</x:v>
+      </x:c>
+      <x:c r="C137" s="12" t="str">
+        <x:v>Keiko Maruyama</x:v>
+      </x:c>
+      <x:c r="D137" s="12" t="str">
+        <x:v>黄昏めもりい</x:v>
+      </x:c>
+      <x:c r="E137" s="12" t="str">
+        <x:v>Tasogare Memory</x:v>
+      </x:c>
+      <x:c r="F137" s="12" t="str">
+        <x:v>King</x:v>
+      </x:c>
+      <x:c r="G137" s="12" t="str">
+        <x:v>SKD-1036</x:v>
+      </x:c>
+      <x:c r="H137" s="12" t="str">
+        <x:v>1976</x:v>
+      </x:c>
+      <x:c r="I137" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J137" s="12" t="str"/>
+      <x:c r="K137" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L137" s="12" t="str"/>
+      <x:c r="M137" s="12" t="str"/>
+      <x:c r="N137" s="12" t="str">
+        <x:v>IMG_3252.jpg</x:v>
+      </x:c>
+      <x:c r="O137" s="12" t="str">
+        <x:v>136_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P137" s="12" t="str"/>
+      <x:c r="Q137" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/tasogare-memory/1655086395?uo=4</x:v>
+      </x:c>
+      <x:c r="R137" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S137" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3252.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. Metadata source: https://www.stereo-records.com/detail.php?itemCd=88496</x:v>
+      </x:c>
+      <x:c r="T137" s="12" t="str"/>
+      <x:c r="U137" s="12" t="str"/>
+      <x:c r="V137" s="12" t="str"/>
+      <x:c r="W137" s="12" t="str"/>
+      <x:c r="X137" s="12" t="str"/>
+      <x:c r="Y137" s="12" t="str"/>
+      <x:c r="Z137" s="12" t="str"/>
+      <x:c r="AA137" s="12" t="str"/>
+      <x:c r="AB137" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC137" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD137" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE137" s="12" t="str">
+        <x:v>Keiko Maruyama’s 1976 album Tasogare Memory includes Dozo Kono Mama, Rhapsody in Blue and Bye Bye. This sleeve shows King catalogue number SKD-1036.</x:v>
+      </x:c>
+      <x:c r="AF137" s="12" t="str">
+        <x:v>https://www.stereo-records.com/detail.php?itemCd=88496</x:v>
+      </x:c>
+      <x:c r="AG137" s="12" t="str">
+        <x:v>Stereo Records release listing</x:v>
+      </x:c>
+      <x:c r="AH137" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E4%B8%B8%E5%B1%B1%E5%9C%AD%E5%AD%90/204557857?uo=4</x:v>
+      </x:c>
+      <x:c r="AI137" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="120" customHeight="1">
+      <x:c r="A138" s="12" t="str">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B138" s="12" t="str">
+        <x:v>浅田美代子</x:v>
+      </x:c>
+      <x:c r="C138" s="12" t="str">
+        <x:v>Miyoko Asada</x:v>
+      </x:c>
+      <x:c r="D138" s="12" t="str">
+        <x:v>ヒット全曲集</x:v>
+      </x:c>
+      <x:c r="E138" s="12" t="str">
+        <x:v>Hit Zenkyokushu</x:v>
+      </x:c>
+      <x:c r="F138" s="12" t="str">
+        <x:v>CBS/Sony</x:v>
+      </x:c>
+      <x:c r="G138" s="12" t="str"/>
+      <x:c r="H138" s="12" t="str"/>
+      <x:c r="I138" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J138" s="12" t="str"/>
+      <x:c r="K138" s="12" t="str"/>
+      <x:c r="L138" s="12" t="str"/>
+      <x:c r="M138" s="12" t="str"/>
+      <x:c r="N138" s="12" t="str">
+        <x:v>IMG_3252.jpg</x:v>
+      </x:c>
+      <x:c r="O138" s="12" t="str">
+        <x:v>137_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P138" s="12" t="str"/>
+      <x:c r="Q138" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3252.jpg</x:v>
+      </x:c>
+      <x:c r="R138" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S138" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3252.jpg. </x:v>
+      </x:c>
+      <x:c r="T138" s="12" t="str"/>
+      <x:c r="U138" s="12" t="str"/>
+      <x:c r="V138" s="12" t="str"/>
+      <x:c r="W138" s="12" t="str"/>
+      <x:c r="X138" s="12" t="str"/>
+      <x:c r="Y138" s="12" t="str"/>
+      <x:c r="Z138" s="12" t="str"/>
+      <x:c r="AA138" s="12" t="str"/>
+      <x:c r="AB138" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC138" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD138" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE138" s="12" t="str">
+        <x:v>Collection note: Miyoko Asada compilation titled Hit Zenkyokushu. The photographed sleeve identifies the collection; its exact pressing and track list still need checking.</x:v>
+      </x:c>
+      <x:c r="AF138" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3252.jpg</x:v>
+      </x:c>
+      <x:c r="AG138" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH138" s="12" t="str"/>
+      <x:c r="AI138" s="12" t="str"/>
+    </x:row>
+    <x:row r="139" ht="120" customHeight="1">
+      <x:c r="A139" s="12" t="str">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B139" s="12" t="str">
+        <x:v>赤い鳥</x:v>
+      </x:c>
+      <x:c r="C139" s="12" t="str">
+        <x:v>The Red Birds (Akai Tori)</x:v>
+      </x:c>
+      <x:c r="D139" s="12" t="str">
+        <x:v>竹田の子守唄</x:v>
+      </x:c>
+      <x:c r="E139" s="12" t="str">
+        <x:v>Takeda no Komoriuta</x:v>
+      </x:c>
+      <x:c r="F139" s="12" t="str">
+        <x:v>Liberty</x:v>
+      </x:c>
+      <x:c r="G139" s="12" t="str"/>
+      <x:c r="H139" s="12" t="str">
+        <x:v>1971</x:v>
+      </x:c>
+      <x:c r="I139" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J139" s="12" t="str"/>
+      <x:c r="K139" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L139" s="12" t="str"/>
+      <x:c r="M139" s="12" t="str"/>
+      <x:c r="N139" s="12" t="str">
+        <x:v>IMG_3252.jpg</x:v>
+      </x:c>
+      <x:c r="O139" s="12" t="str">
+        <x:v>138_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P139" s="12" t="str"/>
+      <x:c r="Q139" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/%E7%AB%B9%E7%94%B0%E3%81%AE%E5%AD%90%E5%AE%88%E5%94%84/1536765405?uo=4</x:v>
+      </x:c>
+      <x:c r="R139" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S139" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3252.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T139" s="12" t="str"/>
+      <x:c r="U139" s="12" t="str"/>
+      <x:c r="V139" s="12" t="str"/>
+      <x:c r="W139" s="12" t="str"/>
+      <x:c r="X139" s="12" t="str"/>
+      <x:c r="Y139" s="12" t="str"/>
+      <x:c r="Z139" s="12" t="str"/>
+      <x:c r="AA139" s="12" t="str"/>
+      <x:c r="AB139" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC139" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD139" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE139" s="12" t="str">
+        <x:v>Collection note: Takeda no Komoriuta by The Red Birds, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF139" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3252.jpg</x:v>
+      </x:c>
+      <x:c r="AG139" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH139" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E8%B5%A4%E3%81%84%E9%B3%A5/207332572?uo=4</x:v>
+      </x:c>
+      <x:c r="AI139" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="120" customHeight="1">
+      <x:c r="A140" s="12" t="str">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B140" s="12" t="str">
+        <x:v>松任谷由実</x:v>
+      </x:c>
+      <x:c r="C140" s="12" t="str">
+        <x:v>Yumi Matsutoya</x:v>
+      </x:c>
+      <x:c r="D140" s="12" t="str">
+        <x:v>リ・インカーネイション</x:v>
+      </x:c>
+      <x:c r="E140" s="12" t="str">
+        <x:v>Reincarnation</x:v>
+      </x:c>
+      <x:c r="F140" s="12" t="str">
+        <x:v>Express</x:v>
+      </x:c>
+      <x:c r="G140" s="12" t="str"/>
+      <x:c r="H140" s="12" t="str">
+        <x:v>1983</x:v>
+      </x:c>
+      <x:c r="I140" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J140" s="12" t="str"/>
+      <x:c r="K140" s="12" t="str">
+        <x:v>Pop</x:v>
+      </x:c>
+      <x:c r="L140" s="12" t="str"/>
+      <x:c r="M140" s="12" t="str"/>
+      <x:c r="N140" s="12" t="str">
+        <x:v>IMG_3252.jpg</x:v>
+      </x:c>
+      <x:c r="O140" s="12" t="str">
+        <x:v>139_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P140" s="12" t="str"/>
+      <x:c r="Q140" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/reincarnation/1436015852?uo=4</x:v>
+      </x:c>
+      <x:c r="R140" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S140" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3252.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T140" s="12" t="str"/>
+      <x:c r="U140" s="12" t="str"/>
+      <x:c r="V140" s="12" t="str"/>
+      <x:c r="W140" s="12" t="str"/>
+      <x:c r="X140" s="12" t="str"/>
+      <x:c r="Y140" s="12" t="str"/>
+      <x:c r="Z140" s="12" t="str"/>
+      <x:c r="AA140" s="12" t="str"/>
+      <x:c r="AB140" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC140" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD140" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE140" s="12" t="str">
+        <x:v>Collection note: Reincarnation by Yumi Matsutoya, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF140" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3252.jpg</x:v>
+      </x:c>
+      <x:c r="AG140" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH140" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E6%9D%BE%E4%BB%BB%E8%B0%B7%E7%94%B1%E5%AE%9F/76458419?uo=4</x:v>
+      </x:c>
+      <x:c r="AI140" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="120" customHeight="1">
+      <x:c r="A141" s="12" t="str">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B141" s="12" t="str">
+        <x:v>美空ひばり</x:v>
+      </x:c>
+      <x:c r="C141" s="12" t="str">
+        <x:v>Hibari Misora</x:v>
+      </x:c>
+      <x:c r="D141" s="12" t="str"/>
+      <x:c r="E141" s="12" t="str">
+        <x:v>Title to verify (white kimono and moon sleeve)</x:v>
+      </x:c>
+      <x:c r="F141" s="12" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="G141" s="12" t="str"/>
+      <x:c r="H141" s="12" t="str"/>
+      <x:c r="I141" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J141" s="12" t="str"/>
+      <x:c r="K141" s="12" t="str"/>
+      <x:c r="L141" s="12" t="str"/>
+      <x:c r="M141" s="12" t="str"/>
+      <x:c r="N141" s="12" t="str">
+        <x:v>IMG_3253.jpg</x:v>
+      </x:c>
+      <x:c r="O141" s="12" t="str">
+        <x:v>140_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P141" s="12" t="str"/>
+      <x:c r="Q141" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3253.jpg</x:v>
+      </x:c>
+      <x:c r="R141" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S141" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3253.jpg. </x:v>
+      </x:c>
+      <x:c r="T141" s="12" t="str"/>
+      <x:c r="U141" s="12" t="str"/>
+      <x:c r="V141" s="12" t="str"/>
+      <x:c r="W141" s="12" t="str"/>
+      <x:c r="X141" s="12" t="str"/>
+      <x:c r="Y141" s="12" t="str"/>
+      <x:c r="Z141" s="12" t="str"/>
+      <x:c r="AA141" s="12" t="str"/>
+      <x:c r="AB141" s="12" t="str">
+        <x:v>Exact title needs a back-cover or label photo | Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC141" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD141" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE141" s="12" t="str">
+        <x:v>Collection note: Title to verify (white kimono and moon sleeve). Identification is incomplete; the original reference photograph is retained for checking the sleeve and labels.</x:v>
+      </x:c>
+      <x:c r="AF141" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3253.jpg</x:v>
+      </x:c>
+      <x:c r="AG141" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH141" s="12" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Hibari_Misora</x:v>
+      </x:c>
+      <x:c r="AI141" s="12" t="str">
+        <x:v>Wikipedia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="120" customHeight="1">
+      <x:c r="A142" s="12" t="str">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B142" s="12" t="str">
+        <x:v>二葉百合子</x:v>
+      </x:c>
+      <x:c r="C142" s="12" t="str">
+        <x:v>Yuriko Futaba</x:v>
+      </x:c>
+      <x:c r="D142" s="12" t="str">
+        <x:v>演歌大劇場</x:v>
+      </x:c>
+      <x:c r="E142" s="12" t="str">
+        <x:v>Enka Daigekijo</x:v>
+      </x:c>
+      <x:c r="F142" s="12" t="str">
+        <x:v>King</x:v>
+      </x:c>
+      <x:c r="G142" s="12" t="str"/>
+      <x:c r="H142" s="12" t="str"/>
+      <x:c r="I142" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J142" s="12" t="str"/>
+      <x:c r="K142" s="12" t="str"/>
+      <x:c r="L142" s="12" t="str"/>
+      <x:c r="M142" s="12" t="str"/>
+      <x:c r="N142" s="12" t="str">
+        <x:v>IMG_3253.jpg</x:v>
+      </x:c>
+      <x:c r="O142" s="12" t="str">
+        <x:v>141_reference_crop.jpg</x:v>
+      </x:c>
+      <x:c r="P142" s="12" t="str"/>
+      <x:c r="Q142" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3253.jpg</x:v>
+      </x:c>
+      <x:c r="R142" s="12" t="str">
+        <x:v>reference_photo</x:v>
+      </x:c>
+      <x:c r="S142" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3253.jpg. </x:v>
+      </x:c>
+      <x:c r="T142" s="12" t="str"/>
+      <x:c r="U142" s="12" t="str"/>
+      <x:c r="V142" s="12" t="str"/>
+      <x:c r="W142" s="12" t="str"/>
+      <x:c r="X142" s="12" t="str"/>
+      <x:c r="Y142" s="12" t="str"/>
+      <x:c r="Z142" s="12" t="str"/>
+      <x:c r="AA142" s="12" t="str"/>
+      <x:c r="AB142" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed | Release year unverified</x:v>
+      </x:c>
+      <x:c r="AC142" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD142" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE142" s="12" t="str">
+        <x:v>Collection note: Enka Daigekijo by Yuriko Futaba, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF142" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3253.jpg</x:v>
+      </x:c>
+      <x:c r="AG142" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH142" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E4%BA%8C%E8%91%89%E7%99%BE%E5%90%88%E5%AD%90/1535229692?uo=4</x:v>
+      </x:c>
+      <x:c r="AI142" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="120" customHeight="1">
+      <x:c r="A143" s="12" t="str">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B143" s="12" t="str">
+        <x:v>森進一</x:v>
+      </x:c>
+      <x:c r="C143" s="12" t="str">
+        <x:v>Shinichi Mori</x:v>
+      </x:c>
+      <x:c r="D143" s="12" t="str">
+        <x:v>再会</x:v>
+      </x:c>
+      <x:c r="E143" s="12" t="str">
+        <x:v>Saikai</x:v>
+      </x:c>
+      <x:c r="F143" s="12" t="str">
+        <x:v>Victor</x:v>
+      </x:c>
+      <x:c r="G143" s="12" t="str"/>
+      <x:c r="H143" s="12" t="str">
+        <x:v>1971</x:v>
+      </x:c>
+      <x:c r="I143" s="12" t="str">
+        <x:v>LP</x:v>
+      </x:c>
+      <x:c r="J143" s="12" t="str"/>
+      <x:c r="K143" s="12" t="str">
+        <x:v>Kayokyoku</x:v>
+      </x:c>
+      <x:c r="L143" s="12" t="str"/>
+      <x:c r="M143" s="12" t="str"/>
+      <x:c r="N143" s="12" t="str">
+        <x:v>IMG_3253.jpg</x:v>
+      </x:c>
+      <x:c r="O143" s="12" t="str">
+        <x:v>142_official_front.jpg</x:v>
+      </x:c>
+      <x:c r="P143" s="12" t="str"/>
+      <x:c r="Q143" s="12" t="str">
+        <x:v>https://music.apple.com/jp/album/saikai/1538372864?uo=4</x:v>
+      </x:c>
+      <x:c r="R143" s="12" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="S143" s="12" t="str">
+        <x:v>Identified from the front sleeve in IMG_3253.jpg. Year is the album/release date from the cited discography or digital catalogue; the physical pressing date remains unconfirmed. Published artwork visually compared with the reference sleeve; digital artwork may omit the original obi. </x:v>
+      </x:c>
+      <x:c r="T143" s="12" t="str"/>
+      <x:c r="U143" s="12" t="str"/>
+      <x:c r="V143" s="12" t="str"/>
+      <x:c r="W143" s="12" t="str"/>
+      <x:c r="X143" s="12" t="str"/>
+      <x:c r="Y143" s="12" t="str"/>
+      <x:c r="Z143" s="12" t="str"/>
+      <x:c r="AA143" s="12" t="str"/>
+      <x:c r="AB143" s="12" t="str">
+        <x:v>Exact pressing and catalogue number need label verification | Track list not yet transcribed</x:v>
+      </x:c>
+      <x:c r="AC143" s="12" t="str">
+        <x:v>Needs verification</x:v>
+      </x:c>
+      <x:c r="AD143" s="12" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AE143" s="12" t="str">
+        <x:v>Collection note: Saikai by Shinichi Mori, identified from the photographed sleeve. Exact pressing details and the track list remain to be checked.</x:v>
+      </x:c>
+      <x:c r="AF143" s="12" t="str">
+        <x:v>https://github.com/richardmands/record_collection/blob/main/data/reference-photos/IMG_3253.jpg</x:v>
+      </x:c>
+      <x:c r="AG143" s="12" t="str">
+        <x:v>Collection notes from reference photograph</x:v>
+      </x:c>
+      <x:c r="AH143" s="12" t="str">
+        <x:v>https://music.apple.com/jp/artist/%E6%A3%AE-%E9%80%B2%E4%B8%80/275368573?uo=4</x:v>
+      </x:c>
+      <x:c r="AI143" s="12" t="str">
+        <x:v>Artist on Apple Music</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23c16bbbadd34bfe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b52e77f737749b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12547,7 +20166,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8567bfd133c54917"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R696d8e1c069b4c0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
